--- a/1年内销售库存大于10育种+上海_补全结果.xlsx
+++ b/1年内销售库存大于10育种+上海_补全结果.xlsx
@@ -504,8 +504,6 @@
           <t>兰卡</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>兰卡椰壳是一种优质的土壤改良材料，采用天然椰壳经过特殊工艺加工而成。具有良好的透气性、保水性和排水性，能够有效改善土壤结构，增加介质疏松度。适用于兰花、虎皮兰、吊兰等肉质根系的植物栽培，也可与泥炭土、珍珠岩等混合使用，配制成适合各类盆栽植物的复合介质。能有效防止土壤板结，减少根系腐烂风险，是家庭园艺和商业花卉栽培中常用的基础改良材料。</t>
@@ -548,8 +546,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>帝罗马国际盆白陶15，意大利进口品牌花盆，采用优质白陶材质，透气性好，有利于植物根系生长。简约欧式设计风格，质感细腻，适合种植各类花卉绿植，可用于阳台、花园、室内等场景装饰。15寸规格适合中小型植物栽培。</t>
@@ -592,8 +588,6 @@
           <t>印度椰糠</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>印度椰糠低盐款是一种优质的园艺栽培介质，由椰子外壳纤维加工而成。经过特殊工艺处理，盐分含量低，适合各种花卉、蔬菜的种植。可单独使用或与其他介质混合使用具有良好的透气性、保水性和排水性，能为植物根系提供健康的生长环境。适用于播种、育苗、换盆等园艺操作，是家庭园艺和商业种植的理想选择。</t>
@@ -636,8 +630,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>福袋花彩师植物营养颗粒（爆花型）是一款专为促进开花植物设计的园艺肥料。产品为颗粒状缓释肥料，规格16g/袋，适合各类开花植物如月季、绣球、铁线莲等使用。富含磷钾元素及微量元素，能有效促进花芽分化、增加开花数量、提升花色鲜艳度。使用时均匀撒施于盆土表面或浅埋土中，肥效持久省心。注意避免直接接触植株根部，薄肥勤施效果更佳。</t>
@@ -680,8 +672,6 @@
           <t>成都神龙</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>成都神龙园艺家品牌12升容量花盆，代工生产产品。适用于家庭园艺种植，可用于栽种各类花卉、蔬菜及小型植物。12L容量适合中型植物换盆或种植需求，材质通常为塑料或树脂，耐用轻便。选购时需注意盆底排水孔设计，确保透气透水性。建议根据植物生长需求选择合适尺寸花盆，定期换盆可促进植物根系发育。</t>
@@ -719,9 +709,6 @@
           <t>椰糠</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>印度椰糠颗粒是采用印度优质椰子外壳经加工而成的园艺栽培介质。颗粒状结构质地轻盈、疏松透气、排水良好，富含植物生长所需的有机质和微量元素，pH值呈弱酸性至中性，非常适合各类园艺植物栽培使用。可单独使用或与其他介质（如泥炭土、赤玉土等）混合使用，广泛应用于多肉植物、兰花、盆栽花卉及蔬菜育苗等领域，能有效改善土壤结构，防止盆土板结，促进根系健康生长。使用前建议清洗或浸泡脱盐处理后再行使用。</t>
@@ -868,8 +855,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>花彩师植物营养液通用型是一款高效浓缩的水溶性肥料，规格为18g/袋。该产品采用科学配比，富含氮磷钾及多种微量元素，能为各类植物提供全面均衡的营养支持。适用于家庭园艺中的花卉、蔬菜、果树等植物的追肥使用。使用时按比例稀释后浇灌或叶面喷施即可，操作简便。本品溶解性好，吸收率高，可促进植物生长发育，增强植株抗病能力，改善开花结果质量。建议在植物生长期每隔7-10天使用一次效果更佳。</t>
@@ -912,8 +897,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>花彩师生根液是一种植物生长调节剂，主要用于促进植物根系发育，提高扦插成活率。适用于花卉、蔬菜、林木等多种植物的扦插、移栽、换盆等场景。能快速诱导不定根形成，增强根系活力，提高植物抗逆性。本品为50ml包装，稀释后使用，使用时需注意浓度，避免灼伤植物根部。</t>
@@ -931,14 +914,46 @@
           <t>虹安宿根 紫菀"小卡罗"</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>植物</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>种苗苗木</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>多年生草本</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>其他多年生草本</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>虹安</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>紫菀</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>小卡罗</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>虹安宿根紫菀“小卡罗”是多年生草本植物，花色优雅，花期通常在夏秋季节，适合花坛、庭院或盆栽种植。性喜阳光充足、排水良好的环境，耐寒性较强，养护简单，适合新手园艺爱好者。开花时花序繁密，色彩鲜艳，具有较高的观赏价值。</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -963,32 +978,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>藤本</t>
+          <t>多年生草本</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>葡萄</t>
+          <t>其他多年生草本</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>虹安果树</t>
+          <t>虹安宿根</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>葡萄</t>
+          <t>紫菀</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>红宝石</t>
+          <t>小卡罗</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>圆叶葡萄红宝石是一种多年生藤本果树品种，树势旺盛，果实呈圆形，成熟时果皮呈红宝石色，外观艳丽。适合家庭园艺种植，可用于庭院廊架、阳台藤架等场景观赏与采收。喜阳光充足的环境，耐热性较好，需搭架引蔓修剪管理。每年结果量大，果实酸甜可口，可鲜食或加工。栽植以春季为佳，保持通风透光，注意防治病虫害。</t>
+          <t>紫菀小卡罗是虹安宿根品牌下的多年生草本植物品种，花色优雅，适应性较强，花期通常在夏秋季节，适合家庭园艺种植观赏，也可用于花境搭配或庭院装饰。</t>
         </is>
       </c>
     </row>
@@ -1028,8 +1043,6 @@
           <t>花逸乐</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>花逸乐海藻有机颗粒肥是一款以天然海藻为主要原料的有机肥料，颗粒状设计便于均匀撒施。产品富含海藻中的天然有机质、氨基酸和微量元素，可改良土壤结构，增加土壤肥力。适用于家庭园艺中的花卉、蔬菜、果树等多种植物的基肥或追肥使用。4kg包装适合家庭阳台、庭院种植使用，安全环保，适合追求有机种植的用户。施肥时建议埋入土中或撒于土表后适当覆土，避免直接接触根系。</t>
@@ -1176,8 +1189,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>花彩师缓释肥料是一款通用型园艺肥料，氮磷钾配比为14-14-14的均衡配方，并添加TE微量元素，可为植物提供全面持久的营养供给。采用缓释技术，营养元素缓慢释放，一次施肥可长期供给养分，减少施肥频率，使用方便省心。适用于家庭园艺中各类花卉、蔬菜、果树等植物的追肥使用。20g小包装规格适合阳台园艺或小面积使用，便于控制用量。建议作为基肥或追肥使用，按照植物需求和生长阶段适量施用。</t>
@@ -1319,9 +1330,6 @@
           <t>基础工具</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>外螺纹内牙-30040G是一种园艺灌溉系统或管道连接配件，用于水管道的连接和转接。该产品采用外螺纹内牙设计，便于与其他管件进行连接，实现水流的有效输送和分配。适用于花园灌溉系统、自动浇水设备、滴灌系统等园艺设施的安装和改造。使用时需注意密封性，避免漏水。建议根据实际管道规格选择相应型号，确保连接牢固可靠。</t>
@@ -1416,8 +1424,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>花彩师是园艺肥料品牌，该商品为浓度1%的新型肥料产品，适用于家庭园艺植物的营养补充，可促进植物健康生长，提高抗病能力。具体使用方法和适用植物类型需参考产品说明。</t>
@@ -1720,8 +1726,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>花彩师园艺磷酸二氢钾是一种高浓度速效磷钾复合肥，纯度高达99%以上，可快速补充植物所需的磷和钾元素。磷元素促进根系发育和花芽分化，钾元素增强植株抗病抗逆性并提高果实品质。适用于叶面喷施或根部浇灌，使用时需按推荐比例稀释，避免浓度过高造成肥害。常用于花卉、果蔬的生长期和开花结果期，是园艺爱好者常用的优质水溶肥料。</t>
@@ -1868,8 +1872,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>帝罗马圆型托盘红陶是一款经典的园艺盆器配件，采用优质红陶材质制成，具有良好的透气性和排水性。圆型设计简洁大方，能够有效收集花盆底部多余的水分，防止水流四处散漫，保持地面整洁。红陶材质自然质朴，与各种植物搭配协调，提升整体美观度。适用于室内外各类盆栽的配套使用，是园艺爱好者不可或缺的实用配件。</t>
@@ -1887,14 +1889,46 @@
           <t>花叶小青柠 GZ</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>植物</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>种苗苗木</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>灌木</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>其他灌木</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>未提供</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>小青柠</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>花叶小青柠</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>花叶小青柠是芸香科柑橘属的观赏灌木品种，叶片带有美丽的花纹，小型常绿灌木，株型紧凑适合盆栽观赏。喜温暖湿润气候，喜阳光充足环境，耐阴性较好。适合阳台、窗台或室内明亮处养护。生长季需要保持盆土湿润，定期施用稀释的液体肥料。叶色美观，既可观叶又可赏型，是常见的室内观赏绿植。</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1919,32 +1953,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>藤本</t>
+          <t>灌木</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>葡萄</t>
+          <t>其他灌木</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>虹安果树</t>
+          <t>未提供</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>葡萄</t>
+          <t>小青柠</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>寒香蜜</t>
+          <t>未提供</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>懒人葡萄“寒香蜜”是一款适合新手栽培的葡萄品种，抗病性强、管理粗放。果实香甜多汁，皮薄肉脆，适合家庭阳台、庭院种植。春季开花，夏季结果，冬季落叶休眠。喜阳光充足、排水良好的环境，生长期需适当浇水施肥，修剪时注意保留结果枝。该品种为多年生藤本植物，搭架高度建议1.5-2米，种植后2-3年可进入盛果期。</t>
+          <t>花叶小青柠是一种观叶与观果兼具的小型灌木植物，叶片带有花纹，果实小巧可爱，适合阳台盆栽或庭院种植。喜阳光充足环境，耐半阴，土壤要求排水良好。生长期适量浇水，保持土壤微湿，冬季注意防寒。适合作为观赏植物或小型果树栽培。</t>
         </is>
       </c>
     </row>
@@ -1984,8 +2018,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>帝罗马圆型托盘摩卡11是一款高品质园艺盆器配件，采用帝罗马品牌经典设计，圆型结构搭配摩卡色调，简约大方。该托盘主要用于承接花盆底部流出的水分，防止浇水时弄湿地面或家具，同时可保持根系湿度，适用于各类室内外盆栽的配套使用。产品做工精细，边缘光滑，经久耐用，是提升盆栽整体美观度和实用性的理想选择。</t>
@@ -2028,8 +2060,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>花彩师园艺毛巾是一款专为园艺爱好者设计的实用周边产品，橙色配色清新明亮，方便在花园劳作、浇水、施肥或修剪后擦拭双手及清洁园艺工具。产品具有良好的吸水性和耐用性，便于清洗和重复使用，是园艺活动中不可或缺的辅助用品，为您的园艺体验带来更多便利与舒适。</t>
@@ -2124,8 +2154,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>花彩师植物通用介质是专为家庭园艺设计的通用型营养土，容量15L。采用优质泥炭、椰糠、珍珠岩等原料科学配比而成，具有良好的透气性、保水性和肥效。适用于室内外各类盆栽植物的种植与换盆，能为植物提供均衡的营养支持，促进根系健康生长，使用方便，直接即可使用。</t>
@@ -2324,8 +2352,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>花彩师三合一有机肥是一款以鸡粪、牛粪、羊粪为主要原料精制而成的有机肥料产品，氮磷钾含量均衡配比，富含有机质和有益微生物菌群。适用于各类花卉、蔬菜、果树及家庭园艺植物的基肥和追肥使用，能有效改良土壤结构，提升土壤肥力，增强植物抗病能力，促进植物健康生长。包装规格为900g，适合家庭园艺场景使用。</t>
@@ -2420,8 +2446,6 @@
           <t>Jay</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>200L椰糠颗粒2S是经过加工处理的园艺栽培介质，以椰子外壳为原料制成颗粒状。具有良好的透气性和保水性，结构稳定不易分解，可改善土壤结构。适用于多肉植物、盆栽花卉、蔬菜育苗等多种园艺场景，能为植物根系提供良好的生长环境。使用前建议清洗或浸泡以降低盐分含量。</t>
@@ -2620,8 +2644,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>花彩师园艺粘虫板是一款高效的害虫物理防治工具，采用粘虫板技术利用害虫的趋色性（如黄色、蓝色）诱捕蚜虫、白粉虱、斑潜蝇、蓟马等小型飞行昆虫。16片装设计适合家庭园艺、阳台种植、蔬菜大棚等多种场景使用。使用时将粘虫板悬挂于植物上方或周围，定期检查粘捕效果并及时更换。产品安全环保，无需使用化学农药，适合有机园艺和绿色种植，能有效减少害虫基数，保护植物健康生长。</t>
@@ -2721,7 +2743,6 @@
           <t>绣球</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>安镇大花绣球多株混苗是一款灌木类绣球种苗，植株形态为丛生状，茎干直立且木质化程度较高。绣球花大而丰满，花序呈球形或伞房状，花色丰富（常见蓝、紫、粉、白色），极具观赏价值。喜半阴环境，忌强光直射，喜湿润但怕积水，适宜疏松肥沃、排水良好的土壤。适合庭院种植、花境配置或盆栽观赏，混苗设计便于快速营造丰花效果。</t>
@@ -2816,8 +2837,6 @@
           <t>虹越</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>虹越定制短款防刺手套是专为园艺作业设计的防护用品，采用防刺材质制作，能有效防止玫瑰、月季等带刺植物刺伤手部。短款设计便于灵活操作，适合日常修剪、换盆、除草等园艺工作。掌心防滑处理，抓握工具更稳固。透气舒适，长时间佩戴不闷热，是园艺爱好者必备的基础防护工具。</t>
@@ -2860,8 +2879,6 @@
           <t>虹越</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>虹越定制直头气压喷壶，容量1.5L，采用气压式设计，喷洒均匀省力。复古蓝色外观，时尚美观。适用于家庭园艺、花卉植物浇水养护，也可用于喷施叶面肥、农药等。直头设计出水集中，适合定点浇灌，操作简便，是家庭养花的好帮手。</t>
@@ -2904,8 +2921,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>花彩师球根植物专用介质是专门为球根花卉配制的营养土，容量为3.5L。该介质具有良好的排水性和透气性，富含球根植物生长所需的营养元素，能有效促进球根花卉的根系发育和开花。适用于郁金香、朱顶红、百合、风信子等球根类植物的种植和养护。</t>
@@ -2948,8 +2963,6 @@
           <t>花逸乐</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>花逸乐海藻有机颗粒肥是一款以天然海藻为主要原料的有机肥料产品，颗粒状设计便于均匀撒施。富含有机质、氮磷钾及微量元素，可改善土壤结构，增加土壤肥力，促进植物根系发育。适用于家庭园艺中各类花卉、蔬菜、果树的基肥或追肥使用，安全温和，不易造成肥害。2.5kg包装适合阳台、庭院小规模种植使用。使用时建议均匀撒施后浅翻入土，并保持适度水分。</t>
@@ -2992,8 +3005,6 @@
           <t>奥石克莱尔</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>奥石克莱尔圆型两用种植盆，采用优质环保材质制作，造型圆润美观，适用于室内外园艺种植。黑色设计简约大气，耐晒耐候，可用于栽种花卉、蔬菜、多肉等多种植物。盆底设有排水孔设计，防止积水烂根，保证植物健康生长。17cm尺寸适中，适合中小型植物种植需求。</t>
@@ -3036,8 +3047,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>花彩师浓缩营养液天南星科型是专为天南星科植物（如绿萝、龟背竹、红掌、白掌、蔓绿绒等）研发的液态肥料。产品采用科学配比，富含氮磷钾及微量元素，pH值适宜天南星科植物吸收。浓缩型设计方便稀释使用，适用于日常浇灌和叶面喷施。能有效促进叶片翠绿有光泽，增强植株抗病能力，适合家庭养护天南星科观叶植物使用。使用时按说明书比例稀释，避免浓度过高造成肥害。</t>
@@ -3132,8 +3141,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>帝罗马经典宽边高圆型盆白陶22是一款高品质陶土花盆，采用经典设计，宽边造型增添优雅感，白陶材质具有良好的透气性和排水性，有助于植物根系健康生长。圆型设计适合种植各类草本花卉、灌木等植物，22厘米尺寸适合中小型植物种植。陶土盆体厚重稳固，耐磨损耐候性好，适合室内外园艺使用，是追求品质与美观兼具的理想花盆选择。</t>
@@ -3540,8 +3547,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>花彩师家庭园艺植物精油防护剂是一种环保型的植物保护产品，采用天然植物精油配方精制而成。主要用于家庭园艺中花卉、蔬菜、果树等植物的病虫害防护，能够有效驱避常见害虫并预防真菌性疾病。产品以植物精油为有效成分，温和不刺激，适合家庭环境使用，对人体和宠物相对安全。该防护剂为补充装设计，便于用户灌装到喷雾器中使用，适用于各类室内外植物的日常护理。</t>
@@ -3584,8 +3589,6 @@
           <t>奥石克莱尔</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>奥石克莱尔圆型两用种植盆，尺寸17英寸，叶绿色设计。圆形花盆采用两用设计，适合室内外园艺栽培。可用于种植各种花卉、蔬菜及小型灌木。采用优质塑料材质，耐候性强，不易褪色。底部设有排水孔，防止积水烂根。叶绿色清新自然，适合家居园艺装饰或苗圃育苗使用。</t>
@@ -4091,7 +4094,6 @@
           <t>其他灌木</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
           <t>锦带</t>
@@ -4144,8 +4146,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>花彩师花卉通用介质（粗颗粒）28L是一款专为花卉栽培设计的优质栽培介质。该产品采用粗颗粒配方，具有良好的透气性和排水性，能够为花卉根系提供充足的氧气，减少积水导致的烂根问题。适用于各类室内外观赏花卉的盆栽换土、播种育苗或地栽改良。粗颗粒结构有助于土壤疏松，促进根系健康生长，是家庭园艺和商业花卉生产的理想选择。</t>
@@ -4188,8 +4188,6 @@
           <t>虹越</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>虹越定制园艺通用手套，墨绿色设计，防水耐磨，适合各种园艺操作。手套采用亲肤材质，透气舒适，能有效保护手部免受土壤、刺枝和肥料的伤害。通用尺寸设计，适合大多数人手使用，是花园种植、修剪、移植等日常园艺活动的理想防护工具。</t>
@@ -4232,8 +4230,6 @@
           <t>雷欧</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
           <t>雷欧6分快速接口是一种园艺灌溉系统的管道连接配件，采用快速插拔设计，方便水管的快速连接和拆卸。6分规格适用于常见园艺水管尺寸，不含内牙设计使其可与带内牙的阀门或管道直接连接。该产品主要用于花园灌溉、浇水管路搭建等场景，能够提高园艺浇水作业的便捷性和效率。材质坚固耐用，密封性好，连接牢固不易漏水。</t>
@@ -4432,8 +4428,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
           <t>花彩师骨粉颗粒是一种高钙高磷有机肥料，采用优质动物骨源经高温处理制成，颗粒状形态便于均匀撒施。富含植物所需的磷、钙元素，可促进根系发育、增强抗病能力、提高开花结果率。适用于各类花卉、蔬菜、果树及球根植物做底肥或追肥使用，肥效温和持久，不伤根系，是家庭园艺常用的有机肥产品。</t>
@@ -4471,7 +4465,6 @@
           <t>绣球</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
           <t>绣球</t>
@@ -4524,8 +4517,6 @@
           <t>成都神龙</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
           <t>成都神龙月季小盆扦插基质，容量60L，专为月季等花卉扦插繁殖设计的专用介质。具有良好的透气性和保水性，能有效促进插穗生根，提高扦插成活率。配方科学合理，适合家庭园艺爱好者进行月季小盆扦插繁殖使用，也可用于其他木本和草本花卉的扦插育苗。</t>
@@ -4615,7 +4606,6 @@
           <t>冬青</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
           <t>冬青</t>
@@ -4668,8 +4658,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
           <t>花彩师绣球调蓝剂是一种专门用于调节绣球花色的园艺试剂，通过调节土壤酸碱度，使绣球花呈现蓝色或蓝紫色。绣球花色受土壤pH值影响，酸性土壤（pH值5.0-5.5）开蓝色花，碱性土壤开粉色花。本品为三联包设计，携带使用方便，45g规格适合家庭园艺使用。使用时需根据土壤现状和目标花色按说明施用，通常配合浇水一同进行。建议在绣球萌芽期或花苞形成前使用效果更佳。</t>
@@ -4759,7 +4747,6 @@
           <t>绣球</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
           <t>绣球</t>
@@ -4812,8 +4799,6 @@
           <t>马雅</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
           <t>马雅Maya90浓缩营养液是一种高浓度植物营养补充剂，容量为10ml/支，适用于各类室内外植物的日常养护。该产品为通用型配方，可为植物提供均衡的氮磷钾及微量元素，促进植株健康生长、叶色浓绿、花果丰满。使用时需按比例稀释后浇灌或叶面喷施，适合家庭园艺、蔬菜种植、花卉栽培等多种场景。使用前请摇匀，遵循薄肥勤施的原则，避免浓度过高造成肥害。阴雨天或高温时段建议减少使用频率。</t>
@@ -4908,8 +4893,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
           <t>花彩师蓝绣球专用型介质是一款专为绣球植物研发的盆栽土壤基质，容量为8升。产品针对蓝绣球喜酸喜湿润的生长特性调配，酸碱度适中，富含绣球生长所需的有机质和微量元素，透气性和保水性良好。使用时可直接作为种植介质，也可与园土混合使用，能有效促进绣球根系发育和花朵着色。建议每1-2年更换一次介质，保持土壤肥力。</t>
@@ -5051,7 +5034,6 @@
           <t>冬青</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
           <t>冬青</t>
@@ -5312,8 +5294,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
           <t>花彩师珠穆朗玛壶是一款园艺浇水工具，容量为700ml，设计灵感来源于珠穆朗玛峰的雄伟形态。产品采用优质塑料材质，轻巧耐用，适合家庭园艺日常浇灌使用。该浇水壶设计合理，出水均匀，可有效避免水流过大冲刷土壤或损伤幼苗，适用于各类盆栽、花卉、蔬菜的浇水需求。</t>
@@ -5507,7 +5487,6 @@
           <t>绣球</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
           <t>绣球</t>
@@ -5659,13 +5638,11 @@
           <t>其他灌木</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
           <t>厚皮香</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
           <t>厚皮香是山茶科厚皮香属的常绿灌木或小乔木，原产于中国、日本等地。株高1-3米，叶片浓绿有光泽，倒卵形或椭圆形，革质。花期6-7月，花白色或淡黄色，清香宜人。果实球形，成熟时呈红色，具有较高的观赏价值。性强健，耐阴耐寒，适应性强，适合庭园绿化、盆栽或做绿篱使用。喜温暖湿润气候，疏松排水良好的微酸性土壤。繁殖以播种或扦插为主。</t>
@@ -5755,7 +5732,6 @@
           <t>冬青</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
           <t>冬青</t>
@@ -5808,8 +5784,6 @@
           <t>虹越定制</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
           <t>这是一款由虹越定制的气压式喷壶，容量为1.5L，采用直头设计，柠檬绿配色清新美观。气压喷壶通过手动打气产生压力，使水流呈雾状喷出，适合给植物叶面浇水、喷洒叶面肥或农药，也能用于调节空气湿度。采用优质塑料材质，轻便耐用，操作简单，是家庭园艺日常浇水和植物养护的实用工具。</t>
@@ -5852,8 +5826,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
           <t>花彩师草莓专用介质是专为草莓种植研发的优质培养土，容量3.5L。该介质针对草莓生长需求特别调配，酸碱度适宜，富含草莓所需的营养元素，透气性和保水性良好。能有效促进草莓根系发育，提高成活率，为草莓开花结果提供良好基础环境。适用于阳台盆栽、庭院地栽等多种草莓种植场景。使用时根据植株大小适量添加，保持介质湿润但避免积水。</t>
@@ -5896,8 +5868,6 @@
           <t>维特</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
           <t>维特0-10泥炭是一种优质园艺介质，粒径规格为0-10mm，容量250升。泥炭是园艺中常用的栽培基质，具有良好的保水保肥能力、透气性和结构性，适用于播种、育苗、成株栽培等多种用途。可单独使用或与其他介质混合调配，适合种植花卉、蔬菜、果树等各类植物。使用前建议根据植物需求添加珍珠岩、椰糠等材料进行改良。</t>
@@ -5940,8 +5910,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
           <t>花彩师家庭园艺植物浓缩精油防护剂是一款专为家庭园艺设计的植物保护产品，容量为50ml，浓缩配方便于稀释使用。该产品采用天然植物精油成分，可用于防治园艺植物常见的病虫害问题，适用于各类室内外观赏植物、果蔬等的日常防护。使用时需按照说明比例稀释后均匀喷施于植物叶面及茎秆，起到驱虫、杀菌的作用。产品小巧便携，适合家庭日常园艺养护使用。</t>
@@ -5989,7 +5957,6 @@
           <t>中国樱桃</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
           <t>中国樱桃是我国的传统果树品种，果实小巧圆润，色泽红艳，口感酸甜多汁。该品种适应性强，耐寒耐旱，适合我国大部分地区种植。春季开花，夏季结果，既可观花又可采果，适合家庭庭院或阳台盆栽种植。喜阳光充足的环境，需保持土壤湿润排水良好。</t>
@@ -6032,8 +5999,6 @@
           <t>维特</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
           <t>维特育苗1号泥炭，容量250L，是专为育苗阶段设计的优质泥炭介质。具有良好的透气性和保水性，结构松散有利于幼苗根系发育。pH值适宜，酸碱度适中，富含腐殖质和营养成分。可直接用于播种、扦插、种苗培育等场景，是家庭园艺和专业化育苗的理想选择。建议使用时根据植物种类适量搭配珍珠岩或蛭石以增强排水性。</t>
@@ -6076,8 +6041,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
           <t>帝罗马（Terracotta）是一款源自意大利的经典陶土盆品牌，以其优质的红陶材质和精湛的工艺著称。产品具有良好的透气性和排水性，非常适合园艺种植使用。陶盆表面天然质朴，能够自然调节盆土温湿度，为植物根系提供健康的生长环境。帝罗马花盆造型经典耐用，适合种植各类花卉、蔬菜及小型灌木，是园艺爱好者喜爱的经典盆器品牌。</t>
@@ -6120,8 +6083,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
           <t>花彩师家庭园艺植物精油防护剂，容量480ml，是一种以天然植物精油为主要成分的园艺保护产品。该产品主要用于家庭园艺中花卉、蔬菜、果树等植物的病虫害防护，采用植物源成分，温和不刺激，适合家庭室内外园艺使用。使用时直接喷洒于植物叶面及茎部，可有效驱避常见害虫如蚜虫、红蜘蛛等，同时具有一定的杀菌作用。产品环保安全，适合有儿童和宠物的家庭使用，建议在清晨或傍晚喷施效果更佳。</t>
@@ -6164,8 +6125,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr">
         <is>
           <t>麦饭石是一种天然硅酸盐矿物颗粒，粒径3-5mm，重量900g。具有良好的透气透水性和离子交换能力，可调节土壤酸碱度，增加土壤蓬松度。常用于多肉植物、兰花、盆栽花卉等需要良好排水性的植物栽培基质中，也可铺面使用防止杂草生长和水分蒸发。建议与营养土等介质混合使用，比例约为10%-30%。</t>
@@ -6265,7 +6224,6 @@
           <t>草莓</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
           <t>覆盆子（草莓）为多年生灌木植物，株型紧凑，适合家庭园艺种植。果实小巧可爱，呈心形或圆锥形，颜色鲜红，口感酸甜可口。喜阳光充足的环境，适应性较强，适合庭院、阳台盆栽种植，需保证充足的水分和养分供应，每年春季开花，夏季结果，观赏与食用价值兼具。</t>
@@ -6308,8 +6266,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr">
         <is>
           <t>花彩师月季专用介质是专为月季植物研发的种植基质，容量28L。该介质采用科学配比，疏松透气、排水良好，富含月季生长所需的营养元素，pH值适宜。适用于盆栽和地栽月季的种植、换盆及补充基质使用，能有效促进月季根系发育和开花生长，是月季爱好者的理想种植伴侣。</t>
@@ -6352,8 +6308,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
           <t>园艺腐植酸是一种天然有机土壤改良剂，富含腐殖质成分，能够有效改善土壤结构，增加土壤透气性和保水性，促进土壤微生物活动。该产品可调节土壤酸碱度，提高肥料利用率，增强植物根系发育和抗逆性。适用于各类花卉、蔬菜、果树及园艺植物的土壤改良，使用时按比例均匀混入土壤或作为基肥施用，安全环保，适合家庭园艺和农业生产使用。</t>
@@ -6448,8 +6402,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
           <t>鹿沼土是一种产自日本鹿沼市的火山灰质栽培介质，呈酸性，颗粒状，具有优异的排水性和透气性。广泛应用于多肉植物、仙人掌、兰花、食虫植物等怕积水植物的栽培。可单独使用或与泥炭土、珍珠岩等混合配比使用，能有效防止根系腐烂，促进植物健康生长。1.6L装适合家庭园艺小规模栽培使用。</t>
@@ -6700,8 +6652,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr">
         <is>
           <t>帝罗马国际盆摩卡系列是一款高品质园艺花盆，摩卡色系温暖自然，适合室内外各种植物栽种。采用优质材料制成，具有良好的透气性和排水性，有助于植物根系健康生长。盆器设计简约大方，质感细腻，是家庭园艺和商业景观的理想选择。尺寸为17规格，适合中小型植物栽培。</t>
@@ -6853,7 +6803,6 @@
           <t>龙胆</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
           <t>龙胆是龙胆科龙胆属多年生草本植物，株高30-60厘米，茎直立，叶对生呈卵形。花朵呈漏斗状，颜色丰富，有蓝、紫、白等色，花期夏秋季。龙胆喜欢阳光充足、排水良好的环境，耐寒性较强。适合种植于花境、岩石园或作切花使用。其根可入药，具有清热燥湿、泻肝胆火的功效。作为观赏花卉，龙胆的花形优美、色彩艳丽，是庭园中重要的草本花卉之一。</t>
@@ -7052,8 +7001,6 @@
           <t>成都神龙</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr"/>
-      <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
           <t>打磨型松鳞是一种高品质园艺覆盖材料，选用优质松树皮经过打磨处理，颗粒均匀（1.5-2.5cm规格）。具有良好的透气性、保水性和保温性能，适用于庭院地被、花坛覆盖、盆栽表面铺面等。能有效抑制杂草生长、保持土壤湿度、调节土温，同时其自然纹理美观大方，是园林景观和园艺栽培的理想选择。</t>
@@ -7408,8 +7355,6 @@
           <t>奥石克莱尔</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr"/>
-      <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
           <t>奥石克莱尔圆型两用种植盆17灰色是一款高品质园艺盆器，采用优质塑料材质，耐用抗老化。圆型设计适合多种植物种植，两用功能既可用于播种育苗，也可用于成株栽培。灰色配色简约大方，适合各种园艺风格。口径17寸规格，容量适中，适合家庭园艺使用。建议配合排水层和疏松透气介质使用，定期检查排水孔保持畅通。</t>
@@ -7504,8 +7449,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr"/>
-      <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
           <t>花彩师庭院土壤改良介质是一种专为庭院植物设计的土壤改良产品，容量50L。该介质能够有效改善土壤结构，增加土壤透气性和排水性，调节土壤酸碱度，为植物根系提供良好的生长环境。适用于各类庭院花卉、蔬菜、果树等植物的土壤改良，可与原土混合使用或直接铺设使用。使用时建议根据植物类型和原土状况，按比例掺入以达到最佳改良效果。</t>
@@ -7543,7 +7486,6 @@
           <t>绣球</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr">
         <is>
           <t>绣球</t>
@@ -7596,8 +7538,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr"/>
-      <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr">
         <is>
           <t>帝罗马国际盆摩卡系列，采用优质陶瓷材质，摩卡棕色设计典雅大方，适合室内外各种花卉绿植栽培使用。13寸规格适合种植中型植物，排水孔设计合理，透气性好，便于植物根系生长。品牌源自意大利，设计风格简约时尚，是园艺爱好者喜爱的盆器品牌之一。</t>
@@ -7640,8 +7580,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr"/>
-      <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
           <t>花彩师细颗粒盆栽通用介质，容量28L，适用于各类盆栽植物的种植栽培。该介质具有良好的透气性、排水性和保水性，细颗粒配方更适合盆栽环境，可为植物根系提供充足的养分和良好的生长环境，适合用于室内绿植、花卉、蔬菜等多种盆栽植物的种植。</t>
@@ -7679,9 +7617,6 @@
           <t>兰卡椰壳</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr"/>
-      <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
           <t>来自东南亚地区的优质椰壳介质，经过特殊处理工艺，无需提前浸泡即可直接使用。具有良好的透气性和排水性，能有效改善土壤结构，防止土壤板结。100L大容量包装适合大面积盆栽、花坛或花园土壤改良使用，可为植物根系提供疏松透气的生长环境，适合多肉、兰花及各类花卉盆栽使用。</t>
@@ -7771,9 +7706,6 @@
           <t>其他改良材料</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr"/>
-      <c r="H153" t="inlineStr"/>
-      <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
           <t>松鳞树皮是优质的园艺覆盖材料，采用松树皮经过腐熟加工而成。具有良好的透气性、保温性和保湿性，可有效防止土壤水分过快蒸发，调节土壤温度，抑制杂草生长。适用于盆栽植物表面覆盖、花坛地被、花园路径铺设等场景。使用时可铺设在土壤表面3-5厘米厚度，既能美化园艺景观，又能改善土壤结构，促进植物健康生长。袋装6#为标准包装规格，方便储存与使用。</t>
@@ -7816,8 +7748,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr"/>
-      <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr">
         <is>
           <t>花彩师植物通用活力液是一款广谱性植物营养液，规格为35ml/支，共10支装。本品富含多种微量元素和植物生长因子，可快速补充植物所需营养，促进根系发育，增强植株抗病抗逆能力。适用于各类室内外观赏植物、蔬菜、果树等的日常养护。使用时按比例稀释后浇灌或叶面喷施，建议每隔7-14天使用一次效果更佳。产品为浓缩液体状，便于稀释保存，是家庭园艺必备的多功能植物营养补给品。</t>
@@ -8063,9 +7993,6 @@
           <t>其他改良材料</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr"/>
-      <c r="H159" t="inlineStr"/>
-      <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr">
         <is>
           <t>松鳞树皮是一种优质的园艺覆盖材料，选用天然松树皮经过腐熟加工而成。具有良好的透气性、保水性和排水性，能够有效改善土壤结构，增加土壤有机质含量。适用于花园地表覆盖、花盆表面铺装、盆栽介质改良等用途。可调节土壤温度，防止杂草生长，减少水分蒸发，为植物根系创造良好的生长环境。袋装设计便于储存和使用，5#规格适合家庭园艺使用。</t>
@@ -8108,8 +8035,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr"/>
-      <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr">
         <is>
           <t>花彩师球根植物专用介质是专为球根类花卉研发的优质种植基质，容量15L。该介质针对球根植物根系特点优化配比，透气性和排水性俱佳，能有效防止球根积水腐烂。富含有机质和微量元素，为郁金香、朱顶红、百合、风信子等球根花卉提供适宜的生长环境。质地疏松轻便，便于球根扎根与膨大，是球根植物盆栽和地栽的理想选择。</t>
@@ -8303,13 +8228,11 @@
           <t>其他灌木</t>
         </is>
       </c>
-      <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr">
         <is>
           <t>南天竹</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr">
         <is>
           <t>南天竹是常绿灌木，原产于中国长江流域及华南地区。株高1-3米，茎干直立，羽状复叶互生，革质有光泽。夏季开白色圆锥花序，秋冬季节结红色球形浆果，经冬不落，观赏价值高。性强健，耐寒耐热，喜半阴环境，适应性强。对土壤要求不严，适合庭院孤植或丛植，也可作为绿篱材料。其红色果实和秋季红叶是重要的观赏点。</t>
@@ -8404,8 +8327,6 @@
           <t>虹越</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr"/>
-      <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr">
         <is>
           <t>虹越定制360度旋转喷头气压喷壶，容量1.5L，采用复古蓝配色设计。配备气压喷头，可实现360度旋转喷洒，覆盖范围广，雾化效果均匀细腻。适合浇灌花卉、绿植、蔬菜等，适用于室内外园艺场景。气压式设计操作省力，喷洒细腻不伤植物叶面，是家庭园艺养护的实用工具。</t>
@@ -8448,8 +8369,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr"/>
-      <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr">
         <is>
           <t>花彩师赤玉土是一种高品质园艺介质，由火山灰沉积而成，呈弱酸性，透气性和排水性优异。颗粒结构稳定，不易分解，适合多肉植物、兰花、盆景等对土壤透气性要求较高的植物使用。赤玉土可单独使用或与其他介质混合，能有效改善土壤结构，防止积水烂根，是盆栽植物的理想基质材料。1.6L装适合家庭园艺使用。</t>
@@ -8648,8 +8567,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr"/>
-      <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr">
         <is>
           <t>花彩师换花盆垫是一款实用的园艺配件产品，采用绿色环保材质制作，尺寸为1米*1米。该产品主要用于花盆底部，能够有效防止水分渗漏，保护地面清洁，同时具有良好的透气性和排水性。在换盆操作时作为垫层使用，方便快捷，避免泥土弄脏环境。适用于各类盆栽植物的换盆护理，是园艺爱好者必备的工具配件。</t>
@@ -8692,8 +8609,6 @@
           <t>马雅Maya</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr"/>
-      <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr">
         <is>
           <t>马雅Maya93.1多肉植物专用营养液，容量10ml，适合多肉、仙人掌、景天科等肉质植物使用。能促进多肉植物健康生长，增强抗病能力，使用便捷，直接稀释后浇灌即可。注意按照说明比例使用，避免过量造成肥害。</t>
@@ -8736,8 +8651,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr"/>
-      <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr">
         <is>
           <t>花彩师有机肥料（鸡粪肥）是一款以天然鸡粪为原料发酵而成的有机肥料，肥效温和持久，富含氮磷钾及多种微量元素。有机质含量高，能有效改良土壤结构，增加土壤蓬松度和透气性，促进根系发育。适用于各类花卉、蔬菜、果树及家庭园艺植物的基肥和追肥使用。2.8KG包装设计合理，便于储存和施用。使用时建议深施入土或穴施，避免直接接触根系，配合浇水效果更佳。</t>
@@ -8775,9 +8688,6 @@
           <t>其他浇水工具</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr"/>
-      <c r="H174" t="inlineStr"/>
-      <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr">
         <is>
           <t>内螺纹内牙连接件（型号30039G）是一种管道连接配件，通常用于园艺灌溉系统或水管管道的连接。该产品具有内螺纹设计，可与其他外螺纹管道或阀门进行连接，实现水流通道的搭建与延伸。材质多为铜、不锈钢或塑料，具有耐腐蚀、密封性好等特点。适用于家庭园艺灌溉、工程绿化浇水系统等场景的管道布设与维修。</t>
@@ -8820,8 +8730,6 @@
           <t>成都神龙</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr"/>
-      <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr">
         <is>
           <t>成都神龙育苗基质60L，是专为植物育苗研发的优质栽培介质。精选泥炭、椰糠、珍珠岩等原料科学配比，具有透气性好、保水性强、无菌无虫卵等特点。适用于播种育苗、扦插繁殖、组培苗过渡等场景，可为幼苗提供充足的养分和适宜的生长环境。使用时可直接装盆或与园土混合使用，适合花卉、蔬菜、林木等多种植物的育苗管理。</t>
@@ -8916,8 +8824,6 @@
           <t>君沐</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr"/>
-      <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr">
         <is>
           <t>君沐1000目喷头是一款园艺浇水工具配件，采用1000目精细过滤设计，橙色外观。该喷头适用于浇水壶等浇水设备，能够产生细腻均匀的水雾或水流，适合花卉、蔬菜等植物的灌溉需求。9%可能指水雾覆盖率或喷射角度等参数。使用时可根据植物种类和生长阶段调节水雾细密度，避免对娇嫩植物造成损伤。</t>
@@ -9012,8 +8918,6 @@
           <t>马雅</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr"/>
-      <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr">
         <is>
           <t>马雅Maya92.3种球植物专用营养液，容量10ml单支装，专为种球植物设计的液态肥料。可用于郁金香、朱顶红、百合、风信子等球根类花卉，提供种球生长所需的营养元素，促进种球发育和开花。使用时按比例稀释后浇灌，适合种球植物的各个生长阶段。注意避光保存，开封后尽快使用。</t>
@@ -9160,8 +9064,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr"/>
-      <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr">
         <is>
           <t>花彩师蓝莓专用介质是专为蓝莓等酸性植物配制的种植介质，容量12L。产品针对蓝莓根系生长特性设计，酸碱度适宜富含有机质，疏松透气保水保肥，能够满足蓝莓对酸性土壤环境的需求，促进根系发育和植株健壮生长。适用于蓝莓盆栽、地栽换土使用，是种植蓝莓的理想基质选择。</t>
@@ -9256,8 +9158,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr"/>
-      <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr">
         <is>
           <t>帝罗马带边高圆型盆摩卡25是一款高品质陶土花盆，产自意大利知名品牌帝罗马（Deroma）。该花盆采用优质陶土高温烧制而成，具有良好的透气性和排水性，有助于植物根系健康生长。独特的带边设计不仅美观大方，还能防止浇水时水流出。摩卡色低调优雅，25厘米的直径适合种植各类中小型花卉、蔬菜或室内绿植，是阳台、花园、露台及室内装饰的理想选择。盆体质地坚固耐用，适合长期使用。</t>
@@ -9295,9 +9195,6 @@
           <t>其他浇水工具</t>
         </is>
       </c>
-      <c r="G185" t="inlineStr"/>
-      <c r="H185" t="inlineStr"/>
-      <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr">
         <is>
           <t>浇水把手开关是一种园艺浇水工具的配件，采用美标螺纹设计，黑色外观。该配件主要用于连接水管与浇水设备，控制水流的开关。安装便捷，密封性好，适用于各种灌溉系统。材质坚固耐用，抗腐蚀，适合户外长期使用。是园艺灌溉系统中不可或缺的控制部件。</t>
@@ -9340,8 +9237,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr"/>
-      <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr">
         <is>
           <t>帝罗马圆型托盘摩卡系列，采用优质环保材质制成，圆形设计配合摩卡色系，简约时尚。该托盘用于承接花盆底部排出的多余水分，防止地面弄脏或潮湿，适合室内外花盆配套使用。尺寸17指托盘直径约17厘米，轻巧耐用，易于清洁，是家庭园艺和商业花卉摆设的理想配件选择。</t>
@@ -9384,8 +9279,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr"/>
-      <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr">
         <is>
           <t>花彩师植物高浓缩营养液（花卉型）是一款专为花卉植物设计的液态肥料，容量250ml/瓶。采用高浓缩配方，营养配比均衡，富含氮磷钾及微量元素，能快速补充花卉生长所需的营养元素。适用于各类室内外观赏花卉，可促进花卉枝叶繁茂、花朵艳丽、花期延长。使用时按比例稀释后浇灌或叶面喷施，操作简便，是家庭园艺花卉养护的理想选择。</t>
@@ -9433,7 +9326,6 @@
           <t>无花果</t>
         </is>
       </c>
-      <c r="I188" t="inlineStr"/>
       <c r="J188" t="inlineStr">
         <is>
           <t>无花果是落叶灌木或小乔木，属桑科无花果属，原产于地中海沿岸，喜温暖湿润气候，耐寒性较强。无花果果实营养丰富，含有多种维生素和矿物质，可鲜食或加工制干。植株生长较快，栽培管理相对简单，适合家庭庭院或果园种植。虹安果树品牌的无花果苗经过精心培育，适应性广，移栽成活率高，购入后注意保持土壤湿润，适当遮阴缓苗后正常养护。</t>
@@ -9533,7 +9425,6 @@
           <t>铁线莲</t>
         </is>
       </c>
-      <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr">
         <is>
           <t>铁线莲是毛茛科铁线莲属的多年生藤本植物，以花大色艳、花期长著称，有“藤本皇后”之美誉。虹安铁线莲精品盆栽精选优质种苗，植株健壮、根系发达，适合阳台、庭院藤架、篱笆装饰。喜阳光充足、通风良好的环境，耐寒性较强，冬季休眠。土壤宜疏松肥沃、排水良好。生长期需适度浇水，避免积水。春季萌芽后适当追肥，花后及时修剪残花，可促进再次开花。盆栽需设立支架供其攀援缠绕。</t>
@@ -9737,7 +9628,6 @@
           <t>铁线莲</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr">
         <is>
           <t>铁线莲是毛茛科铁线莲属的藤本植物，被誉为"藤本皇后"。大道-科琳属于大道系列矮生型铁线莲，株型紧凑，适合盆栽或小型花架。喜阳光充足但忌暴晒，土壤需疏松透气、排水良好。耐寒性较强，花期通常在春季至秋季，修剪方式为三类修剪（重剪）。浇水遵循见干见湿原则，生长期适当施肥促进开花。</t>
@@ -9780,8 +9670,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr"/>
-      <c r="I195" t="inlineStr"/>
       <c r="J195" t="inlineStr">
         <is>
           <t>帝罗马圆型托盘白陶，采用优质陶瓷材质，白色釉面清新雅致，圆形设计便于承接花盆沥水，有效防止浇水时水流外溢，保持地面整洁。适合搭配帝罗马品牌圆形花盆使用，是室内外绿植养护的实用配件，具有良好的耐用性和装饰性。</t>
@@ -9871,7 +9759,6 @@
           <t>其他乔木</t>
         </is>
       </c>
-      <c r="G197" t="inlineStr"/>
       <c r="H197" t="inlineStr">
         <is>
           <t>柏</t>
@@ -9919,13 +9806,11 @@
           <t>其他灌木</t>
         </is>
       </c>
-      <c r="G198" t="inlineStr"/>
       <c r="H198" t="inlineStr">
         <is>
           <t>厚皮香</t>
         </is>
       </c>
-      <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr">
         <is>
           <t>厚皮香（Ternstroemia gymnanthera）是山茶科厚皮香属常绿灌木或小乔木，原产中国南方各省。叶革质光亮，浓绿四季常青，株型紧凑美观。花小而清香，果实球形红色，具有较高观赏价值。耐阴耐寒，适应性强，对土壤要求不高。适合庭院、园林孤植或群植配置，也可修剪为绿篱使用，是优良的园林绿化树种。栽培时注意保持土壤湿润，夏季避免暴晒。</t>
@@ -9968,8 +9853,6 @@
           <t>虹越定制</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr"/>
-      <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr">
         <is>
           <t>虹越定制长筒护臂园艺手套，采用优质面料制作，设计有加长护臂部分，可有效保护手臂免受植物刺伤、土壤污渍及园艺作业中的轻微伤害。蓝色碎花图案清新雅致，兼具实用性与美观性。适用于花卉种植、蔬菜栽培、花园整理等各类园艺活动，是园艺爱好者必备的基础防护工具。</t>
@@ -10012,8 +9895,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr"/>
-      <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr">
         <is>
           <t>花彩师园艺不锈钢盆栽勺是一款专业园艺种植工具，采用优质不锈钢材质，防锈耐腐蚀，经久耐用。勺形设计适合盆栽种植、换盆、疏松土壤、挖掘小坑等操作。人体工学手柄，握持舒适，使用省力。适用于家庭园艺、花卉盆栽、蔬菜种植等场景，是花卉爱好者的必备工具之一。</t>
@@ -10212,8 +10093,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr"/>
-      <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr">
         <is>
           <t>花彩师高磷缓释营养颗粒是一款专为促进植物开花结果设计的园艺肥料。产品采用缓释技术，可持续为植物提供均衡营养，高磷配方有效促进花芽分化，增强开花质量。颗粒状设计便于均匀撒施，适用于各类花卉、蔬菜及果树的基肥和追肥使用。使用时可根据植物需求适量施用，避免过量，保持土壤湿润以提高肥效。</t>
@@ -10308,8 +10187,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr"/>
-      <c r="I206" t="inlineStr"/>
       <c r="J206" t="inlineStr">
         <is>
           <t>花彩师复合肥料，氮磷钾配比为10-10-10-1，属于均衡型复合肥，适用于各类园艺植物。可作为基肥或追肥使用，适合花卉、蔬菜、果树等多种植物生长需求。使用时可根据植物种类和生长阶段调整用量，建议深施或溶解后浇灌，避免直接接触根系。肥效持久，使用方便，是家庭园艺和专业种植的理想选择。</t>
@@ -10352,8 +10229,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr"/>
-      <c r="I207" t="inlineStr"/>
       <c r="J207" t="inlineStr">
         <is>
           <t>花彩师园艺冰袖是专为园艺工作者设计的防晒护具，采用冰丝材质制成，触感冰凉舒适。能有效阻挡紫外线，防止手臂在长时间户外园艺活动中被晒伤。黑色款式经典实用，适合各种园艺场景使用，是夏季园艺操作的必备防护用品。</t>
@@ -10396,8 +10271,6 @@
           <t>马雅</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr"/>
-      <c r="I208" t="inlineStr"/>
       <c r="J208" t="inlineStr">
         <is>
           <t>马雅Maya92.1玫瑰月季专用液肥是一款针对月季（玫瑰）植物开发的专用水溶性肥料，规格为30ml。该产品根据月季的生长需求特点配制，含有氮磷钾及微量元素，能促进月季生长发育、开花鲜艳。建议使用时按比例稀释后浇灌或叶面喷施，适合家庭园艺月季养护使用。注意避光保存，放在儿童接触不到的地方。</t>
@@ -10492,8 +10365,6 @@
           <t>吉普</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr"/>
-      <c r="I210" t="inlineStr"/>
       <c r="J210" t="inlineStr">
         <is>
           <t>FJGD吉普XQZ是一款园艺浇水工具类产品，具体类型和规格未提供。该产品可能为滴水器、浇水壶或其他浇水辅助设备，适用于家庭园艺灌溉需求。建议根据具体规格选择合适的园艺浇水工具，确保植物水分管理得当。</t>
@@ -10531,13 +10402,11 @@
           <t>其他灌木</t>
         </is>
       </c>
-      <c r="G211" t="inlineStr"/>
       <c r="H211" t="inlineStr">
         <is>
           <t>厚皮香</t>
         </is>
       </c>
-      <c r="I211" t="inlineStr"/>
       <c r="J211" t="inlineStr">
         <is>
           <t>厚皮香是山茶科厚皮香属常绿灌木或小乔木，原产于中国、日本等地。株高可达3-8米，树冠圆润，枝叶茂密。叶片革质有光泽，深绿色，椭圆形或倒卵形，边缘略反卷。夏季开花，花朵黄白色或淡粉色，具淡香。秋季结果，浆果红色或橙红色，观果价值高。喜温暖湿润气候，耐阴性强，适应性广。是优良的庭院绿化树种和园林景观植物，可孤植、丛植或做绿篱使用。</t>
@@ -10892,8 +10761,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr"/>
-      <c r="I218" t="inlineStr"/>
       <c r="J218" t="inlineStr">
         <is>
           <t>帝罗马托斯卡尼亚陶片装饰品，产自意大利托斯卡纳地区，采用优质陶土手工制作，表面饰有古希腊人物图案，展现古典艺术风格。规格13*3厘米，造型精美，适合用于盆栽装饰、花盆点缀或独立摆放，为园艺空间增添典雅的地中海风情。陶片材质透气性好，耐久性佳，适合室内外使用。</t>
@@ -10936,8 +10803,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr"/>
-      <c r="I219" t="inlineStr"/>
       <c r="J219" t="inlineStr">
         <is>
           <t>花彩师陶粒是一种优质的园艺栽培介质，采用高温烧制工艺制成，具有多孔结构、质轻透气、排水良好的特点。可铺设在盆底作排水层，或混入土壤中改善土壤结构，增加透气性和保水性。适用于多肉植物、花卉、蔬菜等多种植物的栽培，能够有效防止盆底积水烂根，是家庭园艺和商业种植中常用的基础栽培材料。</t>
@@ -10980,8 +10845,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr"/>
-      <c r="I220" t="inlineStr"/>
       <c r="J220" t="inlineStr">
         <is>
           <t>花彩师蓝莓专用介质是专为蓝莓植株设计的酸性培养介质，容量28L。介质配方针对蓝莓生长特性调配，富含蓝莓所需的有机质和微量元素，酸碱度适宜（偏酸性），疏松透气，保水保肥性能优良。适用于蓝莓盆栽、地栽换土、家庭阳台种植等场景，能有效促进蓝莓根系发育和植株健康生长，提高开花结果率。使用时可根据植株大小适量添加，配合适当浇水施肥管理效果更佳。</t>
@@ -11076,8 +10939,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr"/>
-      <c r="I222" t="inlineStr"/>
       <c r="J222" t="inlineStr">
         <is>
           <t>花彩师兰花专用介质是一款专为兰花类植物研发的栽培基质，容量8L。产品采用进口泥炭、树皮、珍珠岩等优质原料科学配比，具有良好的排水性、透气性和保水性，能为兰花肉质根系提供疏松健康的生长环境，有效防止积水烂根。该介质适合蝴蝶兰、石斛兰、文心兰等各类兰花栽培使用，也可用于君子兰等肉质根花卉。换盆或上盆时使用，可提高兰花成活率和开花质量。</t>
@@ -11115,9 +10976,6 @@
           <t>其他多年生草本</t>
         </is>
       </c>
-      <c r="G223" t="inlineStr"/>
-      <c r="H223" t="inlineStr"/>
-      <c r="I223" t="inlineStr"/>
       <c r="J223" t="inlineStr">
         <is>
           <t>商品名称FJGD青春XQZ具体信息不明，无法准确判断植物类型。若为多年生草本种苗，建议根据实际植物特性进行养护，注意光照、水分和土壤条件。具体分类以实物为准。</t>
@@ -11207,9 +11065,6 @@
           <t>珍珠岩</t>
         </is>
       </c>
-      <c r="G225" t="inlineStr"/>
-      <c r="H225" t="inlineStr"/>
-      <c r="I225" t="inlineStr"/>
       <c r="J225" t="inlineStr">
         <is>
           <t>珍珠岩是一种常用的园艺改良材料，具有质轻、多孔、透气性好、保水性强等特点。80L大包装适合家庭园艺和规模化种植使用。可有效改良土壤结构，增加介质透气性和排水性，防止土壤板结，促进根系生长。适用于多肉植物、播种育苗、扦插繁殖等多种园艺场景。使用时建议与其他介质混合搭配使用，比例可根据植物种类和用途适当调整。</t>
@@ -11356,8 +11211,6 @@
           <t>花逸乐</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr"/>
-      <c r="I228" t="inlineStr"/>
       <c r="J228" t="inlineStr">
         <is>
           <t>花逸乐家庭园艺通用营养土，容量为15L。这是一种专为家庭园艺设计的通用型培养土，质地疏松透气、保水保肥性能优良，富含有机质和植物生长所需的营养元素。适用于各类花卉、蔬菜、果树及观叶植物的种植，可直接用于盆栽、地栽或土壤改良。使用时可根据植物特性适量混合园土或其他介质，以达到最佳种植效果。建议存放于阴凉干燥处，避免受潮。</t>
@@ -11400,8 +11253,6 @@
           <t>领优</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr"/>
-      <c r="I229" t="inlineStr"/>
       <c r="J229" t="inlineStr">
         <is>
           <t>领优液压式水壶1.5L是一款实用的园艺浇水工具，采用液压设计，操作省力便捷。1.5L容量适中，适合小型盆栽、花卉及阳台园艺浇水使用。出水均匀，可控制水流大小，避免浇水过多或过少。轻巧便携，手柄设计符合人体工程学，握持舒适。适用于各类室内外植物的日常浇水养护，是家庭园艺爱好者不可或缺的浇灌好帮手。</t>
@@ -11449,7 +11300,6 @@
           <t>龙胆</t>
         </is>
       </c>
-      <c r="I230" t="inlineStr"/>
       <c r="J230" t="inlineStr">
         <is>
           <t>龙胆是龙胆科多年生草本植物，株高30-60厘米，茎直立不分枝。叶片对生，呈卵形或披针形。花朵顶生或腋生，多为蓝紫色，钟状花形，花期7-10月。龙胆喜阳光充足、凉爽湿润的环境，耐寒性较强，适合种植于花境、林缘或岩石园。开花繁茂，花色艳丽，是夏秋季重要的观赏花卉之一。适合疏松肥沃、排水良好的土壤，养护简单，需注意避免积水。</t>
@@ -11492,8 +11342,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr"/>
-      <c r="I231" t="inlineStr"/>
       <c r="J231" t="inlineStr">
         <is>
           <t>帝罗马带边高圆型盆，采用优质白陶材质制作，造型优雅大方，带边设计便于搬动和组合搭配。圆型高桩设计适合种植各类小型盆栽、花卉或多肉植物，通风透气性好，有利于植物根系生长。白陶材质具有良好的保湿性和透气性，适合室内外摆设，提升家居或园艺空间的装饰品味。</t>
@@ -11536,8 +11384,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr"/>
-      <c r="I232" t="inlineStr"/>
       <c r="J232" t="inlineStr">
         <is>
           <t>帝罗马圆型托盘摩卡19是意大利知名园艺品牌帝罗马推出的经典托盘产品，采用优质陶土高温烧制而成，质感细腻，色泽温润的摩卡色调。圆型设计搭配花盆使用，有效收集多余水分，防止桌面或地面潮湿，同时保持植物根系透气。19厘米尺寸适合中型花盆配套使用，是室内外绿植养护的理想配件，兼具实用性与装饰性。</t>
@@ -11580,8 +11426,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr"/>
-      <c r="I233" t="inlineStr"/>
       <c r="J233" t="inlineStr">
         <is>
           <t>帝罗马圆型托盘摩卡21是一款高品质园艺配件产品，采用帝罗马品牌经典的陶土材质制作，具有良好的透气性和排水性，能够有效防止花盆底部积水，保护植物根系健康。圆型设计简洁大方，摩卡色低调优雅，适合各种风格的花盆搭配使用。适用于家庭园艺、阳台种植、庭院装饰等场景，是花卉绿植养护的实用辅助工具。使用时只需将托盘放置在花盆底部，定期清理积水即可保持良好的使用效果。</t>
@@ -11728,8 +11572,6 @@
           <t>虹越</t>
         </is>
       </c>
-      <c r="H236" t="inlineStr"/>
-      <c r="I236" t="inlineStr"/>
       <c r="J236" t="inlineStr">
         <is>
           <t>虹越定制短款园艺手套，采用柳叶型设计，贴合手部曲线，佩戴舒适灵活。短款剪裁方便操作，适合日常园艺养护、种植、翻土等场景使用。有效保护双手免受泥土、枝条刮伤，是园艺爱好者必备的基础工具之一。</t>
@@ -11767,7 +11609,6 @@
           <t>绣球</t>
         </is>
       </c>
-      <c r="G237" t="inlineStr"/>
       <c r="H237" t="inlineStr">
         <is>
           <t>绣球</t>
@@ -11820,8 +11661,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H238" t="inlineStr"/>
-      <c r="I238" t="inlineStr"/>
       <c r="J238" t="inlineStr">
         <is>
           <t>帝罗马圆型托盘白陶21是意大利帝罗马（Deroma）品牌的园艺盆器配件，采用优质白色陶瓷材质制成。圆型设计，21厘米规格，适合搭配同品牌花盆使用。托盘主要用于承接花盆排水、防止水渍污染地面，同时保持植物根系透气。白色陶瓷材质质感细腻，造型简约大方，适合各种家居园艺风格，既实用又具有装饰效果。适用于室内外阳台、花园、露台等场所的花盆配套使用。</t>
@@ -11859,7 +11698,6 @@
           <t>其他乔木</t>
         </is>
       </c>
-      <c r="G239" t="inlineStr"/>
       <c r="H239" t="inlineStr">
         <is>
           <t>柏</t>
@@ -11964,8 +11802,6 @@
           <t>ARTSTONE</t>
         </is>
       </c>
-      <c r="H241" t="inlineStr"/>
-      <c r="I241" t="inlineStr"/>
       <c r="J241" t="inlineStr">
         <is>
           <t>ARTSTONE艾拉花槽37是一款黑色树脂材质的园艺种植槽，设计简约现代，适用于室内外阳台、庭院、露台等空间种植花卉、蔬菜或多肉植物。材质轻便耐用，防水防腐，底部设有排水孔设计，防止积水烂根。黑色经典百搭，适合各种装修风格，可单独摆放或组合使用，满足不同种植需求。</t>
@@ -12060,8 +11896,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H243" t="inlineStr"/>
-      <c r="I243" t="inlineStr"/>
       <c r="J243" t="inlineStr">
         <is>
           <t>花彩师园艺竹炭是一种优质的土壤改良材料，采用高温烧制工艺制作，质地疏松多孔具有良好的透气性和保水性。可有效改善土壤结构，增加土壤中的有机质含量，调节土壤酸碱度。适用于多肉植物、兰花等喜酸性环境的植物栽培，也可用于改善黏重土壤的排水性。使用时建议与其他介质混合搭配，添加量约占总介质的10%-20%为宜。本品容量1.6L，适合家庭园艺小规模使用。</t>
@@ -12104,8 +11938,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H244" t="inlineStr"/>
-      <c r="I244" t="inlineStr"/>
       <c r="J244" t="inlineStr">
         <is>
           <t>花彩师园艺松鳞是采用松树皮加工而成的园艺覆盖材料，颗粒规格为M1.6L。该产品具有优良的透气性和保水性，能够有效调节土壤温湿度，减少水分蒸发，同时抑制杂草生长。松鳞在分解过程中可以为土壤提供有机质，改善土壤结构，适用于盆栽植物、地栽花卉、果树等园艺场景的土壤表面覆盖或改良。使用时可铺设在盆土表面或混入栽培介质中，建议铺设厚度为2-3厘米。</t>
@@ -12148,8 +11980,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H245" t="inlineStr"/>
-      <c r="I245" t="inlineStr"/>
       <c r="J245" t="inlineStr">
         <is>
           <t>帝罗马圆型托盘摩卡23是一款高品质园艺配件，采用帝罗马品牌经典的陶土盆材质制作。圆型设计，摩卡色配色温馨雅致，23厘米规格适合搭配同品牌中型花盆使用。托盘主要用于承接花盆底部排出的多余水分，防止浇水时弄湿地面或家具，同时保持室内清洁。该产品具有优良的透气性和排水性，能有效防止植物根系积水腐烂，是室内外花卉绿植栽培的理想辅助工具。帝罗马品牌以精湛的制盆工艺著称，产品坚固耐用，兼具实用性与装饰性。</t>
@@ -12192,8 +12022,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H246" t="inlineStr"/>
-      <c r="I246" t="inlineStr"/>
       <c r="J246" t="inlineStr">
         <is>
           <t>帝罗马国际盆摩卡19是一款高品质陶瓷花盆，摩卡色调典雅大方，适合各种室内外植物栽种。品牌源自意大利，以精湛工艺和优质材料著称。盆体设计合理，底部设有排水孔，透气性好，有利于植物根系生长。适用于多肉植物、小型花卉、蔬菜育苗等。养护时注意避免暴晒和严寒，保持盆土适度湿润，定期清洁盆面以保持美观。</t>
@@ -12236,8 +12064,6 @@
           <t>维特</t>
         </is>
       </c>
-      <c r="H247" t="inlineStr"/>
-      <c r="I247" t="inlineStr"/>
       <c r="J247" t="inlineStr">
         <is>
           <t>维特10-25泥炭土是一种高品质园艺栽培介质，规格为250升。泥炭土具有良好的保水性、透气和保肥性能，质地疏松轻便，酸碱度适中，适合用于花卉、蔬菜、果树等多种植物的栽培。可单独使用或与其他介质混合使用，是园艺种植中常用的基础栽培材料，适用于盆栽、育苗、花坛等多种应用场景。</t>
@@ -12436,8 +12262,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H251" t="inlineStr"/>
-      <c r="I251" t="inlineStr"/>
       <c r="J251" t="inlineStr">
         <is>
           <t>花彩师植物营养颗粒（爆花型）是一款专为促进花卉开花而设计的缓释肥料。产品为颗粒状，规格400g，使用方便，可直接撒施于土壤表面或与基质混合。富含磷、钾元素，能有效促进花芽分化，增加开花数量，提升花朵色泽艳丽度。肥效持久释放，减少施肥次数，适合各类开花植物如月季、绣球、茉莉等的日常养护。使用时注意避开阳光直射，密封保存于阴凉干燥处。</t>
@@ -12480,8 +12304,6 @@
           <t>虹越</t>
         </is>
       </c>
-      <c r="H252" t="inlineStr"/>
-      <c r="I252" t="inlineStr"/>
       <c r="J252" t="inlineStr">
         <is>
           <t>虹越水溶性肥料20-20-20是一种通用型全元素水溶肥，氮磷钾比例均衡为1:1:1，适用于绝大多数植物的追肥使用。可快速溶解于水中，通过浇灌或叶面喷施方式为植物提供均衡营养，促进植株健康生长。适合花卉、蔬菜、果树及室内绿植使用，尤其在生长期和开花期使用效果显著。使用时需按照推荐浓度稀释，避免浓度过高造成肥害。</t>
@@ -12628,8 +12450,6 @@
           <t>龙泉</t>
         </is>
       </c>
-      <c r="H255" t="inlineStr"/>
-      <c r="I255" t="inlineStr"/>
       <c r="J255" t="inlineStr">
         <is>
           <t>龙泉硬质赤玉土是一种优质的园艺栽培介质，主要成分为火山土，具有良好的透气性、排水性和保水性。颗粒大小3-6mm属于小粒规格，适合多肉植物、仙人掌、兰花等对土壤排水性要求较高的植物使用。硬质赤玉土不易粉化，可长期保持土壤结构稳定，适合作为播种、扦插或成株栽培的基质材料。可单独使用或与其他介质混合配比使用，是阳台园艺和室内盆栽的理想选择。</t>
@@ -12672,8 +12492,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H256" t="inlineStr"/>
-      <c r="I256" t="inlineStr"/>
       <c r="J256" t="inlineStr">
         <is>
           <t>花彩师优+铁线莲专用介质是专为铁线莲等藤本花卉研发的配方土壤，容量28L。采用优质泥炭、珍珠岩、椰糠等原料科学配比，具有良好的透气性、排水性和保水性，pH值适宜铁线莲根系生长。可直接用于铁线莲盆栽或地栽换土，能有效预防根系腐烂，促进植株健康生长，开花更多更艳。</t>
@@ -12716,8 +12534,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H257" t="inlineStr"/>
-      <c r="I257" t="inlineStr"/>
       <c r="J257" t="inlineStr">
         <is>
           <t>花彩师生物有机肥海藻型是一种添加海藻提取物的有机肥料，规格为2.8kg。富含天然海藻活性物质及有机质，可改善土壤结构，增加土壤保水保肥能力，促进植物根系发育。适用于各类花卉、蔬菜、果树等植物的基肥或追肥使用，安全温和，不易烧根，适合家庭园艺和农业生产使用。</t>
@@ -12812,8 +12628,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H259" t="inlineStr"/>
-      <c r="I259" t="inlineStr"/>
       <c r="J259" t="inlineStr">
         <is>
           <t>花彩师果树专用介质是专为果树种植研发的营养土介质，容量8L。该介质针对果树生长特点科学配比，富含有机质和矿物质元素，透气性和排水性优良，能为果树根系提供良好的生长环境。适用于盆栽果树、地栽果树换土或新种时使用，可促进果树健康生长，提高挂果率。建议根据果树种类和生长阶段配合适量基肥使用，每隔1-2年更换一次介质以保持肥力。</t>
@@ -13012,8 +12826,6 @@
           <t>雷欧</t>
         </is>
       </c>
-      <c r="H263" t="inlineStr"/>
-      <c r="I263" t="inlineStr"/>
       <c r="J263" t="inlineStr">
         <is>
           <t>雷欧4分快速接口是一种用于灌溉系统的快速连接配件，适用于4分水管或阀门连接，可实现快速拆装，无需内牙设计，方便用户在园艺灌溉、庭院浇灌等场景中更换或维修管道，提升工作效率。</t>
@@ -13056,8 +12868,6 @@
           <t>爱贝施</t>
         </is>
       </c>
-      <c r="H264" t="inlineStr"/>
-      <c r="I264" t="inlineStr"/>
       <c r="J264" t="inlineStr">
         <is>
           <t>爱贝施蓝宝石包膜硫酸铝是一种土壤改良材料，采用包膜缓释技术，可长期调节土壤酸碱度。硫酸铝能有效降低土壤pH值，适用于蓝莓、杜鹃、茶花、栀子花等喜酸性花卉的栽培。该产品具有缓释性好、用量可控、效果持久等特点，可改善土壤结构，防止植物因土壤碱化引起的黄化病。使用时建议根据土壤检测结果适量施用，避免过量导致土壤过酸。使用时期以早春或秋季为宜，可基施也可追施。</t>
@@ -13147,7 +12957,6 @@
           <t>枫树</t>
         </is>
       </c>
-      <c r="G266" t="inlineStr"/>
       <c r="H266" t="inlineStr">
         <is>
           <t>枫树</t>
@@ -13195,7 +13004,6 @@
           <t>冬青</t>
         </is>
       </c>
-      <c r="G267" t="inlineStr"/>
       <c r="H267" t="inlineStr">
         <is>
           <t>冬青</t>
@@ -13248,8 +13056,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H268" t="inlineStr"/>
-      <c r="I268" t="inlineStr"/>
       <c r="J268" t="inlineStr">
         <is>
           <t>帝罗马国际盆白陶19是一款高端陶瓷花盆，采用优质白色陶土高温烧制而成，质地细腻坚硬，透气性好，适合种植各类花卉绿植。盆器设计简约大方，白色外观易于搭配各种园艺风格，适用于阳台、庭院、窗台等场所种植。可种植多肉植物、小型草花、室内绿植等，是追求品质园艺生活的理想选择。养护时注意避免暴晒和严寒冻裂。</t>
@@ -13292,8 +13098,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H269" t="inlineStr"/>
-      <c r="I269" t="inlineStr"/>
       <c r="J269" t="inlineStr">
         <is>
           <t>帝罗马圆型托盘白陶23是一款高品质陶瓷园艺托盘，采用白色陶瓷材质，圆形设计，简洁大方。作为花盆配套托盘，可有效收集多余水分，防止浇水时弄湿地面，同时增加花盆底部的空气流通性，适合室内外各种盆栽使用，提升整体园艺装饰效果。</t>
@@ -13388,8 +13192,6 @@
           <t>ARTSTONE</t>
         </is>
       </c>
-      <c r="H271" t="inlineStr"/>
-      <c r="I271" t="inlineStr"/>
       <c r="J271" t="inlineStr">
         <is>
           <t>ARTSTONE菲奥纳圆型吊盆25绿色，是一款适合悬挂种植的园艺花盆，材质为仿石质感树脂，坚固耐用且具有良好的透气性和排水性。绿色配色清新自然，适合吊挂种植各类藤本植物、垂吊花卉或多肉植物，可用于阳台、露台、花园等场所装饰。该花盆尺寸约为25cm，适合中小型植物种植，可搭配挂钩或吊链使用，便于垂直空间的绿化装饰。</t>
@@ -13479,7 +13281,6 @@
           <t>冬青</t>
         </is>
       </c>
-      <c r="G273" t="inlineStr"/>
       <c r="H273" t="inlineStr">
         <is>
           <t>冬青</t>
@@ -13532,8 +13333,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H274" t="inlineStr"/>
-      <c r="I274" t="inlineStr"/>
       <c r="J274" t="inlineStr">
         <is>
           <t>帝罗马带边高圆型盆摩卡色是一款来自意大利的经典陶土盆，选用优质黏土高温烧制而成，质地坚固透气性好。带边设计增加了盆器的层次感，圆型造型简洁大方，摩卡色调沉稳典雅，适合各种室内外绿植栽种。帝罗马盆以手工制作著称，盆壁均匀细腻，具有良好的排水性和透气性，有助于植物根系健康生长。此款花盆适合种植多肉、观叶植物、小型灌木等，是提升家居园艺品味的理想选择。</t>
@@ -13628,8 +13427,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H276" t="inlineStr"/>
-      <c r="I276" t="inlineStr"/>
       <c r="J276" t="inlineStr">
         <is>
           <t>花彩师虹彩石是一款高品质园艺颗粒介质，容量1.6L。虹彩石是一种多肉植物常用的颗粒混合土，由多种彩色火山石组成，透气性好、排水性强，可有效防止植物根系积水腐烂。适用于多肉植物、仙人掌、球根花卉等对土壤透气性要求较高的植物栽培。可单独使用或与泥炭土、椰糠等混合使用，改善土壤结构，提升盆栽美观度。建议作为铺面石或栽培介质使用。</t>
@@ -13828,8 +13625,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H280" t="inlineStr"/>
-      <c r="I280" t="inlineStr"/>
       <c r="J280" t="inlineStr">
         <is>
           <t>花彩师矽藻素是一种以硅藻土为主要成分的土壤改良材料，具有优异的透气性和保水性。能有效疏松土壤结构，增加土壤孔隙度，促进根系呼吸和生长。硅藻土富含多种微量元素，可为植物提供养分支持，同时具有调节土壤酸碱度的作用。适用于多肉植物、花卉、蔬菜等多种园艺植物的土壤改良，使用时可与营养土混合或撒施于盆土表面。</t>
@@ -13872,8 +13667,6 @@
           <t>马雅</t>
         </is>
       </c>
-      <c r="H281" t="inlineStr"/>
-      <c r="I281" t="inlineStr"/>
       <c r="J281" t="inlineStr">
         <is>
           <t>马雅彩叶芋专用营养液，规格10ml单支装。本品专为彩叶芋（花叶芋）设计，富含彩叶芋生长所需的营养元素，可促进叶片色彩鲜艳、纹路清晰。使用方法为稀释后浇灌或叶面喷施，适合彩叶芋生长季节（春夏）使用，每7-14天施用一次。注意薄肥勤施，避免浓度过高造成肥害。适用于家庭园艺养护彩叶芋盆栽。</t>
@@ -13916,8 +13709,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H282" t="inlineStr"/>
-      <c r="I282" t="inlineStr"/>
       <c r="J282" t="inlineStr">
         <is>
           <t>花彩师园艺核鳞M1.6L是一款专为球根植物研发的特肥产品，容量为1.6升。核鳞系列主要针对鳞茎类植物的生长发育设计，含有促进球根膨大、根系健壮的营养成分。适用于郁金香、朱顶红、百合、风信子等鳞茎植物的生长期和开花期养护。使用时需按比例稀释后浇灌，注意薄肥勤施的原则。保存时应置于阴凉干燥处，避免阳光直射。产品为液体形态，便于稀释使用和植物快速吸收。</t>
@@ -13960,8 +13751,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H283" t="inlineStr"/>
-      <c r="I283" t="inlineStr"/>
       <c r="J283" t="inlineStr">
         <is>
           <t>花彩师植物高浓缩营养液（草莓型）是一款专为草莓及浆果类植物设计的全能型水溶肥料。产品采用高浓缩配方，富含氮磷钾及微量元素，营养均衡全面。采用水溶技术，溶解迅速彻底，便于根部吸收或叶面喷施。250ml瓶装设计，小巧便携，适合家庭园艺使用。可促进草莓植株健壮生长，提高坐果率，改善果实品质和口感，增强抗病能力。使用时按比例稀释，薄肥勤施，避免烧根。适用于阳台盆栽草莓、庭院草莓种植及各类浆果植物追肥。</t>
@@ -14160,8 +13949,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H287" t="inlineStr"/>
-      <c r="I287" t="inlineStr"/>
       <c r="J287" t="inlineStr">
         <is>
           <t>花彩师蛭石是一种优质的园艺改良材料，规格为14L。蛭石具有质轻、疏松、透气性好、保水保肥能力强等特点，可有效改善土壤结构，增加土壤通气性和排水性。适用于多肉植物栽培、种子育苗、扦插繁殖等场景，能为植物根系提供良好的生长环境。pH值呈中性，化学性质稳定，可与其他介质混合使用。建议配合营养土、椰糠等材料使用，比例可根据植物需求调整。</t>
@@ -14308,8 +14095,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H290" t="inlineStr"/>
-      <c r="I290" t="inlineStr"/>
       <c r="J290" t="inlineStr">
         <is>
           <t>花彩师珍珠岩是一种优质的园艺土壤改良材料，容量为14L。珍珠岩具有质轻、多孔、透气性好、保水性强等特点，能够有效改善土壤结构，增加土壤通气性和排水性，防止土壤板结。本品为中粒规格（M），适用于多肉植物、花卉、蔬菜等多种园艺场景的土壤配比，可与泥炭土、椰糠等基质混合使用，提升整体栽培效果。</t>
@@ -14456,8 +14241,6 @@
           <t>花逸乐</t>
         </is>
       </c>
-      <c r="H293" t="inlineStr"/>
-      <c r="I293" t="inlineStr"/>
       <c r="J293" t="inlineStr">
         <is>
           <t>花逸乐海藻有机颗粒肥是一款以天然海藻为主要原料的有机肥料，富含多种微量元素和植物生长因子。颗粒状设计便于均匀撒施，肥效持久温和，适合各类花卉、蔬菜、果树等植物的基肥和追肥使用。能有效改善土壤结构，增加土壤有机质含量，促进根系发育，增强植物抗病抗逆能力。4kg包装适合家庭园艺和小型花圃使用，安全无污染，是追求有机种植的理想选择。使用时可根据植物需求适量施用，避免直接接触根部。</t>
@@ -14495,13 +14278,11 @@
           <t>蓝莓</t>
         </is>
       </c>
-      <c r="G294" t="inlineStr"/>
       <c r="H294" t="inlineStr">
         <is>
           <t>蓝莓</t>
         </is>
       </c>
-      <c r="I294" t="inlineStr"/>
       <c r="J294" t="inlineStr">
         <is>
           <t>蓝莓是杜鹃花科越橘属的落叶或常绿灌木，原产于北美洲，现已广泛栽培于全球温带地区。蓝莓果实呈蓝色，富含花青素、维生素C、维生素E等营养成分，具有很高的食用价值和保健功能。蓝莓树形矮小紧凑，适合家庭园艺种植，既可观赏又可收获果实。喜酸性土壤（pH值4.5-5.5），喜阳光充足，耐寒性强，成年株高约1-2米，需要异花授粉才能提高结果率。栽植时应选择排水良好、富含有机质的酸性土壤，生长期保持土壤湿润但避免积水，每年春季萌芽前可施用酸性肥料。</t>
@@ -14601,7 +14382,6 @@
           <t>枸杞</t>
         </is>
       </c>
-      <c r="I296" t="inlineStr"/>
       <c r="J296" t="inlineStr">
         <is>
           <t>南方枸杞是适合南方气候种植的枸杞品种，属于茄科枸杞属落叶灌木。其果实为红色小浆果，具有食用和药用价值。喜阳光充足、排水良好的环境，耐旱性较强，适宜在温暖湿润的南方地区栽培。主要用于庭院种植或经济作物栽培，春季开花，秋季结果，养护相对简单。</t>
@@ -14696,8 +14476,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H298" t="inlineStr"/>
-      <c r="I298" t="inlineStr"/>
       <c r="J298" t="inlineStr">
         <is>
           <t>帝罗马国际盆白陶17是一款来自意大利的经典陶土花盆，采用优质白色陶土烧制而成，质地细腻透气，适合种植各类花卉、蔬菜及小型灌木。该盆设计简约大方，白色釉面典雅美观，可搭配多种园艺风格。采用传统工艺制作，具有良好的排水性和透气性，有利于植物根系健康生长。适合室内外使用，可放置于阳台、露台、花园或客厅等场所。清洗方便，可重复使用。</t>
@@ -14735,7 +14513,6 @@
           <t>其他灌木</t>
         </is>
       </c>
-      <c r="G299" t="inlineStr"/>
       <c r="H299" t="inlineStr">
         <is>
           <t>石斑木</t>
@@ -14788,8 +14565,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H300" t="inlineStr"/>
-      <c r="I300" t="inlineStr"/>
       <c r="J300" t="inlineStr">
         <is>
           <t>花彩师月季专用介质是专为月季植物研发的优质栽培介质，容量为10L。本品根据月季的生长习性科学配比，疏松透气、保水保肥、排水良好，能为月季根系提供充足的氧气和养分。适用于盆栽和地栽月季的种植、换盆使用，能有效促进月季生长开花，提高抗病能力。使用时建议配合适量底肥，日常注意适量浇水，保持介质湿润但避免积水。</t>
@@ -14832,8 +14607,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H301" t="inlineStr"/>
-      <c r="I301" t="inlineStr"/>
       <c r="J301" t="inlineStr">
         <is>
           <t>花彩师植物高浓缩营养液是一款有机型园艺液体肥料，容量为250ml/瓶。采用高浓缩配方设计，使用时需稀释后施用。该产品富含有机物质和植物生长所需营养元素，能为家庭园艺植物提供全面的营养支持。有机配方温和不伤根，适合各类室内外观赏植物、蔬菜、果树等使用。使用方法简单便捷，按推荐比例稀释后浇灌或叶面喷施均可。可促进植物健康生长，增强植株抗病抗逆能力，改善土壤微环境，是家庭园艺养护的理想选择。</t>
@@ -14980,8 +14753,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H304" t="inlineStr"/>
-      <c r="I304" t="inlineStr"/>
       <c r="J304" t="inlineStr">
         <is>
           <t>花彩师有机肥料选用优质鸡粪为原料，经过充分发酵腐熟制成，富含有机质和植物生长所需的氮、磷、钾等营养元素。肥效温和持久，不会烧根，适合各类花卉、蔬菜、果树等植物使用。可作底肥或追肥使用，能改良土壤结构，提高土壤肥力，促进植物健康生长。是家庭园艺中常用的环保型肥料。</t>
@@ -15123,7 +14894,6 @@
           <t>冬青</t>
         </is>
       </c>
-      <c r="G307" t="inlineStr"/>
       <c r="H307" t="inlineStr">
         <is>
           <t>冬青</t>
@@ -15176,8 +14946,6 @@
           <t>ARTSTONE</t>
         </is>
       </c>
-      <c r="H308" t="inlineStr"/>
-      <c r="I308" t="inlineStr"/>
       <c r="J308" t="inlineStr">
         <is>
           <t>ARTSTONE菲奥纳圆型吊盆，采用优质树脂材质，轻便耐用，适合悬挂种植藤本花卉或垂吊植物。25号尺寸适合种植中等规格植物，紫色设计优雅美观，可用于阳台、庭院、花架等场景悬挂装饰，提升空间绿化效果。</t>
@@ -15215,13 +14983,11 @@
           <t>其他灌木</t>
         </is>
       </c>
-      <c r="G309" t="inlineStr"/>
       <c r="H309" t="inlineStr">
         <is>
           <t>厚皮香</t>
         </is>
       </c>
-      <c r="I309" t="inlineStr"/>
       <c r="J309" t="inlineStr">
         <is>
           <t>厚皮香（Ternstroemia gymnanthera）是山茶科厚皮香属常绿灌木或小乔木，原产于中国长江以南地区及东南亚。株高可达3-8米，叶片革质、互生，呈椭圆形或倒卵形，表面有光泽。花小而清香，白色或淡黄色，通常在夏季开放。果实为浆果，成熟时呈红色。厚皮香喜温暖湿润气候，耐半阴，适应性较强，适合用于庭院绿化、行道树或公园景观配置，具有较高的观赏价值和生态价值。</t>
@@ -15524,8 +15290,6 @@
           <t>马雅Maya</t>
         </is>
       </c>
-      <c r="H315" t="inlineStr"/>
-      <c r="I315" t="inlineStr"/>
       <c r="J315" t="inlineStr">
         <is>
           <t>马雅90天然植物赋能小黑瓶是一款植物护理产品，采用天然配方设计，可为植物提供营养补充和能量赋能。产品为100ml容量的小瓶装，使用方便，适合家庭园艺使用。适用于各类室内外植物，可促进植物生长活力，增强植物抗逆性。使用时按比例稀释后浇灌或叶面喷施即可。注意避免阳光直射，储存于阴凉干燥处。</t>
@@ -15568,8 +15332,6 @@
           <t>君沐</t>
         </is>
       </c>
-      <c r="H316" t="inlineStr"/>
-      <c r="I316" t="inlineStr"/>
       <c r="J316" t="inlineStr">
         <is>
           <t>君沐0.76m浇水把手是一款园艺浇水辅助工具，长度约0.76米，适合连接水管或浇水壶使用。该产品主要用于花园、庭院浇灌作业，可帮助用户轻松浇灌远处植物或高处盆栽，避免弯腰或踩踏损坏花草。使用时注意定期检查把手连接处是否漏水，保持接口密封性。材质通常为塑料或金属，轻便耐用。适用于各类园艺浇灌场景。</t>
@@ -15612,8 +15374,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H317" t="inlineStr"/>
-      <c r="I317" t="inlineStr"/>
       <c r="J317" t="inlineStr">
         <is>
           <t>花彩师缓释肥料是一款专为园艺植物设计的氮钾型复合肥料，氮磷钾配比为16-06-16，并添加了TE微量元素，全面补充植物生长所需营养。采用缓释技术，营养释放均匀持久，可持续供肥2-3个月，减少施肥次数。适合各类花卉、蔬菜、果树等植物使用，尤其适用于生长期和开花结果期。使用时均匀撒施于盆土表面或浅埋入土中，配合浇水效果更佳。500g包装适合家庭园艺使用。</t>
@@ -15656,8 +15416,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H318" t="inlineStr"/>
-      <c r="I318" t="inlineStr"/>
       <c r="J318" t="inlineStr">
         <is>
           <t>花彩师绣球调蓝剂是一种专为绣球花设计的酸性肥料产品，主要成分为硫酸铝等调蓝物质。400g包装适合家庭园艺使用。使用方法简单，按说明比例溶于水后浇灌绣球根部即可。该产品能有效降低土壤pH值，促进绣球花吸收铝离子，使绣球花呈现鲜艳的蓝色。注意调蓝效果与土壤原有pH值、花色品种有关，建议在绣球花现蕾前开始使用，连续使用2-3次效果更佳。使用时应避免直接接触叶片，防止灼伤。适用于无尽夏等大花绣球品种。</t>
@@ -15700,8 +15458,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H319" t="inlineStr"/>
-      <c r="I319" t="inlineStr"/>
       <c r="J319" t="inlineStr">
         <is>
           <t>花彩师喜酸型介质是专为喜酸性植物配制的栽培介质，容量28L。适用于杜鹃、蓝莓、茶花、栀子花等喜酸植物的种植。介质呈酸性反应，pH值在4.5-5.5之间，含有丰富的腐殖质和营养成分，透气性好、保水性强，能够满足喜酸植物对生长环境的要求。使用时可与其他介质混合调配，也可直接用于盆栽或地栽，能有效改善土壤酸碱度，促进喜酸植物健康生长。</t>
@@ -15744,8 +15500,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H320" t="inlineStr"/>
-      <c r="I320" t="inlineStr"/>
       <c r="J320" t="inlineStr">
         <is>
           <t>帝罗马是知名的园艺盆器品牌，产自意大利，以高质量的红陶和白石陶著称。此款白陶带边高圆型盆采用天然陶土烧制而成，质地透气性好，有利于植物根系生长。白色陶盆色泽素雅美观，适合搭配各种室内外植物，可用于多肉、绿植、花卉的种植栽培。盆器边缘设计带有一圈装饰性边沿，增加产品的精致感和美观度。</t>
@@ -15788,8 +15542,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H321" t="inlineStr"/>
-      <c r="I321" t="inlineStr"/>
       <c r="J321" t="inlineStr">
         <is>
           <t>帝罗马科诺高圆型盆，采用优质白陶材质烧制而成，质感细腻温润，透气性好，适宜种植各类花卉绿植。圆型高盆设计，造型优雅大方，适合种植株型较高的植物，如小型灌木、藤本花卉或观叶植物，可有效支撑植物茎干，防止倒伏。白陶材质排水透气性能优异，有助于根系呼吸生长，是家庭园艺和商业景观的优质选择。</t>
@@ -15832,8 +15584,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H322" t="inlineStr"/>
-      <c r="I322" t="inlineStr"/>
       <c r="J322" t="inlineStr">
         <is>
           <t>花彩师草莓专用介质是专为草莓种植设计的营养土，容量12升。该介质针对草莓根系生长特点优化配方，透气性好、保水性强，富含草莓生长所需营养元素。可直接用于盆栽草莓或地栽草莓土壤改良，使用时保持介质湿润，放置于阳光充足环境，定期施肥管理，有助于草莓茁壮生长并提高果实产量。</t>
@@ -15928,8 +15678,6 @@
           <t>君沐</t>
         </is>
       </c>
-      <c r="H324" t="inlineStr"/>
-      <c r="I324" t="inlineStr"/>
       <c r="J324" t="inlineStr">
         <is>
           <t>君沐400目喷头是一款园艺浇水工具配件，400目表示喷头滤网的精细过滤等级，可实现细密均匀的喷雾效果。该喷头通常用于园艺浇水作业中，可调节喷雾模式，适用于花卉、蔬菜、盆栽等植物的日常浇水、喷雾保湿及叶面施肥等养护需求。9%可能指代产品配方浓度或特定规格参数，需配合相应容器或浇水工具使用。</t>
@@ -15972,8 +15720,6 @@
           <t>成都神龙</t>
         </is>
       </c>
-      <c r="H325" t="inlineStr"/>
-      <c r="I325" t="inlineStr"/>
       <c r="J325" t="inlineStr">
         <is>
           <t>成都神龙-云苗库果树营养土，12L装，是一款专为果树种植设计的营养土产品。富含有机质和营养成分，透气性好，保水保肥能力强，能有效促进果树根系生长发育，提高果树成活率。适用于各种果树苗木的盆栽、地栽种植，是家庭园艺和果树栽培的理想选择。</t>
@@ -16016,8 +15762,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H326" t="inlineStr"/>
-      <c r="I326" t="inlineStr"/>
       <c r="J326" t="inlineStr">
         <is>
           <t>帝罗马托斯卡尼亚长条型托盘，意大利知名陶土盆品牌出品，经典托斯卡纳风格设计。选用优质陶土材质，排水透气性好，适合搭配长条型花盆使用，可有效防止浇水时水分溢出，保护桌面地面清洁。30cm尺寸适合中小型盆栽托底使用，是阳台、花园、露台园艺的理想配件选择。</t>
@@ -16268,8 +16012,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H331" t="inlineStr"/>
-      <c r="I331" t="inlineStr"/>
       <c r="J331" t="inlineStr">
         <is>
           <t>陶粒是一种轻质多孔的颗粒状材料，由黏土等原料经高温烧制而成。在园艺中，常用于改良土壤结构，增加排水性和透气性，防止土壤板结，适用于多肉植物、花卉等的栽培介质。</t>
@@ -16312,8 +16054,6 @@
           <t>云柱</t>
         </is>
       </c>
-      <c r="H332" t="inlineStr"/>
-      <c r="I332" t="inlineStr"/>
       <c r="J332" t="inlineStr">
         <is>
           <t>云柱系列花盆，米白色配色，25cm规格。采用优质陶瓷或树脂材质制作，造型简约大方，适合种植中小型植物。圆柱形设计节省空间，稳定性好，适合室内外阳台、窗台等场景使用。具有良好的透气性和排水性，有助于植物根系健康生长。清洁方便，经久耐用。</t>
@@ -16403,9 +16143,6 @@
           <t>花卉专用介质</t>
         </is>
       </c>
-      <c r="G334" t="inlineStr"/>
-      <c r="H334" t="inlineStr"/>
-      <c r="I334" t="inlineStr"/>
       <c r="J334" t="inlineStr">
         <is>
           <t>铁线莲专用营养土是根据铁线莲的生长习性特别配制的土壤介质，疏松透气、排水良好，富含铁线莲所需的营养成分，酸碱度适宜，有利于铁线莲根系的生长发育。可直接用于铁线莲的盆栽换土或地栽土壤改良，使用时保持土壤湿润但避免积水，定期施肥以补充养分。</t>
@@ -16552,8 +16289,6 @@
           <t>马雅</t>
         </is>
       </c>
-      <c r="H337" t="inlineStr"/>
-      <c r="I337" t="inlineStr"/>
       <c r="J337" t="inlineStr">
         <is>
           <t>马雅Maya91矿物有机肥浓缩营养液是一款通用型液体肥料，容量为100ml。产品富含矿物元素和有机营养成分，采用浓缩配方，使用时需稀释后可应用于各类观赏植物、蔬菜、果树等。具有养分全面、吸收迅速、使用方便等特点，可作为日常追肥或补充营养使用，适用于基质栽培和土壤栽培。建议按照说明书的稀释比例使用，避免浓度过高造成肥害。适合家庭园艺和商业种植场景。</t>
@@ -16596,8 +16331,6 @@
           <t>ARTSTONE</t>
         </is>
       </c>
-      <c r="H338" t="inlineStr"/>
-      <c r="I338" t="inlineStr"/>
       <c r="J338" t="inlineStr">
         <is>
           <t>ARTSTONE菲奥纳圆型吊盆25粉色是一款造型美观的园艺悬挂式花盆，采用优质树脂材料制成，轻巧耐用，适合室内外悬挂种植各类花卉植物。圆形设计搭配粉色配色，清新雅致，可作为阳台、窗台、露台等空间的装饰点缀。盆体设计有排水孔，可有效防止积水，保护植物根系健康。25厘米的直径适合种植中小型植物，如多肉、绿植或草本花卉。</t>
@@ -16640,8 +16373,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H339" t="inlineStr"/>
-      <c r="I339" t="inlineStr"/>
       <c r="J339" t="inlineStr">
         <is>
           <t>帝罗马科诺高圆型盆白陶 16是一款高品质陶瓷花盆，采用优质白陶材质制作，具有出色的透气性和排水性，有利于植物根系健康生长。圆型设计简约大方，科诺高款式线条流畅，适合种植各类花卉、绿植或多肉植物。16寸规格适合中型植物栽培，可用于阳台、庭院、客厅等多种场景装饰。品牌盆定位中高端，工艺精湛，耐久性强，是追求品质生活的园艺爱好者理想选择。</t>
@@ -16788,8 +16519,6 @@
           <t>虹越</t>
         </is>
       </c>
-      <c r="H342" t="inlineStr"/>
-      <c r="I342" t="inlineStr"/>
       <c r="J342" t="inlineStr">
         <is>
           <t>虹越定制1.5L气压喷雾器，柠檬绿配色。采用气压式设计，手柄按压即可产生持续雾化喷洒效果。容量为1.5升，适合室内外植物浇水、叶面清洁、病虫害药物喷洒使用。轻便易操作，是家庭园艺养护的实用辅助工具。</t>
@@ -16988,8 +16717,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H346" t="inlineStr"/>
-      <c r="I346" t="inlineStr"/>
       <c r="J346" t="inlineStr">
         <is>
           <t>花彩师火山石是一种优质的园艺改良材料，选用天然火山石经过筛选加工而成。火山石具有多孔结构，质地轻盈透气，富含多种微量元素，能够改善土壤排水性和透气性。适用于多肉植物、兰花、仙人掌等需要良好排水环境的植物栽培，可铺面或混土使用，能有效防止土壤板结，促进根系呼吸生长。XL规格1.6L适合家庭园艺使用。</t>
@@ -17084,8 +16811,6 @@
           <t>成都神龙</t>
         </is>
       </c>
-      <c r="H348" t="inlineStr"/>
-      <c r="I348" t="inlineStr"/>
       <c r="J348" t="inlineStr">
         <is>
           <t>成都神龙庭院改良土，容量50L，是一种专门用于改良庭院土壤质量的营养介质。富含腐殖质和有机质，能够有效疏松土壤、改善土壤结构、提升土壤肥力和保水保肥能力。适用于庭院花园、家庭菜园、果树种植等场景的土壤改良。使用时建议与原土混合均匀，可显著提升土壤透气性和肥力，适合各类花卉、蔬菜、果树的生长需求。</t>
@@ -17180,8 +16905,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H350" t="inlineStr"/>
-      <c r="I350" t="inlineStr"/>
       <c r="J350" t="inlineStr">
         <is>
           <t>花彩师园艺用骨粉有机肥是一款高品质有机肥料，净含量900g。骨粉是由动物骨骼加工而成的天然肥料，富含磷、钙等营养元素，能促进植物根系发育和开花结果。适用于各类花卉、蔬菜、果树的基肥和追肥使用，可撒施或穴施。使用时需注意适量，避免过量造成肥害。本品有机质含量丰富，能改良土壤结构，提高土壤肥力，是家庭园艺和农业生产中常用的优质有机肥。</t>
@@ -17380,8 +17103,6 @@
           <t>虹越定制</t>
         </is>
       </c>
-      <c r="H354" t="inlineStr"/>
-      <c r="I354" t="inlineStr"/>
       <c r="J354" t="inlineStr">
         <is>
           <t>虹越定制360度旋转喷头气压喷壶，容量1.5L，采用柠檬绿配色。配备360度可旋转喷头，可实现全方位均匀浇灌；气压设计，操作省力便捷；雾化效果细腻，适合花卉、蔬菜、盆栽等浇水需求，也可用于叶面施肥或喷药。是家庭园艺浇水的实用工具。</t>
@@ -17419,9 +17140,6 @@
           <t>其他改良材料</t>
         </is>
       </c>
-      <c r="G355" t="inlineStr"/>
-      <c r="H355" t="inlineStr"/>
-      <c r="I355" t="inlineStr"/>
       <c r="J355" t="inlineStr">
         <is>
           <t>松鳞树皮是一种优质的园艺覆盖材料，选用天然松树皮经过消毒处理加工而成。具有良好的保湿透气性能，可有效防止土壤水分蒸发，调节土壤温度，抑制杂草生长。松鳞树皮自然分解后还能为土壤提供有机质，改善土壤结构，增加土壤肥力。适用于花园地被、盆栽表面覆盖、花坛边缘装饰等场景。使用时建议铺设在土壤表面，厚度约3-5厘米，可根据实际需要调整。该产品为大包装规格，适合庭院、苗圃等大面积使用。</t>
@@ -17464,8 +17182,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H356" t="inlineStr"/>
-      <c r="I356" t="inlineStr"/>
       <c r="J356" t="inlineStr">
         <is>
           <t>花彩师有机肥料采用天然羊粪为原料，经过充分腐熟发酵处理，富含有机质、氮磷钾及微量元素。适用于家庭园艺各类植物的基肥或追肥使用，能有效改良土壤结构，增加土壤肥力，促进植物根系发育和健康生长。肥效温和持久，不易烧根，适合花卉、蔬菜、果树等植物使用。建议作基肥时深施拌土，追肥时开沟埋施后覆土，施肥后保持适量水分以利肥效释放。</t>
@@ -17508,8 +17224,6 @@
           <t>菲力糠</t>
         </is>
       </c>
-      <c r="H357" t="inlineStr"/>
-      <c r="I357" t="inlineStr"/>
       <c r="J357" t="inlineStr">
         <is>
           <t>菲力糠免泡椰糠100L是一款高品质园艺栽培介质，选用优质椰糠原料加工而成。免泡设计，使用方便快捷，节省准备时间。椰糠具有良好的透气性和保水性，质地轻盈，结构稳定，不易分解。可单独使用或与其他介质混合使用，适用于多肉植物、花卉、蔬菜等各种植物的栽培。可改善土壤结构，增加排水性，为根系提供良好的生长环境，是家庭园艺和商业花卉生产的理想选择。</t>
@@ -17552,8 +17266,6 @@
           <t>马雅Maya</t>
         </is>
       </c>
-      <c r="H358" t="inlineStr"/>
-      <c r="I358" t="inlineStr"/>
       <c r="J358" t="inlineStr">
         <is>
           <t>马雅Maya92液体花卉型肥料是一款专为花卉植物设计的液态水溶肥料，容量500ml。采用科学配比，富含氮磷钾及微量元素，能有效促进花卉生长开花，提高开花质量。液体剂型溶解迅速，便于浇灌或叶面喷施，使用便捷。适用于各类室内外观赏花卉，如月季、绣球、仙客来等。使用时按比例稀释，薄肥勤施效果更佳。注意避免阳光直射，存放于阴凉干燥处。</t>
@@ -17648,8 +17360,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H360" t="inlineStr"/>
-      <c r="I360" t="inlineStr"/>
       <c r="J360" t="inlineStr">
         <is>
           <t>帝罗马圆型托盘白陶款，采用优质白陶材质制作，圆型设计经典实用。托盘用于承接花盆底部流出的水分，防止泥土污染地面，同时保持桌面或地面清洁。白色陶土质感温润，与帝罗马品牌花盆搭配统一美观。适用于室内外各种盆栽使用，是园艺装饰中的实用配件。</t>
@@ -17796,8 +17506,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H363" t="inlineStr"/>
-      <c r="I363" t="inlineStr"/>
       <c r="J363" t="inlineStr">
         <is>
           <t>花彩师优+蔬菜介质是专为蔬菜种植研发的优质培养土，容量8L。采用科学配比的营养基质，富含蔬菜生长所需的有机质和微量元素，具有良好的透气性和保水性。适用于家庭阳台菜园、室内盆栽蔬菜、果菜类蔬菜育苗等场景。能促进蔬菜根系发育，提高移栽成活率，是种植番茄、黄瓜、辣椒、叶菜等蔬菜的理想栽培介质。使用前建议松动介质并适当浇水湿润。</t>
@@ -17892,8 +17600,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H365" t="inlineStr"/>
-      <c r="I365" t="inlineStr"/>
       <c r="J365" t="inlineStr">
         <is>
           <t>花彩师球根专用介质是专为球根类植物研发的栽培基质，容量为50升。本品针对球根花卉根系特点优化配方，透气性和排水性优异，能有效防止球根腐烂。富含有机质和微量元素，适合郁金香、朱顶红、百合、风信子等球根植物的种植与养护。可直接用于盆栽或地栽球根植物，提供良好的根际环境，促进球根健康成长和开花。</t>
@@ -17931,7 +17637,6 @@
           <t>冬青</t>
         </is>
       </c>
-      <c r="G366" t="inlineStr"/>
       <c r="H366" t="inlineStr">
         <is>
           <t>冬青</t>
@@ -17984,8 +17689,6 @@
           <t>马雅</t>
         </is>
       </c>
-      <c r="H367" t="inlineStr"/>
-      <c r="I367" t="inlineStr"/>
       <c r="J367" t="inlineStr">
         <is>
           <t>马雅90浓缩营养液是一种通用型植物肥料，规格为30ml浓缩装。适用于各类室内外观赏植物、果蔬等，可快速补充植物生长所需营养元素。使用时需按比例稀释后浇灌或叶面喷施，适合家庭园艺日常养护使用。</t>
@@ -18127,13 +17830,11 @@
           <t>其他灌木</t>
         </is>
       </c>
-      <c r="G370" t="inlineStr"/>
       <c r="H370" t="inlineStr">
         <is>
           <t>赤楠</t>
         </is>
       </c>
-      <c r="I370" t="inlineStr"/>
       <c r="J370" t="inlineStr">
         <is>
           <t>赤楠是桃金娘科蒲桃属的常绿灌木或小乔木，原产于中国南方各省。植株株型紧凑，叶片对生且小巧革质，呈深绿色有光泽。春季开白色小花，秋季结紫色小果，具有一定观赏价值。赤楠适应性强，耐修剪，萌芽性好，是制作盆景的优质材料，也可用于园林地被、庭院点缀或道路绿化。喜温暖湿润气候，对土壤要求不严，适宜光照充足或半阴环境生长。</t>
@@ -18176,8 +17877,6 @@
           <t>马雅</t>
         </is>
       </c>
-      <c r="H371" t="inlineStr"/>
-      <c r="I371" t="inlineStr"/>
       <c r="J371" t="inlineStr">
         <is>
           <t>马雅92浓缩营养液花卉型是一款高浓度水溶性肥料，富含氮磷钾及微量元素，专门针对花卉植物的生长发育需求配制。浓缩型设计便于稀释使用，适用于各类室内外观赏花卉的追肥需求。产品能促进花卉叶片翠绿、花朵艳丽，延长开花期。使用时需按说明比例稀释后浇灌或叶面喷施，避免浓度过高造成肥害。建议在生长期和花期定期施用，每次施肥间隔7-14天为宜。</t>
@@ -18220,8 +17919,6 @@
           <t>马雅</t>
         </is>
       </c>
-      <c r="H372" t="inlineStr"/>
-      <c r="I372" t="inlineStr"/>
       <c r="J372" t="inlineStr">
         <is>
           <t>马雅Maya93液体果蔬型肥料是一款专为果蔬植物设计的液体水溶肥，容量30ml。该产品采用液体剂型，易于溶解于水后浇灌或叶面喷施，使用便捷。富含果蔬生长所需的营养元素，能有效促进植物生长、开花结果，提高果实品质和产量。适用于家庭园艺中种植的各类果蔬作物，如番茄、黄瓜、草莓等。使用时按说明稀释后施用，避免直接接触根部造成肥害。阴凉干燥处保存，注意避免儿童误食。</t>
@@ -18420,8 +18117,6 @@
           <t>雪瑞奇</t>
         </is>
       </c>
-      <c r="H376" t="inlineStr"/>
-      <c r="I376" t="inlineStr"/>
       <c r="J376" t="inlineStr">
         <is>
           <t>雪瑞奇青蛙滴水器是一款创意园艺浇水工具，设计成可爱的青蛙造型，绿色配色清新自然。该滴水器采用自动滴灌原理，通过调节水流速度实现持续、均匀的浇水效果，适用于室内外观赏植物的养护。使用时将装满水的瓶子倒置插入滴水器，的水会通过滴水器缓慢滴入土壤，避免积水或干旱，特别适合出差、旅行等外出场景下植物的自动浇水需求。安装简便，可重复使用，是家庭园艺爱好者的实用小工具。</t>
@@ -18464,8 +18159,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H377" t="inlineStr"/>
-      <c r="I377" t="inlineStr"/>
       <c r="J377" t="inlineStr">
         <is>
           <t>花彩师植物营养颗粒是一款通用型园艺肥料产品，规格为400g。该产品采用颗粒状设计，便于均匀撒施或混入土壤中使用。适用于各类室内外观赏植物、蔬菜、果树等的日常施肥管理。能提供植物生长所需的氮磷钾等营养元素，促进植株健康生长，增强抗病能力。颗粒型缓释设计可缓慢释放养分，减少施肥频次，使用方便省心。建议根据植物种类和生长阶段适量施用，避免过量造成肥害。</t>
@@ -18560,8 +18253,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H379" t="inlineStr"/>
-      <c r="I379" t="inlineStr"/>
       <c r="J379" t="inlineStr">
         <is>
           <t>鹿沼土是一种源自日本鹿沼地区的酸性火山土，质地疏松透气，排水性良好，PH值呈酸性（5.5-6.0）。小粒规格适合作为栽培基质配料或铺面使用，常用于种植杜鹃、茶花、蓝莓、兰花等喜酸性植物。可单独使用或与泥炭、珍珠岩等混合调配，能有效改善土壤结构，防止板结，促进根系生长。使用时可根据植物需求适量添加。</t>
@@ -18604,8 +18295,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H380" t="inlineStr"/>
-      <c r="I380" t="inlineStr"/>
       <c r="J380" t="inlineStr">
         <is>
           <t>花彩师园艺围裙-蓝色牛仔，采用优质牛仔布料制作，具有耐磨、防水、防污的特性，设计合理配有可调节腰带，适合各种园艺作业场景穿着使用，能有效保护衣物免受泥土、水分和肥料的侵染，蓝色牛仔配色清新自然，是家庭园艺爱好者和专业园艺工作者进行种植、施肥、修剪等作业时的实用防护用品。</t>
@@ -18648,8 +18337,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H381" t="inlineStr"/>
-      <c r="I381" t="inlineStr"/>
       <c r="J381" t="inlineStr">
         <is>
           <t>室内绿植专用介质是专为室内观叶植物设计的培养土配方，具有良好的透气性、保水性和排水性，能为绿萝、吊兰、龟背竹、虎皮兰等室内绿植提供适宜的生长环境。该介质通常由泥炭、椰糠、珍珠岩、缓释肥等科学配比而成，PH值适宜室内植物生长需求。可直接用于换盆或拌土使用，适合家居园艺种植。</t>
@@ -18692,8 +18379,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H382" t="inlineStr"/>
-      <c r="I382" t="inlineStr"/>
       <c r="J382" t="inlineStr">
         <is>
           <t>帝罗马国际盆白陶13是一款意大利进口的白色陶土花盆，经典设计造型，透气性好，适合种植各类花卉和小型灌木。陶土材质具有良好的排水性和透气性，有利于植物根系生长。白色外观简洁大方，适用于阳台、花园、露台等多种场景。尺寸规格适合中小型植物栽培。</t>
@@ -18840,8 +18525,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H385" t="inlineStr"/>
-      <c r="I385" t="inlineStr"/>
       <c r="J385" t="inlineStr">
         <is>
           <t>花彩师优+月季专用介质是专为月季植物配制的营养土介质，容量8L。该介质针对月季的生长需求优化配方，具有良好的透气性和排水性，同时富含月季生长所需的营养成分，能够促进月季根系发育和开花。使用时可直接用于月季盆栽或地栽换土，适合春季换盆或日常追肥添加。注意保持介质湿润但避免积水，月季喜欢阳光充足的环境，日常养护需注意通风和定期施肥。</t>
@@ -18884,8 +18567,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H386" t="inlineStr"/>
-      <c r="I386" t="inlineStr"/>
       <c r="J386" t="inlineStr">
         <is>
           <t>花彩师浓缩营养液花卉型是一款高效浓缩的水溶性肥料，专为花卉植物研发。产品规格为18g，小巧便携。产品富含氮磷钾及微量元素，能够为花卉提供全面均衡的营养支持，促进植株健康生长、花色艳丽。使用时需按照说明稀释后浇灌或叶面喷施，适用于家庭园艺中各类开花植物的追肥需求。建议在生长季节定期施用，避免阳光直射保存。</t>
@@ -18923,7 +18604,6 @@
           <t>其他造型苗</t>
         </is>
       </c>
-      <c r="G387" t="inlineStr"/>
       <c r="H387" t="inlineStr">
         <is>
           <t>造型苗</t>
@@ -18976,8 +18656,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H388" t="inlineStr"/>
-      <c r="I388" t="inlineStr"/>
       <c r="J388" t="inlineStr">
         <is>
           <t>花彩师PH试纸是用于测量土壤酸碱度的专业检测试纸。通过检测土壤pH值，帮助园艺爱好者了解土壤酸碱度状况，为植物选择合适的栽培介质和肥料提供参考依据。适用于阳台花卉、蔬菜种植、室内绿植养护等多种场景。使用方法简便，取少量土壤样品与蒸馏水混合后，将试纸浸入溶液片刻，对照色卡读取pH数值。建议定期检测土壤酸碱度，以确保植物处于适宜的生长环境。</t>
@@ -19332,8 +19010,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H395" t="inlineStr"/>
-      <c r="I395" t="inlineStr"/>
       <c r="J395" t="inlineStr">
         <is>
           <t>花彩师多肉颗粒土是专为多肉植物研发的专用栽培介质，容量5L。该产品采用多孔结构颗粒配方，具有良好的透气性和排水性，能有效防止多肉植物根部积水腐烂。颗粒土含有适量微量元素，ph值适中，适合多肉、仙人掌等肉质植物的栽培换土使用。建议配合透气排水性好的花盆使用，浇水遵循"干透浇透"原则，适合家庭园艺爱好者和专业多肉玩家使用。</t>
@@ -19376,8 +19052,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H396" t="inlineStr"/>
-      <c r="I396" t="inlineStr"/>
       <c r="J396" t="inlineStr">
         <is>
           <t>花彩师蛭石是一种优质的园艺栽培介质材料，规格为5L。蛭石具有质轻、多孔、透气性好、保水保肥能力强的特点。可作为土壤改良剂使用，能有效改善土壤结构，增加土壤通气性，促进根系发育。适用于多肉植物栽培、播种育苗、扦插繁殖以及盆栽基质配制等多种园艺场景。使用时可根据需要与泥炭土、珍珠岩等材料混合搭配。</t>
@@ -19472,8 +19146,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H398" t="inlineStr"/>
-      <c r="I398" t="inlineStr"/>
       <c r="J398" t="inlineStr">
         <is>
           <t>帝罗马国际盆白陶款，经典意大利工艺陶盆，选用优质白陶土高温烧制，质地透气排水良好，适合种植各类花卉、蔬菜及小型灌木。白色陶盆简约大方，易于搭配各种园艺风格，可用于阳台、露台、花园等场景。盆壁厚实耐用，抗寒耐热，适合室内外通用。</t>
@@ -19516,8 +19188,6 @@
           <t>BerryBird</t>
         </is>
       </c>
-      <c r="H399" t="inlineStr"/>
-      <c r="I399" t="inlineStr"/>
       <c r="J399" t="inlineStr">
         <is>
           <t>BerryBird第三代长嘴浇水壶（知更鸟款）是一款专为园艺设计的多肉花卉浇水工具。其独特的加长嘴设计能够轻松深入花盆内部，精准浇水，避免水分溅到叶片上，减少病虫害发生。人体工学手柄设计，握持舒适省力，适合家庭园艺、花卉养护、多肉植物浇水等多种场景使用。</t>
@@ -19560,8 +19230,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H400" t="inlineStr"/>
-      <c r="I400" t="inlineStr"/>
       <c r="J400" t="inlineStr">
         <is>
           <t>帝罗马宽边圆型套盆摩卡13是一款意大利进口品牌花盆，采用优质环保树脂材质制作，具有宽边设计，防磕碰损伤，适合套盆使用。摩卡色系低调优雅，可搭配各种绿植花卉使用。该套盆具有良好的透气性和排水性底孔设计，室内外均适用，便于日常养护管理。</t>
@@ -19651,7 +19319,6 @@
           <t>其他乔木</t>
         </is>
       </c>
-      <c r="G402" t="inlineStr"/>
       <c r="H402" t="inlineStr">
         <is>
           <t>桃树</t>
@@ -19907,9 +19574,6 @@
           <t>水溶肥</t>
         </is>
       </c>
-      <c r="G407" t="inlineStr"/>
-      <c r="H407" t="inlineStr"/>
-      <c r="I407" t="inlineStr"/>
       <c r="J407" t="inlineStr">
         <is>
           <t>水溶性肥料（SL9-45-15）是一种高效的水溶肥产品，氮磷钾配比为9-45-15，以磷元素含量高为特点。高磷配方有利于促进植物花芽分化、开花结果和根系生长，适用于花卉、果蔬等植物的追肥使用。可溶于水，适合通过灌溉系统、叶面喷施等方式施用，使用便捷，吸收效率高。注意按照说明适量使用，避免过量施肥造成浪费或烧根。</t>
@@ -20056,8 +19720,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H410" t="inlineStr"/>
-      <c r="I410" t="inlineStr"/>
       <c r="J410" t="inlineStr">
         <is>
           <t>帝罗马圆型托盘摩卡是一款精致的园艺盆器配件，采用优质陶土材质，具有良好的透气性和排水性，能够有效防止积水，保护植物根系。圆型设计简约大方，摩卡色调沉稳典雅，可与多种风格的花盆搭配使用，适用于室内外各种植物盆栽的配套托盘，提升整体美观度的同时便于日常浇水管理。</t>
@@ -20100,8 +19762,6 @@
           <t>虹越</t>
         </is>
       </c>
-      <c r="H411" t="inlineStr"/>
-      <c r="I411" t="inlineStr"/>
       <c r="J411" t="inlineStr">
         <is>
           <t>虹越定制款印花保暖手套，采用3M保暖材料，有效阻挡冷空气侵入，适合秋冬季节园艺作业使用。掌心防滑纹理设计，抓握园艺工具更稳固。印花工艺美观时尚，一体成型保暖舒适，是园艺爱好者冬季必备的防护手套。</t>
@@ -20248,8 +19908,6 @@
           <t>花逸乐</t>
         </is>
       </c>
-      <c r="H414" t="inlineStr"/>
-      <c r="I414" t="inlineStr"/>
       <c r="J414" t="inlineStr">
         <is>
           <t>花逸乐草花基质是专为草本花卉培育研发的优质土壤介质，容量为60升。基质采用椰糠、泥炭土、珍珠岩等优质原料科学配比而成，具有疏松透气、保水保肥、排水良好的特性。适用于各类一年生和多年生草本花卉的播种、育苗及成株栽培。使用前建议先松土混合均匀，根据植物需求适当添加底肥，注意保持基质湿润但避免积水。简装设计便于存储和搬运，适合家庭园艺爱好者使用。</t>
@@ -20448,8 +20106,6 @@
           <t>马雅</t>
         </is>
       </c>
-      <c r="H418" t="inlineStr"/>
-      <c r="I418" t="inlineStr"/>
       <c r="J418" t="inlineStr">
         <is>
           <t>马雅Maya 92.5兰花专用液肥，容量30ml。这是一款专为兰科植物设计的营养液肥料，配方编号92.5代表其特殊配比。产品为水溶性肥料，易于植物吸收利用。适用于蝴蝶兰、文心兰、石斛兰等各类兰科花卉，可促进兰花生长、开花旺盛。使用时按比例稀释后浇灌或叶面喷施，注意薄肥勤施原则，避免浓度过高造成肥害。适合室内阳台养护兰花使用。</t>
@@ -20492,8 +20148,6 @@
           <t>马雅</t>
         </is>
       </c>
-      <c r="H419" t="inlineStr"/>
-      <c r="I419" t="inlineStr"/>
       <c r="J419" t="inlineStr">
         <is>
           <t>马雅103矿物有机肥果实型是一款专为果树和结果类植物设计的肥料产品，净含量160g。该肥料采用矿物与有机相结合的科学配方，富含果实发育所需的营养元素，能有效促进果实膨大、着色均匀、提升果实品质。适用于家庭园艺中的果树盆栽、果蔬种植等场景。使用时建议按照说明书的用量比例兑水浇施或基施，避免直接接触根部，以防肥害。需放置于阴凉干燥处保存。</t>
@@ -20588,8 +20242,6 @@
           <t>马雅</t>
         </is>
       </c>
-      <c r="H421" t="inlineStr"/>
-      <c r="I421" t="inlineStr"/>
       <c r="J421" t="inlineStr">
         <is>
           <t>马雅Maya92矿物有机肥浓缩营养液（花卉型）是一款专为花卉植物设计的液态有机肥料，容量100ml。产品采用矿物与有机相结合的配方，富含氮磷钾及微量元素，浓缩型设计便于稀释使用。适用于各类室内外观赏花卉，可促进植株生长健壮、开花繁茂。使用时需按比例稀释后浇灌或叶面喷施，生长季每7-14天施用一次。注意薄肥勤施，避免浓度过高造成肥害。</t>
@@ -20996,8 +20648,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H429" t="inlineStr"/>
-      <c r="I429" t="inlineStr"/>
       <c r="J429" t="inlineStr">
         <is>
           <t>花彩师园艺不锈钢三指叉是一款专业园艺种植工具，采用优质不锈钢材质制成，具有耐腐蚀、耐磨损、坚固耐用的特点。三指叉设计符合人体工程学，便于握持操作，适用于花园、庭院、蔬菜种植等场景。主要功能包括翻土、松土、挖坑、移栽幼苗、疏松土壤等，能够有效改善土壤透气性和排水性。适用于各种土壤类型，是家庭园艺和专业种植的实用帮手。</t>
@@ -21139,7 +20789,6 @@
           <t>其他灌木</t>
         </is>
       </c>
-      <c r="G432" t="inlineStr"/>
       <c r="H432" t="inlineStr">
         <is>
           <t>灌木</t>
@@ -21244,8 +20893,6 @@
           <t>维特</t>
         </is>
       </c>
-      <c r="H434" t="inlineStr"/>
-      <c r="I434" t="inlineStr"/>
       <c r="J434" t="inlineStr">
         <is>
           <t>维特0-25泥炭土是一种优质园艺栽培介质，规格250L，颗粒度0-25mm，适合各类花卉、蔬菜及种苗培育使用。泥炭土具有良好的透气性、保水性和保肥能力，pH值适中，富含天然有机质，可改善土壤结构，促进根系发育。适用于盆栽花卉、蔬菜育苗、家庭园艺等多种场景，是园艺爱好者常用的基础栽培介质。使用时可与其他介质如珍珠岩、椰糠等混合调配，以达到最佳栽培效果。</t>
@@ -21340,8 +20987,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H436" t="inlineStr"/>
-      <c r="I436" t="inlineStr"/>
       <c r="J436" t="inlineStr">
         <is>
           <t>稻壳炭是采用优质稻壳经高温炭化而成的土壤改良材料，呈碱性，富含钾元素和多种微量元素。具有疏松土壤、增强透气性、调节土壤酸碱度、保水保肥等功效。适用于多肉植物栽培、土壤酸化改良、育苗介质配制等。使用时可与泥炭土、椰糠等基质混合搭配，比例通常为10%-20%。14L包装适合家庭园艺使用。</t>
@@ -21493,7 +21138,6 @@
           <t>绣球</t>
         </is>
       </c>
-      <c r="I439" t="inlineStr"/>
       <c r="J439" t="inlineStr">
         <is>
           <t>大花绣球是虎耳草科绣球属的落叶灌木，花型硕大丰满、花色丰富艳丽，具有极高的观赏价值。该品种专为展会场景培育，植株健壮、花期整齐、观赏效果佳，适合用于园林景观布置、花境打造或大型展览装饰。喜半阴环境，耐寒性较好，适宜种植于疏松肥沃、排水良好的土壤中。展会专用绣球经过特殊栽培管理，可确保在特定时间达到最佳观赏状态，是各类花卉展会、园艺展览的理想材料。</t>
@@ -21771,14 +21415,46 @@
           <t>虹安果树 蓝莓“一号蓝莓”</t>
         </is>
       </c>
-      <c r="C445" t="inlineStr"/>
-      <c r="D445" t="inlineStr"/>
-      <c r="E445" t="inlineStr"/>
-      <c r="F445" t="inlineStr"/>
-      <c r="G445" t="inlineStr"/>
-      <c r="H445" t="inlineStr"/>
-      <c r="I445" t="inlineStr"/>
-      <c r="J445" t="inlineStr"/>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>植物</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>种苗苗木</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>灌木</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>蓝莓</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>虹安果树</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>蓝莓</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>一号蓝莓</t>
+        </is>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>蓝莓是多年生灌木果树，株高1-3米，喜酸性土壤（pH值4.5-5.5），喜阳光充足、通风良好的环境。果实为浆果，富含花青素和维生素，口感酸甜可口。适合庭院种植或盆栽观赏，结果期可品尝新鲜蓝莓。种植时需保持土壤湿润但忌积水，冬季需适当修剪枝条以促进来年结果。</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -21808,27 +21484,27 @@
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>杜鹃</t>
+          <t>蓝莓</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>虹越植物</t>
+          <t>虹安果树</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>杜鹃</t>
+          <t>蓝莓</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
         <is>
-          <t>赤焰</t>
+          <t>一号蓝莓</t>
         </is>
       </c>
       <c r="J446" t="inlineStr">
         <is>
-          <t>落叶杜鹃“赤焰”是一款观赏性较高的灌木花卉品种，春季开花时花色鲜艳夺目，花朵繁密，具有较高的庭院观赏价值。该品种适应性较强，喜酸性疏松土壤，耐寒性较好，适合种植于庭院、花园或盆栽观赏。养护时需注意保持土壤湿润，避免积水，并适当进行修剪以维持良好株型。</t>
+          <t>蓝莓是多年生灌木果树，果实呈蓝色，富含花青素，营养价值极高。'一号蓝莓'属于早熟品种，适应性强，适合庭院盆栽或地栽种植。喜酸性土壤（pH值4.5-5.5），需充足阳光，浇水保持土壤湿润但忌积水。定植时施足基肥，生长期补充磷钾肥，注意修剪枯枝弱枝。果实可直接食用，也可制作果酱、果汁等，具有明目、抗氧化功效。</t>
         </is>
       </c>
     </row>
@@ -21999,14 +21675,46 @@
           <t>虹安铁线莲 莎拉伊丽莎白</t>
         </is>
       </c>
-      <c r="C450" t="inlineStr"/>
-      <c r="D450" t="inlineStr"/>
-      <c r="E450" t="inlineStr"/>
-      <c r="F450" t="inlineStr"/>
-      <c r="G450" t="inlineStr"/>
-      <c r="H450" t="inlineStr"/>
-      <c r="I450" t="inlineStr"/>
-      <c r="J450" t="inlineStr"/>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>植物</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>种苗苗木</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>藤本</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>铁线莲</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>虹安</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>铁线莲</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>莎拉伊丽莎白</t>
+        </is>
+      </c>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>铁线莲莎拉伊丽莎白是一款大花型藤本植物，花朵呈莲座状排列，花瓣数多，花色通常为淡粉至白色，边缘带有波浪状褶皱，极具观赏价值。该品种攀援能力强，适合用于花架、拱门、墙面等立体绿化装饰。喜阳光充足但忌强光直射，耐寒性较强，适宜在疏松肥沃、排水良好的土壤中生长。春季萌芽前需适当修剪枯枝败叶，保持通风透光，可促进花芽分化与开花。</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -22021,34 +21729,42 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>非植</t>
+          <t>植物</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>肥</t>
+          <t>种苗苗木</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>通用肥</t>
+          <t>藤本</t>
         </is>
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>水溶肥</t>
+          <t>铁线莲</t>
         </is>
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>马雅Maya</t>
-        </is>
-      </c>
-      <c r="H451" t="inlineStr"/>
-      <c r="I451" t="inlineStr"/>
+          <t>虹安</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>铁线莲</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>莎拉伊丽莎白</t>
+        </is>
+      </c>
       <c r="J451" t="inlineStr">
         <is>
-          <t>马雅Maya93浓缩营养液（果蔬型）是一款专为果蔬类植物设计的液态肥料，产品规格183ml。该产品采用浓缩配方，便于稀释使用，能为果蔬提供均衡的氮磷钾及微量元素，促进植株健康生长和果实发育。适用于家庭菜园、果蔬盆栽等场景，使用时需按照说明比例稀释后浇灌或叶面喷施。建议在植物生长期和结果期定期施用，避免过量使用造成肥害。阴凉干燥处保存，稀释后的肥液应尽快用完。</t>
+          <t>虹安品牌推出的铁线莲品种，莎拉伊丽莎白是铁线莲中的优质品种。铁线莲为多年生藤本植物，茎细长柔软，需攀援支撑生长，以花大色艳、品种繁多著称，被誉为"藤本皇后"。该品种具有较强的适应性和观赏性，花朵大而艳丽，适合用于花架、廊架、拱门、围栏等垂直绿化，也可盆栽种植。喜阳光充足、通风良好的环境，忌积水，土壤宜疏松肥沃、排水良好。耐寒性较好，冬季休眠时可适当修剪枯枝。</t>
         </is>
       </c>
     </row>
@@ -22088,8 +21804,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H452" t="inlineStr"/>
-      <c r="I452" t="inlineStr"/>
       <c r="J452" t="inlineStr">
         <is>
           <t>帝罗马经典宽边高圆型盆摩卡22是一款高品质园艺花盆，采用优质陶瓷材质，摩卡色配色经典大方。宽边设计方便搬运，圆型结构适合多种植物栽培，22厘米口径适合中小型植物种植。该盆具有良好的透气性和排水性，适合家庭园艺、阳台种植使用，可种植多肉、绿植、花卉等多种植物，兼具实用性与装饰性。</t>
@@ -22132,8 +21846,6 @@
           <t>ARTSTONE</t>
         </is>
       </c>
-      <c r="H453" t="inlineStr"/>
-      <c r="I453" t="inlineStr"/>
       <c r="J453" t="inlineStr">
         <is>
           <t>ARTSTONE克莱尔圆型套盆，灰色设计，简约现代风格。套盆设计可用于内盆套入或装饰性套放，适合各类绿植、花卉盆栽使用。品牌盆具做工精细，材质耐用，适合家庭园艺及室内装饰场景。</t>
@@ -22176,8 +21888,6 @@
           <t>马雅</t>
         </is>
       </c>
-      <c r="H454" t="inlineStr"/>
-      <c r="I454" t="inlineStr"/>
       <c r="J454" t="inlineStr">
         <is>
           <t>马雅Maya种球植物专用液肥，容量30ml，专为种球类植物（如郁金香、朱顶红、百合、风信子等）设计的专用肥料。产品富含促进种球发育和开花的营养成分，有助于提高种球发芽率和开花质量。适用于鳞茎、球茎、块茎类植物的种植养护。使用时需按说明稀释后浇灌，避免直接接触种球。建议在种球种植期和生长期使用，每隔7-14天施用一次，需遮光保存于阴凉处。</t>
@@ -22220,8 +21930,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H455" t="inlineStr"/>
-      <c r="I455" t="inlineStr"/>
       <c r="J455" t="inlineStr">
         <is>
           <t>花彩师园艺骨粉颗粒是一款高品质有机肥料，主要成分为动物骨骼研磨而成的骨粉，富含磷、钙等营养元素，能促进植物根系发育和花果生长。颗粒状设计便于均匀撒施，适用于多肉、花卉、果树等植物的底肥或追肥使用。建议沿植株周围穴施后覆土，每季度使用1-2次，配合浇水效果更佳。注意避免直接接触根系，以防肥害。</t>
@@ -22264,8 +21972,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H456" t="inlineStr"/>
-      <c r="I456" t="inlineStr"/>
       <c r="J456" t="inlineStr">
         <is>
           <t>花彩师园艺发酵松鳞是经过发酵处理的松树树皮介质，颗粒规格9-12mm，适合作为土壤改良材料使用。能有效改善土壤排水性和透气性，调节土壤酸碱度，适宜种植兰花、杜鹃、栀子花等喜酸性植物。发酵后的松鳞减少了对新栽植物根系的刺激，可直接拌入营养土中使用，也可作为铺面材料减少水分蒸发。每包20L，适合家庭园艺栽培使用。</t>
@@ -22464,8 +22170,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H460" t="inlineStr"/>
-      <c r="I460" t="inlineStr"/>
       <c r="J460" t="inlineStr">
         <is>
           <t>帝罗马圆型托盘白陶是一款高品质陶瓷材质的圆形托盘，采用经典白色设计，简约大方。托盘主要用于承接花盆底部滴漏的水分，有效保护桌面和地面不受水渍污染，同时增加盆栽整体的装饰效果。适用于各种室内外盆栽配套使用，是阳台花园、客厅、办公室等场所的理想选择。</t>
@@ -22508,8 +22212,6 @@
           <t>嘉伯瑞</t>
         </is>
       </c>
-      <c r="H461" t="inlineStr"/>
-      <c r="I461" t="inlineStr"/>
       <c r="J461" t="inlineStr">
         <is>
           <t>嘉伯瑞是知名的花盆品牌，以其优质的园艺盆器产品著称。嘉伯瑞品牌盆具采用高品质材料制作，具有良好的透气性和排水性，适合各类室内外观赏植物栽培使用。产品设计简约大方，线条流畅，兼具实用性与装饰性，能够有效提升植物的观赏价值。品牌产品线丰富，涵盖多种尺寸和款式，可满足不同消费者的园艺需求，是家庭园艺和商业景观布置的理想选择。</t>
@@ -22552,8 +22254,6 @@
           <t>ARTSTONE</t>
         </is>
       </c>
-      <c r="H462" t="inlineStr"/>
-      <c r="I462" t="inlineStr"/>
       <c r="J462" t="inlineStr">
         <is>
           <t>ARTSTONE菲奥纳圆钵是一款简约风格的陶瓷花盆，采用优质陶土材质，透气性好，适合多种室内外植物种植。圆钵设计经典大方，白色釉面清新雅致，可搭配各种绿植和多肉植物。口径约31cm，适合种植中小型植物，是家庭园艺和办公场所的理想选择。盆底设有排水孔设计，可有效防止积水，保护植物根系健康。</t>
@@ -22752,8 +22452,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H466" t="inlineStr"/>
-      <c r="I466" t="inlineStr"/>
       <c r="J466" t="inlineStr">
         <is>
           <t>帝罗马圆型托盘摩卡29是一款高质量园艺盆器配件，采用优质材料制作，耐用美观。圆型设计搭配摩卡色，简约大方，适合搭配各类帝罗马花盆使用。托盘可有效收集多余水分，防止浇水时弄湿地面，同时保持根部湿度，适用于室内外各种园艺场景，如阳台、庭院、花园等。</t>
@@ -22848,8 +22546,6 @@
           <t>维特</t>
         </is>
       </c>
-      <c r="H468" t="inlineStr"/>
-      <c r="I468" t="inlineStr"/>
       <c r="J468" t="inlineStr">
         <is>
           <t>维特0-10纯泥炭是一种高品质园艺栽培介质，采用纯天然泥炭藓经加工而成，pH值适中，透气性好，保水性强，适用于各种花卉、蔬菜、苗木的栽培种植。该产品为大容量包装（Big Bale），适合规模化种植使用。纯泥炭可单独使用或与其他介质混合使用，是园艺种植的理想基质材料。</t>
@@ -22892,8 +22588,6 @@
           <t>成都神龙</t>
         </is>
       </c>
-      <c r="H469" t="inlineStr"/>
-      <c r="I469" t="inlineStr"/>
       <c r="J469" t="inlineStr">
         <is>
           <t>成都神龙月季通用基质，容量60L，专为月季生长配制的高品质土壤介质。选用优质泥炭、椰糠、珍珠岩等原料科学配比，具有良好的透气性、保水性和排水性，酸碱度适宜月季生长。可直接用于月季盆栽、地栽换盆或土壤改良，能有效促进月季根系发育和开花表现。</t>
@@ -22936,8 +22630,6 @@
           <t>ARTSTONE</t>
         </is>
       </c>
-      <c r="H470" t="inlineStr"/>
-      <c r="I470" t="inlineStr"/>
       <c r="J470" t="inlineStr">
         <is>
           <t>ARTSTONE艾拉花槽是一款简约现代的种植容器，采用优质树脂材质制成，具有良好的耐候性和耐用性。55厘米的长度适合阳台、露台或室内空间使用，可种植各类草本植物、蔬菜或小型灌木。黑色设计简约时尚，易于搭配各种园艺风格。花槽设计通常配有排水孔或排水层，可有效防止积水，保护植物根系健康。适合家庭园艺、庭院装饰或商业景观应用。</t>
@@ -22980,8 +22672,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H471" t="inlineStr"/>
-      <c r="I471" t="inlineStr"/>
       <c r="J471" t="inlineStr">
         <is>
           <t>花彩师有机肥料（羊粪肥）是一种纯天然有机肥料，选用优质羊粪为原料，经过充分腐熟发酵工艺加工而成。富含有机质和植物生长所需的氮、磷、钾等营养元素，肥效温和持久，不易烧根。适用于各类花卉、蔬菜、果树及家庭园艺植物的基肥和追肥使用。改良土壤结构，增加土壤透气性和保水性，促进植物健康生长。适合用于家庭园艺、蔬菜种植、花卉栽培等场景。包装规格为2.8KG，适合家庭日常使用。</t>
@@ -23185,7 +22875,6 @@
           <t>紫荆</t>
         </is>
       </c>
-      <c r="I475" t="inlineStr"/>
       <c r="J475" t="inlineStr">
         <is>
           <t>虹安进口紫荆是豆科紫荆属的落叶灌木，原产中国，花朵紫红色或粉红色，簇生于枝干上，先花后叶，观赏价值高。喜阳光充足、耐寒耐旱，适应性强，适合庭院、公园或道路绿化种植。春季开花时满树繁花，是优良的观赏苗木。</t>
@@ -23280,8 +22969,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H477" t="inlineStr"/>
-      <c r="I477" t="inlineStr"/>
       <c r="J477" t="inlineStr">
         <is>
           <t>花彩师陶盆通用介质是一款专为陶盆设计的通用型种植介质，容量8L。该介质经过科学配比，具有良好的透气性、保水性和排水性，适合多种花卉、蔬菜的盆栽种植。介质结构疏松，有利于根系呼吸和生长，适用于家庭园艺、花卉栽培等多种场景。使用时可根据植物需求适量添加肥料，为植物提供均衡的营养支持。</t>
@@ -23532,8 +23219,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H482" t="inlineStr"/>
-      <c r="I482" t="inlineStr"/>
       <c r="J482" t="inlineStr">
         <is>
           <t>花彩师发酵松鳞是一种优质的园艺介质材料，以松树皮为原料经过发酵处理制成。颗粒规格5-20mm，适用于改善土壤透气性和排水性。可作为兰花、杜鹃、茶花等喜酸植物的栽培介质，也可混入营养土中使用，提升土壤结构。发酵松鳞富含有机质，PH值呈酸性，适合南方花卉栽培。使用时建议与其他介质混合搭配，避免单独使用量过大。</t>
@@ -23628,8 +23313,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H484" t="inlineStr"/>
-      <c r="I484" t="inlineStr"/>
       <c r="J484" t="inlineStr">
         <is>
           <t>帝罗马宽边圆型套盆摩卡是一款经典的室内外园艺盆器，采用优质陶瓷材质制成，具有宽边设计方便搬动和换盆。套盆设计可有效防止水分渗漏，保护室内地面清洁，同时具有一定的保湿作用。摩卡色系低调雅致，适合各种家居风格和庭院装饰。该套盆适用于种植多肉植物、小型花卉或作为观赏盆栽的装饰盆使用，清洗方便，经久耐用。</t>
@@ -23776,8 +23459,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H487" t="inlineStr"/>
-      <c r="I487" t="inlineStr"/>
       <c r="J487" t="inlineStr">
         <is>
           <t>花彩师珍珠岩是一种优质的园艺改良材料，由火山岩经高温膨胀制成。它具有多孔、轻质、透气排水性好的特点，能有效改善土壤结构，防止盆土板结，增加根系呼吸空间。本品颗粒均匀（5L规格），适合用于多肉植物、兰花、播种育苗等对排水透气要求高的栽培场景，也可与泥炭土、椰糠等介质混合使用，提升整体排水性能。使用时建议与其他介质混合配比，比例约为10%-30%。</t>
@@ -23924,8 +23605,6 @@
           <t>马雅</t>
         </is>
       </c>
-      <c r="H490" t="inlineStr"/>
-      <c r="I490" t="inlineStr"/>
       <c r="J490" t="inlineStr">
         <is>
           <t>马雅Maya91.2秋海棠专用水溶肥，容量500ml，是一款专为秋海棠植物研发的液体肥料。该产品针对秋海棠的生长需求科学配比营养元素，可促进植株健壮生长和繁花绽放。适用于各类秋海棠品种的日常养护，使用时按比例稀释后浇灌或叶面喷施。肥料溶解性好，吸收率高，建议在生长期每7-14天施用一次，注意薄肥勤施避免肥害。</t>
@@ -24072,8 +23751,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H493" t="inlineStr"/>
-      <c r="I493" t="inlineStr"/>
       <c r="J493" t="inlineStr">
         <is>
           <t>花彩师园艺发酵松鳞是经过充分发酵腐熟的松树皮产品，规格为精选M（12-18mm），容量20L。松鳞质地轻盈、透气性好、保水性强，富含天然有机质和腐殖酸，可改善土壤结构，增加土壤通气性和排水性。适用于兰花、君子兰、蝴蝶兰等肉质根花卉的栽培介质，也可作为地被植物覆盖物或土壤改良剂使用，能有效调节土壤酸碱度，促进植物根系生长发育。</t>
@@ -24168,8 +23845,6 @@
           <t>马雅</t>
         </is>
       </c>
-      <c r="H495" t="inlineStr"/>
-      <c r="I495" t="inlineStr"/>
       <c r="J495" t="inlineStr">
         <is>
           <t>马雅Maya93.1多肉植物专用肥料，专为多肉植物研发的液态肥料，30ml小包装便于控制用量。富含氮磷钾及微量元素，配比适合多肉植物生长需求，可促进多肉叶片肥厚、色泽艳丽。使用时需稀释后浇灌，避免直接接触叶片，薄肥勤施原则，生长期每2-4周施用一次，休眠期停止施肥。适用于各类多肉植物如景天科、十二卷属等。</t>
@@ -24321,7 +23996,6 @@
           <t>铁线莲</t>
         </is>
       </c>
-      <c r="I498" t="inlineStr"/>
       <c r="J498" t="inlineStr">
         <is>
           <t>铁线莲是毛茛科铁线莲属的藤本花卉，被誉为“藤本皇后”。其花型优美、花色丰富，有单瓣和重瓣之分，花期较长。虹安品牌的铁线莲盆栽，经过专业培育，植株健壮，适应性强。适合种植于庭院围栏、阳台花架、墙面等处，可做花墙、花柱装饰。喜阳光充足、通风良好的环境，耐寒性较强，浇水遵循见干见湿原则，生长期适当施肥促进开花。</t>
@@ -24364,8 +24038,6 @@
           <t>云柱</t>
         </is>
       </c>
-      <c r="H499" t="inlineStr"/>
-      <c r="I499" t="inlineStr"/>
       <c r="J499" t="inlineStr">
         <is>
           <t>云柱系列花盆，25cm尺寸规格，采用烟煤色配色方案，简约现代设计风格。适用于家庭园艺种植，可种植各类草本花卉、多肉植物或小型绿植。烟煤色沉稳大气，易于搭配各种家居风格和植物类型。盆器具有良好的透气性和排水性设计，适合室内外使用。</t>
@@ -24408,8 +24080,6 @@
           <t>畾森</t>
         </is>
       </c>
-      <c r="H500" t="inlineStr"/>
-      <c r="I500" t="inlineStr"/>
       <c r="J500" t="inlineStr">
         <is>
           <t>畾森花和野菜培养土是一款通用型园艺营养土，添加腐熟有机质和珍珠岩等透气材料，质地疏松透气、保水保肥能力强。适用于家庭园艺中花卉植物（如月季、绣球、菊花等）以及野菜蔬菜（如菠菜、香菜、小白菜等）的栽培种植。可直接用于盆栽或地栽定植，使用时根据植物种类适量添加底肥，注意保持土壤湿润但避免积水。</t>
@@ -24504,8 +24174,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H502" t="inlineStr"/>
-      <c r="I502" t="inlineStr"/>
       <c r="J502" t="inlineStr">
         <is>
           <t>花彩师鹿沼土是一种高品质火山灰介质，呈弱酸性，颗粒细腻，透气性和排水性优异。细粒规格适合多肉、兰花、茶花、杜鹃等喜酸性植物栽培使用。可单独使用或与其他介质混合，能有效改善土壤结构，调节酸碱度，促进根系发育。适用于播种、扦插、成株养护等多种园艺场景。建议根据植物需求适量使用，避免积水。</t>
@@ -24548,8 +24216,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H503" t="inlineStr"/>
-      <c r="I503" t="inlineStr"/>
       <c r="J503" t="inlineStr">
         <is>
           <t>帝罗马国际盆白陶27是一款高品质陶瓷花盆，采用白色陶瓷材质制作，外观简洁大方。27可能指代盆的尺寸规格（具体尺寸需参考实际产品参数）。陶瓷材质具有良好的透气性和排水性，适合种植各类花卉和绿植。帝罗马品牌以精美的园艺盆器著称，产品设计注重美观与实用性结合，是室内外装饰和园艺种植的理想选择。</t>
@@ -24592,8 +24258,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H504" t="inlineStr"/>
-      <c r="I504" t="inlineStr"/>
       <c r="J504" t="inlineStr">
         <is>
           <t>帝罗马科诺高圆型盆摩卡16寸，采用优质环保树脂材质，具有良好的透气性和排水性，设计简约时尚，摩卡色系自然温馨。圆型盆设计适合种植各类花卉绿植，如月季、绣球、天竺葵等。盆体坚固耐用，抗紫外线，耐高低温和腐蚀，适合室内外使用。16寸规格可满足中大型植物的种植需求，是家庭园艺的理想选择。</t>
@@ -24740,8 +24404,6 @@
           <t>马雅</t>
         </is>
       </c>
-      <c r="H507" t="inlineStr"/>
-      <c r="I507" t="inlineStr"/>
       <c r="J507" t="inlineStr">
         <is>
           <t>马雅Maya90液体通用型肥料，容量500ml。是一种适用于各类植物的通用液体肥料，可广泛用于花卉、蔬菜、果树等植物的施肥。产品以液体形式存在，易于稀释和使用，能为植物提供均衡的营养支持，促进植株健康生长。使用时需按照说明书的稀释比例兑水后施用，避免浓度过高造成肥害。建议作为日常追肥使用，配合浇水进行，适用于家庭园艺各类植物的养分补充。</t>
@@ -25019,14 +24681,46 @@
           <t>虹越植物 落叶杜鹃“流光溢彩”</t>
         </is>
       </c>
-      <c r="C513" t="inlineStr"/>
-      <c r="D513" t="inlineStr"/>
-      <c r="E513" t="inlineStr"/>
-      <c r="F513" t="inlineStr"/>
-      <c r="G513" t="inlineStr"/>
-      <c r="H513" t="inlineStr"/>
-      <c r="I513" t="inlineStr"/>
-      <c r="J513" t="inlineStr"/>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>植物</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>种苗苗木</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>灌木</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>杜鹃</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>虹越</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>杜鹃</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>流光溢彩</t>
+        </is>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>落叶杜鹃"流光溢彩"是虹越推出的观赏型杜鹃花品种。植株为落叶灌木，秋季叶片变为鲜艳的橙红色，具有较高观赏价值。花朵通常为重瓣类型，花色艳丽夺目，呈流光溢彩的渐变效果。适合庭院孤植或群植，也可作为花境配置材料。喜酸性、疏松排水良好的土壤，喜半阴环境，怕强光暴晒。冬季落叶休眠，早春萌芽前可进行适当修剪，促发新枝。耐寒性较好，适合我国大部分地区栽培。</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -25051,32 +24745,32 @@
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>藤本</t>
+          <t>灌木</t>
         </is>
       </c>
       <c r="F514" t="inlineStr">
         <is>
-          <t>铁线莲</t>
+          <t>杜鹃</t>
         </is>
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>虹越</t>
+          <t>虹越植物</t>
         </is>
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>铁线莲</t>
+          <t>杜鹃</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
         <is>
-          <t>昼天使/桃万重</t>
+          <t>流光溢彩</t>
         </is>
       </c>
       <c r="J514" t="inlineStr">
         <is>
-          <t>铁线莲是著名藤本花卉，被誉为"藤本皇后"，花量丰富、花型优美。昼天使和桃万重是两个不同品种的铁线莲，花朵各具特色，颜色艳丽。适合用于阳台、庭院花架、栅栏、廊架等垂直绿化场景。喜阳光充足但忌暴晒，适宜种植在排水良好、疏松肥沃的土壤中。耐寒性较强，但夏季需注意适当遮荫降温。种植时保持土壤微润即可，避免积水导致根系腐烂。花期较长，观赏价值高。</t>
+          <t>落叶杜鹃“流光溢彩”是虹越植物推出的优质种苗产品，属于杜鹃花科落叶灌木。该品种花色鲜艳夺目，花型优美，具有较高的观赏价值。春季开花，花量大，色彩绚丽，适合庭院种植或盆栽观赏。喜酸性、疏松肥沃的土壤，喜半阴环境，适应性较强，是园林绿化和家庭园艺的优良选择。</t>
         </is>
       </c>
     </row>
@@ -25121,7 +24815,6 @@
           <t>蓝莓</t>
         </is>
       </c>
-      <c r="I515" t="inlineStr"/>
       <c r="J515" t="inlineStr">
         <is>
           <t>虹安果树品牌的蓝莓种苗，属于灌木类果树苗木。蓝莓为多年生灌木，果实富含花青素，具有较高的营养价值和食用价值。适合家庭园艺种植，需选择酸性土壤（pH值4.5-5.5），喜阳光充足、通风良好的环境，浇水应保持土壤湿润但避免积水。蓝莓M规格表示中等大小的苗木，适合庭院种植或盆栽观赏，既可作为果树栽培也可作为观赏植物。</t>
@@ -25169,7 +24862,6 @@
           <t>厚皮香</t>
         </is>
       </c>
-      <c r="I516" t="inlineStr"/>
       <c r="J516" t="inlineStr">
         <is>
           <t>厚皮香（学名：Ternstroemia gymnanthera），山茶科厚皮香属常绿灌木或小乔木，原产中国南方各省。叶片革质、倒卵形，浓绿有光泽，质感厚实。耐阴性强，耐寒性较好，适应范围广。生长缓慢，寿命长，适合庭院种植、林下地被或作绿篱使用。花小白色，果实红色，观赏价值较高。</t>
@@ -25207,7 +24899,6 @@
           <t>玉簪</t>
         </is>
       </c>
-      <c r="G517" t="inlineStr"/>
       <c r="H517" t="inlineStr">
         <is>
           <t>玉簪</t>
@@ -25416,8 +25107,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H521" t="inlineStr"/>
-      <c r="I521" t="inlineStr"/>
       <c r="J521" t="inlineStr">
         <is>
           <t>轻石是一种优质的园艺改良材料，由火山喷发形成的玻璃质岩石经处理而成。该产品具有良好的透气性、排水性和保水性，可有效改善土壤结构，防止盆土板结，增加基质的疏松度。适用于多肉植物、兰花、观叶植物等各类园艺植物的栽培介质配制，也可作为铺面材料使用。5L规格适中，适合家庭园艺盆栽使用。</t>
@@ -25616,8 +25305,6 @@
           <t>可利鲜Chrysal</t>
         </is>
       </c>
-      <c r="H525" t="inlineStr"/>
-      <c r="I525" t="inlineStr"/>
       <c r="J525" t="inlineStr">
         <is>
           <t>可利鲜Chrysal鲜花营养保鲜剂加强型是一款专为鲜切花设计的营养补充剂，容量250ml。本品含有鲜花所需的糖分、杀菌成分和酸度调节剂，能有效延长鲜花的观赏期，保持花枝水分平衡，抑制细菌滋生，防止花朵过早凋谢。使用时按说明比例稀释后插入花瓶即可，适用于各种鲜切花如玫瑰、百合、康乃馨等的日常养护和保鲜。</t>
@@ -25655,9 +25342,6 @@
           <t>其他改良材料</t>
         </is>
       </c>
-      <c r="G526" t="inlineStr"/>
-      <c r="H526" t="inlineStr"/>
-      <c r="I526" t="inlineStr"/>
       <c r="J526" t="inlineStr">
         <is>
           <t>稻壳碳是园艺中常用的土壤改良材料，以稻壳为原料经过高温碳化处理而成。主要用于调节土壤酸碱度、增加透气性和改善排水性能。适合用于多肉植物、花卉、蔬菜等种植基质的配制，可以与泥炭土、椰糠等混合使用，有效改善土壤结构。稻壳碳呈弱碱性，特别适合用于改良酸性土壤或配制适合喜碱性植物的栽培介质。其碳化特性还能帮助土壤保持良好的通气状态，促进根系健康生长。</t>
@@ -25804,8 +25488,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H529" t="inlineStr"/>
-      <c r="I529" t="inlineStr"/>
       <c r="J529" t="inlineStr">
         <is>
           <t>花彩师天南星科专业介质是专为天南星科植物（如绿萝、龟背竹、红掌、白掌、滴水观音等）配制的专用栽培介质。容量为25升，适合家庭园艺种植。介质配方根据天南星科植物根系特点设计，透气性和保水性平衡，有助于根系健康生长，促进植株茂盛生长。使用时可直接用于换盆或拌入现有土壤中改善土质。</t>
@@ -25900,8 +25582,6 @@
           <t>ARTSTONE</t>
         </is>
       </c>
-      <c r="H531" t="inlineStr"/>
-      <c r="I531" t="inlineStr"/>
       <c r="J531" t="inlineStr">
         <is>
           <t>ARTSTONE菲奥纳圆钵25粉色是一款时尚美观的园艺花盆，采用优质树脂材质，轻便耐用又兼具装饰性。圆钵造型线条流畅，粉色清新淡雅，适合家居阳台、花园或室内绿植盆栽使用。可搭配多种风格植物，提升空间美感。</t>
@@ -26100,8 +25780,6 @@
           <t>虹越</t>
         </is>
       </c>
-      <c r="H535" t="inlineStr"/>
-      <c r="I535" t="inlineStr"/>
       <c r="J535" t="inlineStr">
         <is>
           <t>虹越水溶性肥料20-10-20是一款高效全水溶性肥料，氮磷钾比例为20-10-20，配方均衡，适合植物生长期间使用。可完全溶解于水，通过灌溉系统或叶面喷施方式施用，快速补充植物所需营养元素。使用便捷，适用于各种花卉、蔬菜、果树等植物的追肥需求。注意遵循推荐用量，避免过量施用。</t>
@@ -26139,7 +25817,6 @@
           <t>冬青</t>
         </is>
       </c>
-      <c r="G536" t="inlineStr"/>
       <c r="H536" t="inlineStr">
         <is>
           <t>冬青</t>
@@ -26343,7 +26020,6 @@
           <t>杜鹃</t>
         </is>
       </c>
-      <c r="G540" t="inlineStr"/>
       <c r="H540" t="inlineStr">
         <is>
           <t>杜鹃</t>
@@ -26448,8 +26124,6 @@
           <t>ARTSTONE</t>
         </is>
       </c>
-      <c r="H542" t="inlineStr"/>
-      <c r="I542" t="inlineStr"/>
       <c r="J542" t="inlineStr">
         <is>
           <t>ARTSTONE菲奥纳圆钵是一款采用优质树脂材质制作的室内外通用花盆，设计为圆形钵状，口径25cm，适合种植各类中小型植物。紫色釉面典雅大方，表面光滑易清洁，透气性和排水性良好。适用于多肉植物、小型草本花卉、迷你盆栽等。可用于家居装饰、办公室绿植摆放、阳台园艺等多种场景，兼具实用性与装饰性。</t>
@@ -26492,8 +26166,6 @@
           <t>马雅</t>
         </is>
       </c>
-      <c r="H543" t="inlineStr"/>
-      <c r="I543" t="inlineStr"/>
       <c r="J543" t="inlineStr">
         <is>
           <t>马雅Maya93液体果蔬型肥料，容量500ml，是一种专为果蔬植物设计的液态水溶肥料。产品采用科学配比，富含氮磷钾及微量元素，速溶性强，适合浇灌和叶面喷施。能有效促进果蔬生长，提高果实品质和产量，增强植株抗病能力。适用于家庭菜园、果树及阳台种植的各类果蔬作物。使用时按比例稀释，遵循薄肥勤施的原则，避免烧根。</t>
@@ -26536,8 +26208,6 @@
           <t>马雅Maya</t>
         </is>
       </c>
-      <c r="H544" t="inlineStr"/>
-      <c r="I544" t="inlineStr"/>
       <c r="J544" t="inlineStr">
         <is>
           <t>马雅园艺浓缩营养液是一款专为多肉植物研发的液态肥料，采用科学配比的高浓度配方，富含多肉生长所需的氮磷钾及微量元素。使用时需按比例稀释，通过浇水方式施用，为多肉提供均衡营养，促进植株健康生长，增强色彩表现力和抗逆性。500ml定量罐装便于精准控制用量，适合家庭多肉盆栽养护使用。</t>
@@ -26580,8 +26250,6 @@
           <t>成都神龙</t>
         </is>
       </c>
-      <c r="H545" t="inlineStr"/>
-      <c r="I545" t="inlineStr"/>
       <c r="J545" t="inlineStr">
         <is>
           <t>成都神龙花涧小椿日和20L是一款家庭园艺专用营养土，容量为20升。产品添加了泥炭、椰糠、有机质等成分，疏松透气、保水保肥，适合种植各类草本花卉、蔬菜、果树及小型灌木。可直接用于盆栽、地栽或改良土壤，使用时根据植物需求适当混合园土即可。注意储存于阴凉干燥处，避免受潮结块。</t>
@@ -26728,8 +26396,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H548" t="inlineStr"/>
-      <c r="I548" t="inlineStr"/>
       <c r="J548" t="inlineStr">
         <is>
           <t>花彩师水溶肥（花卉型）是一款专为花卉植物研发的高浓度水溶性肥料，净含量450g。采用科学配比，富含氮磷钾及微量元素，能快速溶解于水被植物吸收利用。适用于各类室内外观赏花卉，如月季、绣球、栀子花等的追肥使用。建议按1:500-1000比例稀释后浇灌或叶面喷施，生长季每7-14天施用一次。使用前摇匀，避免阳光直射存放。肥效迅速、使用便捷，是家庭园艺养花的理想选择。</t>
@@ -26824,8 +26490,6 @@
           <t>马雅</t>
         </is>
       </c>
-      <c r="H550" t="inlineStr"/>
-      <c r="I550" t="inlineStr"/>
       <c r="J550" t="inlineStr">
         <is>
           <t>马雅Maya 93.2块根植物专用肥料，容量30ml，专为块根植物如大丽花、仙客来、马蹄莲、海棠等设计。富含促进块根发育所需营养元素，有助于增强植株根系活力，提高抗病能力。使用时按说明稀释后浇灌，避免浓度过高造成肥害。适用于家庭园艺中块茎、块根类花卉的日常养护。</t>
@@ -27071,7 +26735,6 @@
           <t>其他灌木</t>
         </is>
       </c>
-      <c r="G555" t="inlineStr"/>
       <c r="H555" t="inlineStr">
         <is>
           <t>黄杨</t>
@@ -27124,8 +26787,6 @@
           <t>马雅</t>
         </is>
       </c>
-      <c r="H556" t="inlineStr"/>
-      <c r="I556" t="inlineStr"/>
       <c r="J556" t="inlineStr">
         <is>
           <t>马雅Maya102矿物有机肥花卉型是一款专为花卉植物设计的肥料产品，净含量160g。该产品采用矿物与有机相结合的科学配方，富含多种植物生长所需的营养元素，能有效改善土壤结构，增强土壤肥力。适用于各类室内外观赏花卉，如月季、玫瑰、绣球、茉莉等。使用方法简单，可穴施或拌土，能够促进花卉健壮生长，增加开花数量和花色鲜艳度，是家庭园艺花卉养护的理想选择。</t>
@@ -27168,8 +26829,6 @@
           <t>可利鲜Chrysal</t>
         </is>
       </c>
-      <c r="H557" t="inlineStr"/>
-      <c r="I557" t="inlineStr"/>
       <c r="J557" t="inlineStr">
         <is>
           <t>可利鲜Chrysal是来自荷兰的花卉护理品牌，专注于花卉保鲜技术的研发。本品为玫瑰专用保鲜粉剂，规格为5克/包，10包装。采用专业配方，可有效延长玫瑰切花的观赏期，保持花瓣色彩鲜艳，防止叶片黄化。使用时按比例稀释，插入花瓶即可。适用于家庭插花、花店陈列、婚礼装饰等场景。使用前需将花茎剪切成适当长度，去除多余叶片，以充分发挥保鲜效果。建议存放在阴凉干燥处，避免受潮。</t>
@@ -27363,7 +27022,6 @@
           <t>木绣球</t>
         </is>
       </c>
-      <c r="G561" t="inlineStr"/>
       <c r="H561" t="inlineStr">
         <is>
           <t>绣球</t>
@@ -27416,8 +27074,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H562" t="inlineStr"/>
-      <c r="I562" t="inlineStr"/>
       <c r="J562" t="inlineStr">
         <is>
           <t>花彩师免稀释速效植物营养液（通用型）是一款高效水溶肥料，规格为480ml。该产品最大特点是无需稀释即可直接使用，方便快捷，适合各类室内外植物。速效配方富含植物生长所需的氮磷钾及微量元素，能快速补充养分，促进植株健壮生长、叶色浓绿、花果繁茂。适用于家庭园艺、蔬菜花卉、果树等多种植物的追肥使用，建议按照说明书指导进行施用，避免浓度过高造成肥害。</t>
@@ -27772,8 +27428,6 @@
           <t>BerryBird</t>
         </is>
       </c>
-      <c r="H569" t="inlineStr"/>
-      <c r="I569" t="inlineStr"/>
       <c r="J569" t="inlineStr">
         <is>
           <t>BerryBird园艺收纳篮是一款实用的园艺收纳工具，采用坚固材质制作，具有良好的耐用性和美观性。主要用于收纳园艺工具、花卉配件、种子、肥料等园艺用品，帮助保持园艺空间的整洁有序。设计轻巧便携，适合家庭园艺、阳台种植、花店等多种场景使用，可有效分类存放各种园艺物资，提升园艺管理效率。</t>
@@ -28180,8 +27834,6 @@
           <t>云柱系列</t>
         </is>
       </c>
-      <c r="H577" t="inlineStr"/>
-      <c r="I577" t="inlineStr"/>
       <c r="J577" t="inlineStr">
         <is>
           <t>云柱系列装饰盆，采用复古蓝色调设计，25cm高度适中，适合桌面或阳台摆放。圆柱形设计简约大方，可用于种植小型多肉植物或作为装饰性花盆使用。具有良好的透气性和排水性，适合室内外园艺装饰需求。</t>
@@ -28224,8 +27876,6 @@
           <t>成都神龙</t>
         </is>
       </c>
-      <c r="H578" t="inlineStr"/>
-      <c r="I578" t="inlineStr"/>
       <c r="J578" t="inlineStr">
         <is>
           <t>成都神龙曜土蓝莓基质是专为蓝莓种植设计的酸性栽培介质，容量100L。蓝莓喜欢酸性土壤环境（pH值4.5-5.5），该基质采用泥炭、椰糠、珍珠岩等材料科学配比，疏松透气、保水保肥性强，富含蓝莓生长所需的有机质和微量元素。可直接用于蓝莓盆栽或地栽定植，有助于促进蓝莓根系发育和植株健壮生长，提升果实品质和产量。使用时可根据植株大小适当混合园土或其他介质，定期检测土壤酸碱度并适时调节。</t>
@@ -28325,7 +27975,6 @@
           <t>木槿</t>
         </is>
       </c>
-      <c r="I580" t="inlineStr"/>
       <c r="J580" t="inlineStr">
         <is>
           <t>造型木槿是经过人工修剪和培育的园艺植物，株型整齐美观，适合庭院种植或盆栽观赏。花色丰富，有单瓣和重瓣品种，花期较长，通常从夏季持续到秋季。造型木槿喜阳光充足的环境，耐热耐旱，对土壤要求不严，但以疏松肥沃的土壤为佳。养护简单，浇水见干见湿，生长期适当施肥，可保持良好长势。</t>
@@ -28472,8 +28121,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H583" t="inlineStr"/>
-      <c r="I583" t="inlineStr"/>
       <c r="J583" t="inlineStr">
         <is>
           <t>花彩师阳台蔬果型栽培基质，容量70L，专为阳台蔬菜水果种植设计。采用优质泥炭、椰糠、珍珠岩等原料科学配比，透气保水性能优异，养分均衡全面。适用于番茄、黄瓜、草莓、辣椒等阳台蔬果盆栽，可直接使用或与园土混合。建议种植前松土，生长期间保持湿润，定期施肥以补充养分。</t>
@@ -28620,8 +28267,6 @@
           <t>未提供</t>
         </is>
       </c>
-      <c r="H586" t="inlineStr"/>
-      <c r="I586" t="inlineStr"/>
       <c r="J586" t="inlineStr">
         <is>
           <t>园艺通用触屏手套，专为园艺爱好者设计，手指尖端采用导电触屏材质，佩戴后可轻松操作智能手机或平板电脑，无需摘下手套即可接听电话或查询种植信息。浅蓝色设计时尚清新，L号适合手掌较大的用户。手套具备基本防护功能，可在浇水、种植、修剪等园艺作业时使用，有效保护双手免受泥土、荆棘和水分的侵扰，是现代园艺操作的实用辅助工具。</t>
@@ -28825,7 +28470,6 @@
           <t>水青冈</t>
         </is>
       </c>
-      <c r="I590" t="inlineStr"/>
       <c r="J590" t="inlineStr">
         <is>
           <t>虹安进口水青冈是山毛榉科山毛榉属的落叶乔木品种，原装进口种苗。水青冈树形高大挺拔，树冠开阔，叶片呈椭圆形，秋季叶色转为金黄或橙红，具有极高的观赏价值。适合作为庭园主景树、行道树或公园绿化树种。喜阳光充足的环境，耐寒性较强，对土壤要求不高，但在肥沃、排水良好的土壤中生长更佳。进口苗木品质优良，根系发达，移栽成活率高。</t>
@@ -28863,7 +28507,6 @@
           <t>其他乔木</t>
         </is>
       </c>
-      <c r="G591" t="inlineStr"/>
       <c r="H591" t="inlineStr">
         <is>
           <t>柏</t>
@@ -28916,8 +28559,6 @@
           <t>ARTSTONE</t>
         </is>
       </c>
-      <c r="H592" t="inlineStr"/>
-      <c r="I592" t="inlineStr"/>
       <c r="J592" t="inlineStr">
         <is>
           <t>ARTSTONE艾拉系列矮方柱型花盆，采用优质树脂材质制成，具有良好的透气性和排水性。矮方柱型设计简洁大方，适合阳台、露台、花园等场景使用。25规格适合种植中小型花卉、蔬菜或多肉植物等。黑色配色经典百搭，耐晒耐候，室内外均适用。该品牌以设计和品质著称，产品广泛应用于家庭园艺领域。</t>
@@ -29012,8 +28653,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H594" t="inlineStr"/>
-      <c r="I594" t="inlineStr"/>
       <c r="J594" t="inlineStr">
         <is>
           <t>帝罗马圆型托盘摩卡色，采用经典水泥材质制作，表面呈现自然的摩卡色调，简约大方。托盘设计用于承接花盆底部渗水，防止泥土弄脏地面，同时可保持桌面整洁。具有良好的耐磨、耐腐蚀特性，适合室内外使用。36规格尺寸，适合搭配相应尺寸的帝罗马花盆使用，是园艺种植的实用配件。</t>
@@ -29160,8 +28799,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H597" t="inlineStr"/>
-      <c r="I597" t="inlineStr"/>
       <c r="J597" t="inlineStr">
         <is>
           <t>帝罗马经典宽边高圆型盆，采用优质树脂材质制成，白色条纹设计搭配摩卡色调，时尚典雅。宽边设计方便搬运，圆型结构适合种植各类花卉绿植，通风透气性好。22厘米口径，适中尺寸适合桌面或阳台摆放。耐晒耐寒，适合室内外使用，是居家园艺的理想选择。</t>
@@ -29308,8 +28945,6 @@
           <t>虹越</t>
         </is>
       </c>
-      <c r="H600" t="inlineStr"/>
-      <c r="I600" t="inlineStr"/>
       <c r="J600" t="inlineStr">
         <is>
           <t>虹越水溶性肥料是一款高效全水溶性肥料，氮磷钾配比为15-10-30，高钾配方适合花卉、果蔬的中后期使用，能够有效促进花芽分化、提高果实品质和产量。溶解性好，使用方便，适用于滴灌、喷灌及叶面追肥等多种施肥方式，适合月季、铁线莲、蔬菜、果树等多种植物使用。使用时按说明书比例稀释，薄肥勤施效果更佳。</t>
@@ -29483,14 +29118,46 @@
           <t>虹越植物 小檗“玫瑰之光”</t>
         </is>
       </c>
-      <c r="C604" t="inlineStr"/>
-      <c r="D604" t="inlineStr"/>
-      <c r="E604" t="inlineStr"/>
-      <c r="F604" t="inlineStr"/>
-      <c r="G604" t="inlineStr"/>
-      <c r="H604" t="inlineStr"/>
-      <c r="I604" t="inlineStr"/>
-      <c r="J604" t="inlineStr"/>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>植物</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>种苗苗木</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>灌木</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>其他灌木</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>虹越植物</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>小檗</t>
+        </is>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>玫瑰之光</t>
+        </is>
+      </c>
+      <c r="J604" t="inlineStr">
+        <is>
+          <t>小檗是一种常见的落叶或常绿灌木，因其鲜艳的枝条和果实而广受欢迎。'玫瑰之光'是该品种的商品名，叶片呈紫红色或绿色，春季开黄色小花，秋季结红色小果，具有较高的观赏价值。适合作为庭园绿篱、观赏灌木或岩石园点缀，也可用于道路绿化和色彩搭配。喜阳光充足或半阴环境，耐寒性强，对土壤要求不严，萌芽力强，易于修剪造型。</t>
+        </is>
+      </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
@@ -29532,7 +29199,7 @@
       <c r="I605" t="inlineStr"/>
       <c r="J605" t="inlineStr">
         <is>
-          <t>BerryBird园艺手套，墨绿色波点设计，手感舒适透气，适合园艺种植、泥土操作、修剪采收等场景使用。掌心防滑设计，抓握工具更稳固，有效保护双手免受泥土、刺枝伤害，新版波点设计时尚美观，是家庭园艺必备基础工具。</t>
+          <t>BerryBird园艺手套，墨绿色波点设计，时尚美观。具有良好的耐磨性和防护性能，有效保护手部免受泥土、荆棘和植物刺的伤害。掌心防滑处理，抓握工具更稳固。透气舒适，适合各类园艺活动，如种植、换盆、除草等日常养护操作。</t>
         </is>
       </c>
     </row>
@@ -29572,8 +29239,6 @@
           <t>维特</t>
         </is>
       </c>
-      <c r="H606" t="inlineStr"/>
-      <c r="I606" t="inlineStr"/>
       <c r="J606" t="inlineStr">
         <is>
           <t>维特0-40泥炭是一种优质的园艺栽培介质，粒径范围0-40mm，适合各种花卉、蔬菜育苗及盆栽使用。泥炭具有良好的保水性、透气性和酸性特点，能够改善土壤结构，促进植物根系生长发育。Big Bale大包装设计适合规模化园艺生产或家庭园艺大量使用，是花卉种植、苗木培育的理想基质材料。</t>
@@ -29772,8 +29437,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H610" t="inlineStr"/>
-      <c r="I610" t="inlineStr"/>
       <c r="J610" t="inlineStr">
         <is>
           <t>花彩师水溶肥（甜果型）是一款专为瓜果类植物设计的全能型肥料，配方科学均衡，富含氮磷钾及微量元素，能有效促进果实膨大、着色增甜、提高产量和品质。产品溶解性好、无残留，适合叶面喷施或根部浇灌，使用便捷、安全性高。适用于番茄、草莓、葡萄、西瓜等各类甜果型蔬菜水果的整个生长期，建议按照说明稀释后薄肥勤施，避免浓度过高造成肥害。</t>
@@ -29816,8 +29479,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H611" t="inlineStr"/>
-      <c r="I611" t="inlineStr"/>
       <c r="J611" t="inlineStr">
         <is>
           <t>花彩师水溶肥（通用型）是一款适用于各类植物的速效性肥料，富含氮磷钾及微量元素，养分全面且易被植物吸收。可用于叶面喷施或根部浇灌，使用方便快捷。适合花卉、蔬菜、果树等多种植物在各生长阶段使用，能有效促进植物生长发育，增强植株抗性，提高开花结果率。建议按照说明书比例稀释后使用，避免浓度过高造成肥害。</t>
@@ -30011,7 +29672,6 @@
           <t>杜鹃</t>
         </is>
       </c>
-      <c r="G615" t="inlineStr"/>
       <c r="H615" t="inlineStr">
         <is>
           <t>杜鹃</t>
@@ -30059,13 +29719,11 @@
           <t>紫薇</t>
         </is>
       </c>
-      <c r="G616" t="inlineStr"/>
       <c r="H616" t="inlineStr">
         <is>
           <t>紫薇</t>
         </is>
       </c>
-      <c r="I616" t="inlineStr"/>
       <c r="J616" t="inlineStr">
         <is>
           <t>紫薇是落叶灌木或小乔木，树姿优美，枝干光滑，花期6-9月，花色丰富包括紫红、粉红、白色等。喜阳光充足的环境，耐热耐旱，适应性强，对土壤要求不严。紫薇花序长而鲜艳，花期持久，是常见的庭院观赏植物和行道树种，也可用于盆景栽培。其树皮光滑细腻，观赏价值高，寿命较长。</t>
@@ -30108,8 +29766,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H617" t="inlineStr"/>
-      <c r="I617" t="inlineStr"/>
       <c r="J617" t="inlineStr">
         <is>
           <t>花彩师生物有机肥海藻型是一款含有海藻提取物的有机肥料产品，规格为350g。该肥料富含有机质和海藻活性成分，能够改善土壤结构，增加土壤肥力，促进植物根系发育和营养吸收。适用于各类花卉、蔬菜、果树等植物的基肥和追肥使用，海藻成分还能增强植物抗逆性，提高抗病能力。有机肥料特性使其更适合追求绿色环保种植的用户，长期使用有助于土壤生态平衡。</t>
@@ -30204,8 +29860,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H619" t="inlineStr"/>
-      <c r="I619" t="inlineStr"/>
       <c r="J619" t="inlineStr">
         <is>
           <t>盆底石是一种园艺基质改良材料，铺设于花盆底部，主要用于增强排水性和透气性。3L容量适合中小型花盆使用，能有效防止土壤流失，避免根系积水腐烂，同时为植物提供更好的生长环境。适用于各种室内外盆栽植物，如多肉、绿植、花卉等。使用时建议铺设厚度为盆高的1/5至1/4，配合疏松透气的土壤效果更佳。</t>
@@ -30352,8 +30006,6 @@
           <t>马雅</t>
         </is>
       </c>
-      <c r="H622" t="inlineStr"/>
-      <c r="I622" t="inlineStr"/>
       <c r="J622" t="inlineStr">
         <is>
           <t>马雅Maya90浓缩营养液是一种通用型高浓度液体肥料，10ml*10条独立包装设计，便于储存和使用。适用于家庭园艺中各类花卉、蔬菜、果树等植物的追肥使用。可快速补充植物生长所需的大量元素和微量元素，促进植株健壮生长、叶色浓绿、花果丰满。使用时需按比例稀释后浇灌或叶面喷施，适合家庭阳台花卉、盆栽植物以及庭院植物的日常养护施肥。</t>
@@ -30423,14 +30075,46 @@
           <t>虹越铁线莲 马祖里</t>
         </is>
       </c>
-      <c r="C624" t="inlineStr"/>
-      <c r="D624" t="inlineStr"/>
-      <c r="E624" t="inlineStr"/>
-      <c r="F624" t="inlineStr"/>
-      <c r="G624" t="inlineStr"/>
-      <c r="H624" t="inlineStr"/>
-      <c r="I624" t="inlineStr"/>
-      <c r="J624" t="inlineStr"/>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>植物</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>种苗苗木</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>藤本</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>铁线莲</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>虹越</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>铁线莲</t>
+        </is>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>马祖里</t>
+        </is>
+      </c>
+      <c r="J624" t="inlineStr">
+        <is>
+          <t>铁线莲马祖里是一款优雅的藤本花卉，以其大花型、丰富的花色和长花期著称。花朵直径可达15-20厘米，花色通常为蓝紫色或粉紫色，花瓣质地坚韧，观赏价值极高。该品种攀援能力强，适合用于花架、拱门、篱笆、墙面等立体绿化，可打造梦幻的花墙效果。喜阳光充足但忌强光暴晒，适宜种植在排水良好、疏松肥沃的土壤中。耐寒性较好，冬季最低可耐-20℃低温，北方地区可露天越冬。春季换盆时需适当修剪枯枝，施肥以磷钾肥为主，可促进开花繁茂。</t>
+        </is>
+      </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
@@ -30460,23 +30144,27 @@
       </c>
       <c r="F625" t="inlineStr">
         <is>
-          <t>其他藤本</t>
+          <t>铁线莲</t>
         </is>
       </c>
       <c r="G625" t="inlineStr">
         <is>
-          <t>虹安果树</t>
+          <t>虹越</t>
         </is>
       </c>
       <c r="H625" t="inlineStr">
         <is>
-          <t>八月瓜</t>
-        </is>
-      </c>
-      <c r="I625" t="inlineStr"/>
+          <t>铁线莲</t>
+        </is>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>马祖里</t>
+        </is>
+      </c>
       <c r="J625" t="inlineStr">
         <is>
-          <t>八月瓜（学名：Akebia trifoliata），又名三叶木通、野香蕉，是木通科木通属多年生藤本植物。掌状复叶，小叶3枚，春季开深紫色花朵，果实为长椭圆形，成熟时果皮呈紫红色，可食用，口感香甜软糯，富含维生素和氨基酸。因其在农历八月成熟而得名，是近年新兴的特色水果品种，适合庭院、阳台种植，既可观赏又可采果。喜阳光充足的环境，较耐寒，适宜排水良好的土壤。</t>
+          <t>铁线莲是多年生藤本花卉，被誉为“藤本皇后”。马祖里是一个观赏性较高的铁线莲品种，花型优美、花色丰富，适合庭院垂直绿化、廊架装饰或阳台盆栽。喜欢阳光充足但根部阴凉的环境，栽培介质需疏松透气、排水良好。冬季可耐寒，夏季需注意通风降温。花期通常在春末至秋季，修剪方式因品种而异，需根据品种特性进行合理修剪以促进开花。</t>
         </is>
       </c>
     </row>
@@ -30719,7 +30407,6 @@
           <t>冬青</t>
         </is>
       </c>
-      <c r="G630" t="inlineStr"/>
       <c r="H630" t="inlineStr">
         <is>
           <t>冬青</t>
@@ -30772,8 +30459,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H631" t="inlineStr"/>
-      <c r="I631" t="inlineStr"/>
       <c r="J631" t="inlineStr">
         <is>
           <t>花彩师椰糠颗粒是一种优质的园艺栽培介质，采用纯天然椰糠原料加工而成。颗粒状设计便于排水透气，适合配制营养土或直接用于兰花、多肉等植物的栽培。能有效改善土壤结构，增加透气性，调节水分，保持根系健康生长。500g小包装适合家庭园艺使用，方便储存和取用。建议与泥炭土、珍珠岩等混合使用，效果更佳。</t>
@@ -30972,8 +30657,6 @@
           <t>BerryBird</t>
         </is>
       </c>
-      <c r="H635" t="inlineStr"/>
-      <c r="I635" t="inlineStr"/>
       <c r="J635" t="inlineStr">
         <is>
           <t>BerryBird园艺尖头花枝剪是一款专业修剪工具，采用尖头设计便于精确修剪细小枝条。适用于花卉、果树、灌木等植物的整形修剪，可轻松处理交叉枝、细弱枝、过密枝等。该剪刀采用优质钢材刀口，锋利耐用，手柄符合人体工程学设计，握持舒适省力。使用后应保持刀口清洁并涂抹防锈油以延长使用寿命。</t>
@@ -31016,8 +30699,6 @@
           <t>可利鲜Chrysal</t>
         </is>
       </c>
-      <c r="H636" t="inlineStr"/>
-      <c r="I636" t="inlineStr"/>
       <c r="J636" t="inlineStr">
         <is>
           <t>可利鲜Chrysal鲜花营养保鲜粉剂是一种专为鲜花设计的保鲜营养产品，5克小包装便于使用。每包10袋装，适合家庭日常使用或花店备货。该产品能有效延长鲜切花观赏期，为花朵提供充足养分，保持花瓣鲜艳度，防止过早凋谢。使用时按比例溶于水中，可用于日常养护或花束处理，是养花爱好者和花店从业者的常用辅助用品。</t>
@@ -31060,8 +30741,6 @@
           <t>ARTSTONE</t>
         </is>
       </c>
-      <c r="H637" t="inlineStr"/>
-      <c r="I637" t="inlineStr"/>
       <c r="J637" t="inlineStr">
         <is>
           <t>ARTSTONE菲奥纳圆钵31灰色是一款造型简约的室内外通用花盆，采用优质树脂材质制成，具有良好的耐久性和抗紫外线性能。圆钵设计适合种植各类草本花卉、小型灌木及多肉植物，灰色色调现代时尚，易于搭配各种家居和园艺风格。底部设有排水孔设计，可有效防止积水烂根，适合家庭园艺、阳台种植及商业景观布置使用。</t>
@@ -31104,8 +30783,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H638" t="inlineStr"/>
-      <c r="I638" t="inlineStr"/>
       <c r="J638" t="inlineStr">
         <is>
           <t>帝罗马西西里柠檬方型盆，意大利知名园艺品牌帝罗马（Deroma）推出的时尚花盆产品。采用地中海风格设计，西西里柠檬色系清新明亮，方型造型适合阳台、庭院等空间摆放。盆体质地坚固耐用，排水透气性良好，适合种植各类草本花卉、蔬菜及小型灌木。采用优质陶土材质，具有良好的保水性和透气性，有助于植物根系健康生长。17号尺寸适中，适合桌面或地面装饰摆设。</t>
@@ -31252,8 +30929,6 @@
           <t>BerryBird</t>
         </is>
       </c>
-      <c r="H641" t="inlineStr"/>
-      <c r="I641" t="inlineStr"/>
       <c r="J641" t="inlineStr">
         <is>
           <t>BerryBird品牌推出的木雕手铲，采用精细木雕工艺制作，设计独特精美。此款为2023世界花园大会纪念版，具有收藏价值和实用功能。手铲设计符合人体工程学，握持舒适，适合用于盆栽换土、小规模挖掘、移栽等园艺操作。木质手柄不仅美观而且防滑耐磨，是园艺爱好者日常种植和维护的理想工具选择。</t>
@@ -31504,8 +31179,6 @@
           <t>BerryBird</t>
         </is>
       </c>
-      <c r="H646" t="inlineStr"/>
-      <c r="I646" t="inlineStr"/>
       <c r="J646" t="inlineStr">
         <is>
           <t>BerryBird品牌的不锈钢三爪园艺工具，主要用于园艺种植中的松土、除草工作。三爪设计能够有效疏松土壤、清除杂草，不锈钢材质具有耐用防锈的特性，适合家庭园艺和专业园艺作业使用。</t>
@@ -31548,8 +31221,6 @@
           <t>美乐棵</t>
         </is>
       </c>
-      <c r="H647" t="inlineStr"/>
-      <c r="I647" t="inlineStr"/>
       <c r="J647" t="inlineStr">
         <is>
           <t>美乐棵家庭园艺浓缩营养液是一种高效浓缩型液体肥料，采用科学配比，富含氮磷钾及微量元素，适用于家庭园艺中各类花卉、蔬菜、果树等植物的追肥使用。产品为通用型配方，可满足植物生长期的基本营养需求。使用时需按比例稀释后浇灌或叶面喷施，建议每7-14天施用一次。浓缩液设计便于存储，小包装适合家庭阳台、窗台种植使用，安全便捷。</t>
@@ -31592,8 +31263,6 @@
           <t>ARTSTONE</t>
         </is>
       </c>
-      <c r="H648" t="inlineStr"/>
-      <c r="I648" t="inlineStr"/>
       <c r="J648" t="inlineStr">
         <is>
           <t>ARTSTONE艾拉花槽是一款高品质的园艺种植容器，采用优质树脂材料制成，具有良好的耐久性和抗老化性能。花槽设计简约时尚，灰色色调百搭各种家居和园艺风格。适用于种植各类草本花卉、蔬菜、香草植物等，可放置于阳台、露台、庭院等场所。产品尺寸为37规格，提供充足的种植空间，底部设有排水孔设计，确保植物根系呼吸透气，避免积水烂根。清洁方便，可重复使用，是家庭园艺和景观装饰的理想选择。</t>
@@ -31792,8 +31461,6 @@
           <t>马雅</t>
         </is>
       </c>
-      <c r="H652" t="inlineStr"/>
-      <c r="I652" t="inlineStr"/>
       <c r="J652" t="inlineStr">
         <is>
           <t>马雅Maya100纯天然速溶有机碳肥是一种高效有机肥料，富含天然有机碳源，能快速补充土壤有机质，改善土壤结构，促进植物根系发育。速溶配方易于溶解吸收，适用于各类花卉、蔬菜、果树等植物的追肥和基肥使用。纯天然成分，温和不伤根，可提高植物抗病抗逆性，适合家庭园艺和农业生产使用。</t>
@@ -31836,8 +31503,6 @@
           <t>马雅Maya</t>
         </is>
       </c>
-      <c r="H653" t="inlineStr"/>
-      <c r="I653" t="inlineStr"/>
       <c r="J653" t="inlineStr">
         <is>
           <t>马雅Maya91.11彩叶芋专用肥料，容量500ml，专为彩叶芋研发的植物营养液。彩叶芋因其绚丽多彩的叶片而受喜爱，这款专用肥针对彩叶芋的生长特点科学配比氮磷钾及微量元素，能有效促进叶片色彩更加鲜艳饱满，增强植株抗病能力。使用时按说明比例稀释后浇灌或叶面喷施，生长季每7-14天施用一次，注意避免强光直射时段施肥，低温或休眠期减少施肥频率。</t>
@@ -31984,8 +31649,6 @@
           <t>ARTSTONE</t>
         </is>
       </c>
-      <c r="H656" t="inlineStr"/>
-      <c r="I656" t="inlineStr"/>
       <c r="J656" t="inlineStr">
         <is>
           <t>ARTSTONE艾拉花槽37棕色是一款高品质的园艺种植容器，专为室内外花卉、蔬菜、香草等植物栽培设计。采用优质材料制作，具有良好的透气性和排水性，有助于植物根系健康生长。简约的棕色设计能够融入各种园艺风格，既实用又美观，适合阳台、庭院、窗台等场所使用。花槽尺寸适中，便于移动和摆放，是园艺爱好者理想的选择。</t>
@@ -32080,8 +31743,6 @@
           <t>马雅</t>
         </is>
       </c>
-      <c r="H658" t="inlineStr"/>
-      <c r="I658" t="inlineStr"/>
       <c r="J658" t="inlineStr">
         <is>
           <t>马雅Maya93.43蓝莓植物专用水溶肥，容量500ml，专为蓝莓等灌木类果树研制的酸性肥料。本品采用科学配比，富含蓝莓生长所需的微量元素和营养成分，pH值适宜蓝莓根系吸收。能有效促进蓝莓植株健壮生长，提高坐果率，改善果实品质。稀释后浇灌或叶面喷施均可，使用方便，适合家庭园艺蓝莓盆栽及地栽养护。注意薄肥勤施，避免浓度过高造成肥害。</t>
@@ -32124,8 +31785,6 @@
           <t>HB-101</t>
         </is>
       </c>
-      <c r="H659" t="inlineStr"/>
-      <c r="I659" t="inlineStr"/>
       <c r="J659" t="inlineStr">
         <is>
           <t>HB-101植物活力液是一种植物生长促进剂，主要成分为植物提取物，可有效激活植物生长潜能，增强植株抗逆性。使用方法简单，稀释后叶面喷施或灌根均可。适用于各类花卉、蔬菜、果树等植物，可促进生根发芽、增强光合作用、提高开花结果率。是家庭园艺和农业生产中常用的植物护理产品。</t>
@@ -32168,8 +31827,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H660" t="inlineStr"/>
-      <c r="I660" t="inlineStr"/>
       <c r="J660" t="inlineStr">
         <is>
           <t>花彩师腐叶土是一种天然有机介质，由落叶经过自然发酵腐熟而成，富含有机质和营养成分。具有良好的疏松透气性和保水保肥能力，可改善土壤结构，增加土壤肥力。适用于各类花卉、蔬菜盆栽以及地栽植物的土壤改良。使用时建议与其他介质混合搭配，避免单独使用量过大。可作为基质或追肥使用，适合家庭园艺各类植物栽培。</t>
@@ -32212,8 +31869,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H661" t="inlineStr"/>
-      <c r="I661" t="inlineStr"/>
       <c r="J661" t="inlineStr">
         <is>
           <t>花彩师三合一有机肥是一款以鸡粪、牛粪、羊粪为主要原料的复合有机肥料，重量为5kg。该产品富含有机质和多种植物生长所需的营养元素，能够改善土壤结构，增加土壤肥力，促进植物健康生长。适用于家庭园艺、蔬菜种植、花卉培育等多种场景。使用时可根据植物需求适量施用，避免直接接触根部，适合做基肥或追肥使用。</t>
@@ -32308,8 +31963,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H663" t="inlineStr"/>
-      <c r="I663" t="inlineStr"/>
       <c r="J663" t="inlineStr">
         <is>
           <t>帝罗马橄榄枝碗型盆18是一款精致的园艺品牌花盆，采用高品质陶瓷材质，碗型设计独特优美，盆面饰有精致的橄榄枝纹样，兼具实用性与装饰性。18厘米口径适合种植小型花卉、多肉植物或桌面绿植，摆放在阳台、窗台或室内客厅都能提升空间美感。品牌盆做工精细，透气性好，底部有排水孔设计，利于植物根系呼吸与水分排出，是追求品质园艺生活的理想选择。</t>
@@ -32560,8 +32213,6 @@
           <t>ARTSTONE</t>
         </is>
       </c>
-      <c r="H668" t="inlineStr"/>
-      <c r="I668" t="inlineStr"/>
       <c r="J668" t="inlineStr">
         <is>
           <t>ARTSTONE正方酷边型花盆，采用优质树脂材质，轻便耐用，适合室内外阳台、花园等场景使用。方形设计简约时尚，边缘造型独特，灰色配色沉稳百搭，可搭配多种植物盆栽。具有良好的透气透水性孔设计，利于植物根系呼吸。尺寸约27cm，适合中小型植物种植或作为装饰性花盆使用。</t>
@@ -32599,9 +32250,6 @@
           <t>其他品牌盆</t>
         </is>
       </c>
-      <c r="G669" t="inlineStr"/>
-      <c r="H669" t="inlineStr"/>
-      <c r="I669" t="inlineStr"/>
       <c r="J669" t="inlineStr">
         <is>
           <t>北欧风格花盆，设计简约时尚，采用自然材质或仿自然质感，呈现斯堪的纳维亚风格。中号尺寸适合多种植物栽种，如小型观叶植物、多肉植物或草本花卉。具有良好的透气性和排水性，适合室内外园艺装饰使用。</t>
@@ -32956,8 +32604,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H676" t="inlineStr"/>
-      <c r="I676" t="inlineStr"/>
       <c r="J676" t="inlineStr">
         <is>
           <t>花彩师椰糠是由椰子外壳加工而成的天然栽培介质，具有良好的保水性和透气性，能够为植物根系提供疏松的生长环境。椰糠质地轻盈、清洁无菌，适用于各种盆栽植物的种植和土壤改良。可单独使用或与其他介质混合配比，适合多肉、花卉、蔬菜等多种植物的栽培。使用前建议用清水充分泡发并冲洗掉多余盐分，以达到最佳使用效果。</t>
@@ -33099,7 +32745,6 @@
           <t>枫树</t>
         </is>
       </c>
-      <c r="G679" t="inlineStr"/>
       <c r="H679" t="inlineStr">
         <is>
           <t>枫树</t>
@@ -33152,8 +32797,6 @@
           <t>君沐</t>
         </is>
       </c>
-      <c r="H680" t="inlineStr"/>
-      <c r="I680" t="inlineStr"/>
       <c r="J680" t="inlineStr">
         <is>
           <t>君沐1000目喷头是一款园艺浇水工具配件，红色外观设计。1000目表示喷头细度适中，可用于喷雾或浇水作业。9%可能指喷头开孔率或雾化程度。适用于家庭园艺、花园浇灌等场景，可安装在浇水壶或其他浇水设备上使用，方便调节水流大小和喷雾范围，提高浇水效率。</t>
@@ -33352,8 +32995,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H684" t="inlineStr"/>
-      <c r="I684" t="inlineStr"/>
       <c r="J684" t="inlineStr">
         <is>
           <t>花彩师优+铁线莲专用介质是专为铁线莲种植研发的配方土壤，容量8L。该介质针对铁线莲根系特点设计，具有良好的透气性、排水性和保水性，pH值适宜铁线莲生长。介质中添加了适量的有机质和营养成分，能够促进铁线莲根系发育和植株健壮生长。适用于铁线莲上盆、换盆及地栽改良，使用时需保持介质湿润但避免积水。</t>
@@ -33552,8 +33193,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H688" t="inlineStr"/>
-      <c r="I688" t="inlineStr"/>
       <c r="J688" t="inlineStr">
         <is>
           <t>花彩师稻壳炭是一种优质的园艺土壤改良材料，采用天然稻壳经过高温碳化工艺制成。具有良好的透气性和保水性，能有效改善土壤结构，调节土壤酸碱度，增加土壤有机质含量。适用于多肉植物栽培、兰科植物培养、蔬菜种植等场景，可作为扦插介质或土壤改良添加材料使用。</t>
@@ -33596,8 +33235,6 @@
           <t>ARTSTONE</t>
         </is>
       </c>
-      <c r="H689" t="inlineStr"/>
-      <c r="I689" t="inlineStr"/>
       <c r="J689" t="inlineStr">
         <is>
           <t>ARTSTONE艾拉花槽是一款专为园艺设计的高端种植容器，采用优质环保材料制成，坚固耐用且具有良好的透气性和排水性。灰色配色简约时尚，能够融入各种庭院、阳台或花园风格。花槽设计适合种植各类草本花卉、蔬菜或小型灌木，为植物提供良好的生长环境。是家庭园艺和景观设计的理想选择。</t>
@@ -33952,8 +33589,6 @@
           <t>BerryBird</t>
         </is>
       </c>
-      <c r="H696" t="inlineStr"/>
-      <c r="I696" t="inlineStr"/>
       <c r="J696" t="inlineStr">
         <is>
           <t>BerryBird不锈钢五合一手工具是一套多功能园艺工具组合，通常包含铲子、叉子、耙子、移植刀、剪刀等多种功能。不锈钢材质防锈耐用，人体工学手柄设计握持舒适。适用于花园种植、盆栽换土、疏松土壤、挖掘坑穴、修剪枝叶等多种园艺操作。一套解决多种需求，适合家庭园艺爱好者日常使用。</t>
@@ -33996,8 +33631,6 @@
           <t>马雅</t>
         </is>
       </c>
-      <c r="H697" t="inlineStr"/>
-      <c r="I697" t="inlineStr"/>
       <c r="J697" t="inlineStr">
         <is>
           <t>马雅Maya95矿物有机激活喷雾是一款高效植物营养激活产品，富含矿物质和有机成分，采用喷雾形式便于叶面吸收。480ml补充袋装设计经济实用，适合家庭园艺使用。不带喷头设计便于与原喷头配合使用，减少浪费。产品能有效激活植物生长潜能，增强光合作用，促进养分吸收转化，提升植物抗逆性。适用于各类室内外观赏植物和蔬果的日常养护，建议每隔7-10天喷施一次，效果更佳。</t>
@@ -34092,8 +33725,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H699" t="inlineStr"/>
-      <c r="I699" t="inlineStr"/>
       <c r="J699" t="inlineStr">
         <is>
           <t>花彩师园艺冰袖（雀斑款）是一款专为园艺爱好者设计的防晒防护用品。采用冰丝材质，触感凉爽透气，袖口采用防滑设计，佩戴舒适不紧绷。能有效阻挡紫外线，保护手臂免受阳光晒伤，同时防止植物枝叶刮伤皮肤。雀斑款设计增添了时尚趣味性，适合庭院园艺、户外种植、花卉养护等多种园艺活动场景使用。</t>
@@ -34396,8 +34027,6 @@
           <t>奥石克莱尔</t>
         </is>
       </c>
-      <c r="H705" t="inlineStr"/>
-      <c r="I705" t="inlineStr"/>
       <c r="J705" t="inlineStr">
         <is>
           <t>奥石克莱尔圆型两用种植盆，灰褐色设计，简约大方。采用优质塑料材质，轻便耐用，适合室内外花卉、蔬菜、多肉等多种植物栽培。两用设计可作为育苗盆或成品盆栽使用，底部排水孔设计合理，透气性好，便于植物根系生长和水分管理。灰褐色配色低调自然，易于融入各种家居或园艺环境。</t>
@@ -34440,8 +34069,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H706" t="inlineStr"/>
-      <c r="I706" t="inlineStr"/>
       <c r="J706" t="inlineStr">
         <is>
           <t>帝罗马宽边圆型套盆红陶盆，意大利进口品牌，以优质红陶为材质，具有良好的透气性和排水性，能有效防止植物根系腐烂。宽边设计不仅美观大方，还便于搬动和日常管理。红色陶土色泽自然古朴，适合搭配各类绿植和花卉，提升居家或园艺空间的装饰品味。套盆设计可保护内盆，方便换盆操作，是室内外绿植养护的理想选择。</t>
@@ -34484,8 +34111,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H707" t="inlineStr"/>
-      <c r="I707" t="inlineStr"/>
       <c r="J707" t="inlineStr">
         <is>
           <t>帝罗马托斯卡尼亚系列圆型托盘，采用高品质树脂材质，耐用防腐，适合室内外使用。托盘设计用于承接花盆底部流出的水分，防止浇水时弄脏地面或桌面，同时可保持土壤湿度均匀。圆润的造型搭配托斯卡尼亚风格设计，简约大方，是花盆搭配的实用配件。</t>
@@ -34523,7 +34148,6 @@
           <t>杜鹃</t>
         </is>
       </c>
-      <c r="G708" t="inlineStr"/>
       <c r="H708" t="inlineStr">
         <is>
           <t>杜鹃</t>
@@ -34571,13 +34195,11 @@
           <t>其他乔木</t>
         </is>
       </c>
-      <c r="G709" t="inlineStr"/>
       <c r="H709" t="inlineStr">
         <is>
           <t>雪铃树</t>
         </is>
       </c>
-      <c r="I709" t="inlineStr"/>
       <c r="J709" t="inlineStr">
         <is>
           <t>雪铃树学名安息香，为安息香科安息香属落叶小乔木，原产东亚。株高3-6米，冠幅2-4米。春季开花，花白色，钟形下垂如铃铛，成串开放，花量丰富极具观赏性。喜光稍耐阴，耐寒性较强，适宜温暖湿润气候。对土壤要求不严，以排水良好的酸性至微酸性土壤为佳。适合庭院孤植或丛植，也可作为行道树。是优秀的春季观花乔木，花姿优美飘逸，盛花时如雪球挂枝，芳香四溢，极具浪漫气息。</t>
@@ -34776,8 +34398,6 @@
           <t>BerryBird</t>
         </is>
       </c>
-      <c r="H713" t="inlineStr"/>
-      <c r="I713" t="inlineStr"/>
       <c r="J713" t="inlineStr">
         <is>
           <t>BerryBird不锈钢盆栽勺是一款专为盆栽植物设计的精细种植工具，采用优质不锈钢材质，具有耐腐蚀、耐磨损的特性。勺形设计便于精确舀取土壤、肥料或移栽小苗，适合多肉植物、花卉、蔬菜育苗等场景使用。手柄设计符合人体工程学，握持舒适，操作省力。是家庭园艺爱好者和专业种植者必备的实用工具。</t>
@@ -34976,8 +34596,6 @@
           <t>TOF</t>
         </is>
       </c>
-      <c r="H717" t="inlineStr"/>
-      <c r="I717" t="inlineStr"/>
       <c r="J717" t="inlineStr">
         <is>
           <t>TOF泥炭土为原装进口优质泥炭原料，颗粒度0-40mm，适合作为园艺种植基础介质。泥炭具有疏松透气、保水保肥、质地轻便的特点，可单独使用或与其他介质混合配比。能有效改善土壤结构，调节酸碱度，为植物根系提供良好的生长环境。广泛应用于花卉、蔬菜、苗木等栽培介质。建议搭配珍珠岩、椰糠等材料使用，以达到更好的透气性和排水效果。</t>
@@ -35228,8 +34846,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H722" t="inlineStr"/>
-      <c r="I722" t="inlineStr"/>
       <c r="J722" t="inlineStr">
         <is>
           <t>轻石是一种优质的园艺改良材料，由火山喷发形成的天然多孔岩石加工而成。具有质轻、疏松、透气、排水良好的特性。5L规格适合家庭园艺使用，可有效改善土壤结构，防止盆土板结，增强根系呼吸作用。适用于多肉植物、兰花、盆栽花卉等需要高透气性环境的植物。可单独使用或与泥炭土、椰糠等介质混合配制成专用培养土，是园艺爱好者必备的改良基质。</t>
@@ -35272,8 +34888,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H723" t="inlineStr"/>
-      <c r="I723" t="inlineStr"/>
       <c r="J723" t="inlineStr">
         <is>
           <t>帝罗马锡耶纳迷你方型盆是意大利进口品牌花盆，采用优质陶土高温烧制而成，质感细腻，透气性好。迷你方型设计适合桌面摆放或小空间种植，可种植多肉、小型草本植物等。11号尺寸为迷你规格，适合育苗或种植小型植物。盆体坚固耐用，适合室内外使用。</t>
@@ -35316,8 +34930,6 @@
           <t>雪瑞奇</t>
         </is>
       </c>
-      <c r="H724" t="inlineStr"/>
-      <c r="I724" t="inlineStr"/>
       <c r="J724" t="inlineStr">
         <is>
           <t>雪瑞奇小鸟滴水器S紫色是一款智能园艺浇水工具，采用小鸟造型设计，兼具装饰性与实用性。该滴水器可自动控制水滴大小和滴水频率，适用于盆栽、花卉、蔬菜等植物的精准浇水。紫色S型号适合中小型花盆使用，帮助园艺爱好者轻松实现定时定量浇水，解决出差或旅行时植物无人照看的难题，同时节约用水，呵护植物健康成长。</t>
@@ -35355,7 +34967,6 @@
           <t>绣球</t>
         </is>
       </c>
-      <c r="G725" t="inlineStr"/>
       <c r="H725" t="inlineStr">
         <is>
           <t>绣球</t>
@@ -35455,7 +35066,6 @@
           <t>枫树</t>
         </is>
       </c>
-      <c r="G727" t="inlineStr"/>
       <c r="H727" t="inlineStr">
         <is>
           <t>枫树</t>
@@ -35503,9 +35113,6 @@
           <t>其他尺寸</t>
         </is>
       </c>
-      <c r="G728" t="inlineStr"/>
-      <c r="H728" t="inlineStr"/>
-      <c r="I728" t="inlineStr"/>
       <c r="J728" t="inlineStr">
         <is>
           <t>北欧风格大号花盆，简约时尚的设计适合现代家居装饰。采用优质材质制作，具有良好的透气性和排水性，适合种植各种室内外植物。大号尺寸适合种植中大型植物或多年生草本花卉，如玉簪、松果菊等。盆壁光滑易清洁，可用于阳台、客厅、书房等空间装饰。</t>
@@ -35548,8 +35155,6 @@
           <t>马雅</t>
         </is>
       </c>
-      <c r="H729" t="inlineStr"/>
-      <c r="I729" t="inlineStr"/>
       <c r="J729" t="inlineStr">
         <is>
           <t>马雅Maya92浓缩营养液花卉型是一款高浓度植物营养液，采用科学配比富含氮磷钾及微量元素，专为室内外花卉植物设计。10ml小包装便于精准稀释使用，条装设计便于储存。适用于各类开花植物如月季、绣球、茉莉等，可促进花芽分化、延长花期、增强开花质量。使用时需按比例稀释后浇灌或叶面喷施，建议每7-14天施用一次，薄肥勤施避免烧根。</t>
@@ -35592,8 +35197,6 @@
           <t>BerryBird</t>
         </is>
       </c>
-      <c r="H730" t="inlineStr"/>
-      <c r="I730" t="inlineStr"/>
       <c r="J730" t="inlineStr">
         <is>
           <t>BerryBird不锈钢移植手铲是一款专业的园艺种植工具，采用优质不锈钢材质制成，具有耐腐蚀、耐磨损、坚固耐用的特点。手铲设计符合人体工程学，握持舒适，操作省力。适用于花卉、蔬菜苗木的移植、盆栽土装填、挖坑松土等工作。不锈钢材质确保工具在潮湿土壤环境中不易生锈，易于清洁维护，是家庭园艺和专业种植的理想帮手。</t>
@@ -35636,8 +35239,6 @@
           <t>BerryBird</t>
         </is>
       </c>
-      <c r="H731" t="inlineStr"/>
-      <c r="I731" t="inlineStr"/>
       <c r="J731" t="inlineStr">
         <is>
           <t>BerryBird特氟龙弯头花枝剪是一款专业园艺修剪工具，采用优质特氟龙涂层处理，具有防锈防腐蚀、不沾粘树脂等特点。弯头设计方便深入枝叶密集处进行精准修剪，提高工作效率。适用于花卉、果树、灌木等植物的枝条修剪，是家庭园艺和专业园林养护的理想工具选择。</t>
@@ -35779,13 +35380,11 @@
           <t>其他灌木</t>
         </is>
       </c>
-      <c r="G734" t="inlineStr"/>
       <c r="H734" t="inlineStr">
         <is>
           <t>溲疏</t>
         </is>
       </c>
-      <c r="I734" t="inlineStr"/>
       <c r="J734" t="inlineStr">
         <is>
           <t>溲疏是虎耳草科溲疏属落叶灌木，原产中国。株高1-3米，叶对生，边缘有细锯齿。圆锥花序顶生，花白色或粉红色，花期5-6月。喜光稍耐阴，耐寒耐旱，对土壤要求不严。适合庭院、公园种植，可作花篱或丛植，也可用于边坡绿化。溲疏花量大、花期长，具有较高的观赏价值，是优良的园林绿化树种。</t>
@@ -35880,8 +35479,6 @@
           <t>马雅</t>
         </is>
       </c>
-      <c r="H736" t="inlineStr"/>
-      <c r="I736" t="inlineStr"/>
       <c r="J736" t="inlineStr">
         <is>
           <t>马雅Maya91液体绿叶型是一款专为促进植物叶片生长而设计的液体肥料，富含氮元素及其他微量元素，能有效增强植物光合作用，使叶片更加浓绿光亮。适用于各类花卉、蔬菜及室内绿植的叶面追肥或根部施肥。使用时建议按照说明书比例稀释后施用，避免浓度过高造成肥害。应存放于阴凉干燥处，避免阳光直射。产品容量为500ml，便于家庭园艺使用。</t>
@@ -35924,8 +35521,6 @@
           <t>马雅</t>
         </is>
       </c>
-      <c r="H737" t="inlineStr"/>
-      <c r="I737" t="inlineStr"/>
       <c r="J737" t="inlineStr">
         <is>
           <t>马雅95矿物有机激活喷剂是一款专为园艺植物设计的叶面喷施肥料，容量505ml。该产品融合矿物元素与有机活性成分，能够快速激活植物生长活力，补充植株所需的微量元素和营养物质。适用于家庭花卉、蔬菜、果树等多种植物的日常养护，可通过叶面喷洒方式被植物快速吸收利用，促进光合作用，增强植物抗病抗逆能力，改善叶色萎黄等问题。使用时建议稀释后均匀喷施于植物叶面，避免强光直射时段施用。</t>
@@ -36015,7 +35610,6 @@
           <t>其他灌木</t>
         </is>
       </c>
-      <c r="G739" t="inlineStr"/>
       <c r="H739" t="inlineStr">
         <is>
           <t>黄杨</t>
@@ -36115,7 +35709,6 @@
           <t>绣球</t>
         </is>
       </c>
-      <c r="G741" t="inlineStr"/>
       <c r="H741" t="inlineStr">
         <is>
           <t>绣球</t>
@@ -36163,13 +35756,11 @@
           <t>其他灌木</t>
         </is>
       </c>
-      <c r="G742" t="inlineStr"/>
       <c r="H742" t="inlineStr">
         <is>
           <t>菲油果</t>
         </is>
       </c>
-      <c r="I742" t="inlineStr"/>
       <c r="J742" t="inlineStr">
         <is>
           <t>菲油果（Feijoa sellowiana）又名南美稔、费约果，是桃金娘科常绿灌木或小乔木，原产于南美洲。高约1-3米，全株密被银灰色细毛。叶对生，椭圆形，厚革质，具小油点。花单生叶腋，花瓣外白内紫，芳香四溢，花期5-6月。果实椭圆形，绿色可食，果肉酸甜多汁，富含维生素C和膳食纤维，口感独特。可鲜食或加工成果汁果酱。喜温暖湿润气候，较耐寒，适应性强，适合庭院种植或盆栽观赏。</t>
@@ -36212,8 +35803,6 @@
           <t>BerryBird</t>
         </is>
       </c>
-      <c r="H743" t="inlineStr"/>
-      <c r="I743" t="inlineStr"/>
       <c r="J743" t="inlineStr">
         <is>
           <t>BerryBird品牌园艺垫，尺寸73*73cm，采用防水耐磨材质制作，可有效防止泥土、水渍弄脏地面，保持种植区域整洁。常用于花盆垫底、操作台铺设或盆栽底部防水保护，便于清洁打理，可反复使用，适合室内外园艺操作场景。</t>
@@ -36313,7 +35902,6 @@
           <t>灯笼树</t>
         </is>
       </c>
-      <c r="I745" t="inlineStr"/>
       <c r="J745" t="inlineStr">
         <is>
           <t>灯笼树，学名Enkianthus chinensis，属于杜鹃花科吊灯花属，是一种落叶灌木或小乔木。因其花形独特，花冠呈灯笼状下垂而得名。叶片椭圆形，秋季变为橙红色，具有较高的观赏价值。花期5-6月，花色淡黄或粉红。喜光，耐半阴，适应性强，对土壤要求不严。适合庭院、公园绿化，也可作为盆景素材。萌芽力强，耐修剪，易于养护管理。</t>
@@ -36435,14 +36023,46 @@
           <t>虹越铁线莲 海德庄园</t>
         </is>
       </c>
-      <c r="C748" t="inlineStr"/>
-      <c r="D748" t="inlineStr"/>
-      <c r="E748" t="inlineStr"/>
-      <c r="F748" t="inlineStr"/>
-      <c r="G748" t="inlineStr"/>
-      <c r="H748" t="inlineStr"/>
-      <c r="I748" t="inlineStr"/>
-      <c r="J748" t="inlineStr"/>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>植物</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>种苗苗木</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>藤本</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>铁线莲</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>虹越</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr">
+        <is>
+          <t>铁线莲</t>
+        </is>
+      </c>
+      <c r="I748" t="inlineStr">
+        <is>
+          <t>海德庄园</t>
+        </is>
+      </c>
+      <c r="J748" t="inlineStr">
+        <is>
+          <t>虹越铁线莲海德庄园是一款大花铁线莲品种，花朵大而艳丽，花色通常为深紫色或蓝紫色，花期较长。该品种攀援能力强，适合用于花架、廊架、篱笆墙等垂直绿化，也可用于阳台装饰。喜阳光充足但稍耐阴，排水良好的环境。修剪方式为轻剪或中剪，保留去年老枝上的花芽。</t>
+        </is>
+      </c>
     </row>
     <row r="749">
       <c r="A749" t="inlineStr">
@@ -36477,7 +36097,7 @@
       </c>
       <c r="G749" t="inlineStr">
         <is>
-          <t>虹安</t>
+          <t>虹越</t>
         </is>
       </c>
       <c r="H749" t="inlineStr">
@@ -36487,12 +36107,12 @@
       </c>
       <c r="I749" t="inlineStr">
         <is>
-          <t>美好回忆</t>
+          <t>海德庄园</t>
         </is>
       </c>
       <c r="J749" t="inlineStr">
         <is>
-          <t>铁线莲美好回忆是虹安品牌推出的藤本花卉品种，花朵大而美丽，花色鲜艳丰富，具有较高的观赏价值。花期较长，适合种植于庭院、阳台等场所，可用于花架、拱门、栅栏等垂直绿化，喜欢阳光充足、通风良好的环境。</t>
+          <t>铁线莲是毛茛科铁线莲属的多年生藤本植物，具有攀援性，花朵大而艳丽，品种丰富。海德庄园是一个经典品种，花色优雅，观赏价值高。适合种植于庭院花架、篱笆、墙垣旁，也可盆栽观赏。喜阳光充足、排水良好的环境，耐寒性较强。春季开花，修剪时注意保留部分老枝以促进开花。</t>
         </is>
       </c>
     </row>
@@ -36532,8 +36152,6 @@
           <t>BerryBird</t>
         </is>
       </c>
-      <c r="H750" t="inlineStr"/>
-      <c r="I750" t="inlineStr"/>
       <c r="J750" t="inlineStr">
         <is>
           <t>BerryBird不锈钢手铲是一款专业的园艺种植工具，采用优质不锈钢材质，具有耐腐蚀、耐用、不易生锈的特点。手铲设计符合人体工程学，握持舒适，操作省力。适用于花盆换土、盆栽种植、小规模松土、挖坑移植等园艺操作。是家庭园艺和专业园艺工作者理想的种植辅助工具。</t>
@@ -36576,8 +36194,6 @@
           <t>马雅</t>
         </is>
       </c>
-      <c r="H751" t="inlineStr"/>
-      <c r="I751" t="inlineStr"/>
       <c r="J751" t="inlineStr">
         <is>
           <t>马雅Maya93.1多肉植物专用水溶肥，容量500ml，专为多肉植物研制的高浓度液体肥料。富含氮磷钾及微量元素配比科学，针对多肉植物喜弱酸、耐干旱的特点设计，能促进多肉叶片饱满、色泽艳丽，增强植株抗病能力。使用时需按比例稀释后浇灌或叶面喷施，适合景天科、十二卷类等各类多肉品种的日常追肥，每隔10-15天施用一次效果更佳。注意薄肥勤施，避免肥料浓度过高造成烧根。</t>
@@ -36672,8 +36288,6 @@
           <t>BerryBird</t>
         </is>
       </c>
-      <c r="H753" t="inlineStr"/>
-      <c r="I753" t="inlineStr"/>
       <c r="J753" t="inlineStr">
         <is>
           <t>BerryBird园艺帆布手提袋，采用优质帆布材质制作，质地厚实耐用，承重性强。设计简约大方，便于携带，适合在花园作业或市集采购时使用，可装纳种子、工具、小型花盆等园艺用品。帆布材质易清洗打理，可重复使用，环保实用，是园艺爱好者日常作业的好帮手。</t>
@@ -36820,8 +36434,6 @@
           <t>BerryBird</t>
         </is>
       </c>
-      <c r="H756" t="inlineStr"/>
-      <c r="I756" t="inlineStr"/>
       <c r="J756" t="inlineStr">
         <is>
           <t>BerryBird园艺手套，胭脂粉新版波点设计，时尚美观。采用优质材料制作，柔软透气，佩戴舒适，适合日常园艺操作如种植、换盆、除草等。波点图案增添趣味性，有效保护双手免受泥土、荆棘伤害，是园艺爱好者的实用防护用品。</t>
@@ -37124,8 +36736,6 @@
           <t>BerryBird</t>
         </is>
       </c>
-      <c r="H762" t="inlineStr"/>
-      <c r="I762" t="inlineStr"/>
       <c r="J762" t="inlineStr">
         <is>
           <t>BerryBird木柄修枝剪是一款专业的园艺修剪工具，采用优质木材制作手柄，握感舒适，操作省力。修枝剪刃口锋利，采用高碳钢材质，硬度高且耐腐蚀，适用于修剪枝条、花卉果木等。设计符合人体工程学，长时间使用不易疲劳。日常使用后应清洁刃口并涂抹防锈油，保持干燥存放，以延长使用寿命。适合家庭园艺、庭院绿化、果树修剪等多种场景使用。</t>
@@ -37225,7 +36835,6 @@
           <t>金桔</t>
         </is>
       </c>
-      <c r="I764" t="inlineStr"/>
       <c r="J764" t="inlineStr">
         <is>
           <t>虹安品牌金桔种苗，为多年生木本果树，株型紧凑美观。叶片浓绿光亮，革质，观赏性强。花期白色芳香，果实金黄色呈圆球形或椭圆形，成熟后可直接食用，味道酸甜可口。适合庭院地栽或阳台盆栽观赏，需阳光充足、通风良好的环境，耐寒性一般，冬季注意防寒。浇水见干见湿，生长期适当施肥有利于开花结果。</t>
@@ -37325,7 +36934,6 @@
           <t>菲油果</t>
         </is>
       </c>
-      <c r="I766" t="inlineStr"/>
       <c r="J766" t="inlineStr">
         <is>
           <t>菲油果（Feijoa）又称斐济果、凤梨番石榴，是一种常绿灌木植物，原产于南美洲。其果实呈椭圆形，皮薄果肉细腻，口感独特，带有菠萝和草莓的混合风味。菲油果树姿优美，四季常绿，花朵粉红色，具有一定观赏价值。适宜在阳光充足、排水良好的环境中种植，较耐寒，适合庭院或阳台盆栽观赏。果实在秋季成熟，可鲜食或加工成果酱、果汁等。</t>
@@ -37420,8 +37028,6 @@
           <t>ARTSTONE</t>
         </is>
       </c>
-      <c r="H768" t="inlineStr"/>
-      <c r="I768" t="inlineStr"/>
       <c r="J768" t="inlineStr">
         <is>
           <t>ARTSTONE黛卡高圆筒30花盆，灰色配色简约大方。高圆筒设计，深度充足，适合种植中型绿植、花卉或多肉植物。品牌源自韩国，以艺术感花盆著称，设计风格现代简约，兼具实用性与装饰性。盆体材质坚固耐用，适合室内外使用，可用于阳台、客厅、书房等空间装饰。</t>
@@ -37464,8 +37070,6 @@
           <t>ARTSTONE</t>
         </is>
       </c>
-      <c r="H769" t="inlineStr"/>
-      <c r="I769" t="inlineStr"/>
       <c r="J769" t="inlineStr">
         <is>
           <t>ARTSTONE正方酷边型花盆，采用优质树脂材质制作，具有现代简约的设计风格。正方形造型搭配酷边设计，外观时尚大方。32号尺寸适合种植中大型植物，灰色色调沉稳百搭，可用于室内外各种场景。花盆具有良好的排水性能，耐候性强，不易褪色，使用寿命长。适合种植多肉植物、花卉、蔬菜等各类植物，是家庭园艺和商业景观的理想选择。</t>
@@ -37508,8 +37112,6 @@
           <t>未提供</t>
         </is>
       </c>
-      <c r="H770" t="inlineStr"/>
-      <c r="I770" t="inlineStr"/>
       <c r="J770" t="inlineStr">
         <is>
           <t>BB工具是一款园艺基础工具，具体用途需要根据实际产品确定。该工具可能用于园艺种植、养护或辅助作业，1%可能表示某种浓度比例或型号标识。在园艺操作中，基础工具是进行日常养护、移栽、换盆等工作的必备用品，建议根据具体使用场景选择合适的工具型号。</t>
@@ -38020,8 +37622,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H780" t="inlineStr"/>
-      <c r="I780" t="inlineStr"/>
       <c r="J780" t="inlineStr">
         <is>
           <t>帝罗马奥真之心长条圆角盆，知名品牌园艺盆具，采用优质环保树脂材质，具有优异的耐候性和抗老化性能。长条设计搭配圆角造型，美观大方，适合种植各类小型植物、多肉或作为桌面装饰盆使用。32规格尺寸适中，便于移动和摆放，是家庭园艺和商业景观的理想选择。盆体设计注重排水透气性，有助于植物根系健康生长。</t>
@@ -38064,8 +37664,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H781" t="inlineStr"/>
-      <c r="I781" t="inlineStr"/>
       <c r="J781" t="inlineStr">
         <is>
           <t>帝罗马国际盆摩卡系列是高端园艺盆品牌，采用优质塑料材质制成，具有耐磨、耐晒、耐寒等特点。摩卡色设计典雅大方，适合室内外各种家居风格和园艺场景使用。23号尺寸适中，可用于种植中小型花卉绿植，如多肉植物、小型观叶植物等。盆底设有排水孔设计，透气性好，有利于植物根系健康生长。品牌以精湛工艺和时尚设计著称，是园艺爱好者提升居家品味的理想选择。</t>
@@ -38212,8 +37810,6 @@
           <t>BerryBird</t>
         </is>
       </c>
-      <c r="H784" t="inlineStr"/>
-      <c r="I784" t="inlineStr"/>
       <c r="J784" t="inlineStr">
         <is>
           <t>BerryBird可调节园艺修枝剪是一款专业级修剪工具，采用人体工学设计，握持舒适，操作省力。刀刃采用优质钢材，锋利耐用，适合修剪各类植物枝条。可调节功能可根据不同修剪需求调整刀口开合度，提高工作效率。适用于家庭园艺、园林维护、果树修剪等多种场景，是园艺爱好者和专业园丁的理想工具选择。</t>
@@ -38360,8 +37956,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H787" t="inlineStr"/>
-      <c r="I787" t="inlineStr"/>
       <c r="J787" t="inlineStr">
         <is>
           <t>花彩师植物高浓缩营养液（球根型）是一款专为球根类植物设计的液态肥料，浓缩配方便于稀释使用。产品富含磷钾元素及微量元素，能促进球根植物的鳞茎发育、花芽分化和根系健壮。适用于郁金香、朱顶红、百合、风信子等球根花卉的生长期和开花期。使用时按说明比例兑水浇灌，避免浓度过高造成肥害。建议每7-14天施用一次，配合适量光照可提升开花效果。</t>
@@ -38431,14 +38025,46 @@
           <t>虹越铁线莲 魔法喷泉</t>
         </is>
       </c>
-      <c r="C789" t="inlineStr"/>
-      <c r="D789" t="inlineStr"/>
-      <c r="E789" t="inlineStr"/>
-      <c r="F789" t="inlineStr"/>
-      <c r="G789" t="inlineStr"/>
-      <c r="H789" t="inlineStr"/>
-      <c r="I789" t="inlineStr"/>
-      <c r="J789" t="inlineStr"/>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>植物</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>种苗苗木</t>
+        </is>
+      </c>
+      <c r="E789" t="inlineStr">
+        <is>
+          <t>藤本</t>
+        </is>
+      </c>
+      <c r="F789" t="inlineStr">
+        <is>
+          <t>铁线莲</t>
+        </is>
+      </c>
+      <c r="G789" t="inlineStr">
+        <is>
+          <t>虹越</t>
+        </is>
+      </c>
+      <c r="H789" t="inlineStr">
+        <is>
+          <t>铁线莲</t>
+        </is>
+      </c>
+      <c r="I789" t="inlineStr">
+        <is>
+          <t>魔法喷泉</t>
+        </is>
+      </c>
+      <c r="J789" t="inlineStr">
+        <is>
+          <t>铁线莲是多年生藤本植物，有“藤本皇后”之称，枝叶繁茂，花大色艳。魔法喷泉是早花型铁线莲品种，花朵呈莲座状，花色独特，观赏价值高。适合庭院、阳台种植，可攀爬于廊架、篱笆、墙面或做花柱装饰。喜阳光充足、排水良好的环境，耐寒性较好，冬季可耐-20℃低温。浇水见干见湿，施肥遵循薄肥勤施原则。花期4-6月，修剪以弱剪为主。</t>
+        </is>
+      </c>
     </row>
     <row r="790">
       <c r="A790" t="inlineStr">
@@ -38463,28 +38089,32 @@
       </c>
       <c r="E790" t="inlineStr">
         <is>
-          <t>乔木</t>
+          <t>藤本</t>
         </is>
       </c>
       <c r="F790" t="inlineStr">
         <is>
-          <t>冬青</t>
-        </is>
-      </c>
-      <c r="G790" t="inlineStr"/>
+          <t>铁线莲</t>
+        </is>
+      </c>
+      <c r="G790" t="inlineStr">
+        <is>
+          <t>虹越</t>
+        </is>
+      </c>
       <c r="H790" t="inlineStr">
         <is>
-          <t>枸骨</t>
+          <t>铁线莲</t>
         </is>
       </c>
       <c r="I790" t="inlineStr">
         <is>
-          <t>黄金枸骨</t>
+          <t>魔法喷泉</t>
         </is>
       </c>
       <c r="J790" t="inlineStr">
         <is>
-          <t>黄金枸骨是冬青科冬青属常绿灌木，是枸骨的园艺品种。叶色金黄，革质有光泽，叶缘有刺。雌雄异株，秋冬季节结红色浆果，挂果期长，具有极高的观赏价值。喜阳光充足的环境，耐修剪，适应性强。适合庭院种植、园林绿化，也可作为盆景素材。自然形苗木保持其天然树形姿态，适合追求自然风格的园艺爱好者。</t>
+          <t>铁线莲是多年生藤本花卉，被誉为"藤本皇后"。魔法喷泉是早花大花组品种，花朵大而华丽，花色为蓝紫色重瓣，春季开花旺盛。该品种攀援能力强，适合用于花架、廊架、篱笆、墙面等垂直绿化，也可盆栽养护。喜光照充足、排水良好的环境，根系喜凉爽，夏季需适当遮荫。</t>
         </is>
       </c>
     </row>
@@ -38524,8 +38154,6 @@
           <t>BerryBird</t>
         </is>
       </c>
-      <c r="H791" t="inlineStr"/>
-      <c r="I791" t="inlineStr"/>
       <c r="J791" t="inlineStr">
         <is>
           <t>BerryBird不锈钢心形手铲是一款小巧精致的园艺种植工具，采用优质不锈钢材质，具有防锈耐腐蚀的特性。心形铲面设计独特可爱，造型小巧便于在花盆、小空间进行精细种植操作，如填土、挖坑、移苗等。人体工学手柄握感舒适，适合各类园艺爱好者在播种、换盆、日常养护等场景使用。</t>
@@ -38568,8 +38196,6 @@
           <t>成都神龙</t>
         </is>
       </c>
-      <c r="H792" t="inlineStr"/>
-      <c r="I792" t="inlineStr"/>
       <c r="J792" t="inlineStr">
         <is>
           <t>成都神龙定制营养土，容量40L。专为家庭园艺设计，富含腐殖质和有机质，透气性好、保水性强，适合各类花卉、蔬菜及绿植种植使用。可直接用于盆栽、地栽或作为土壤改良剂，能有效改善土壤结构，促进植物根系发育，提高植株生长活力。使用时可根据植物需求适量添加或混合其他介质使用。</t>
@@ -38612,8 +38238,6 @@
           <t>BerryBird</t>
         </is>
       </c>
-      <c r="H793" t="inlineStr"/>
-      <c r="I793" t="inlineStr"/>
       <c r="J793" t="inlineStr">
         <is>
           <t>BerryBird小喷壶，容量0.5L，绿色外观，设计轻巧便携。适用于家庭园艺浇水、花卉喷雾、清洁叶片等日常养护工作。小型容量设计方便精准控制浇水量，适合盆栽、小型植物及幼苗的日常护理。人体工学设计握持舒适，操作简便，是家庭园艺必备的实用工具。</t>
@@ -38656,8 +38280,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H794" t="inlineStr"/>
-      <c r="I794" t="inlineStr"/>
       <c r="J794" t="inlineStr">
         <is>
           <t>帝罗马国际盆摩卡系列，采用优质环保树脂材质制成，具有良好的透气性和排水性，适合种植各种花卉绿植。摩卡色设计典雅大方，适合室内外多种场景使用。该品牌花盆以耐用性和美观性著称，是园艺爱好者常用的品牌花盆之一。27厘米规格适合种植中小型植物或作为过渡盆使用。</t>
@@ -38700,8 +38322,6 @@
           <t>马雅</t>
         </is>
       </c>
-      <c r="H795" t="inlineStr"/>
-      <c r="I795" t="inlineStr"/>
       <c r="J795" t="inlineStr">
         <is>
           <t>马雅Maya天南星科专用液体肥料，专为龟背竹、滴水观音、绿萝、白掌等天南星科植物配制。富含氮磷钾及微量元素，易被植物吸收利用。10ml*10条独立包装设计，便于保存和使用，避免肥料污染或挥发。建议按比例稀释后浇灌或叶面喷施，可促进植株健壮生长、叶色浓绿光亮，增强抗病能力。使用时注意避开高温时段，遵循薄肥勤施原则，避免烧根。</t>
@@ -38739,7 +38359,6 @@
           <t>冬青</t>
         </is>
       </c>
-      <c r="G796" t="inlineStr"/>
       <c r="H796" t="inlineStr">
         <is>
           <t>冬青</t>
@@ -39104,8 +38723,6 @@
           <t>马雅</t>
         </is>
       </c>
-      <c r="H803" t="inlineStr"/>
-      <c r="I803" t="inlineStr"/>
       <c r="J803" t="inlineStr">
         <is>
           <t>马雅Maya91.11彩叶芋专用营养液，10ml/条，10条装。专为彩叶芋（彩叶芋/花叶芋）研发的针对性护理产品，富含彩叶芋生长所需的特殊营养元素，促进叶片色彩艳丽、纹路清晰。使用时按比例稀释后浇灌或叶面喷施，适合家庭园艺养护使用。产品需阴凉干燥处保存，避免阳光直射。</t>
@@ -39148,8 +38765,6 @@
           <t>BerryBird</t>
         </is>
       </c>
-      <c r="H804" t="inlineStr"/>
-      <c r="I804" t="inlineStr"/>
       <c r="J804" t="inlineStr">
         <is>
           <t>BerryBird不锈钢复古花枝剪，采用优质不锈钢材质，刀口锋利耐用，复古设计外观精美。适用于修剪花卉枝条、果树枝条等园艺操作，人体工学手柄设计，握持舒适省力。独特的不锈钢材质具有良好的防锈防腐性能，适合长期在户外使用，是家庭园艺和专业园艺工作者理想的修剪工具。</t>
@@ -39192,8 +38807,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H805" t="inlineStr"/>
-      <c r="I805" t="inlineStr"/>
       <c r="J805" t="inlineStr">
         <is>
           <t>帝罗马红陶储水盆，采用优质红陶材质制作，具有良好的透气性和排水性，同时盆底设计有储水功能，可有效减少浇水频率，适合种植各种室内外花卉绿植。红陶盆古朴典雅，色彩自然，能很好地衬托植物美感，是家庭园艺和商业种植的理想选择。</t>
@@ -39397,7 +39010,6 @@
           <t>绣球</t>
         </is>
       </c>
-      <c r="I809" t="inlineStr"/>
       <c r="J809" t="inlineStr">
         <is>
           <t>安镇大花绣球线下红色品种，是绣球花中的经典品种之一。大花绣球花型饱满硕大，花色丰富多变，红色品种尤为鲜艳喜庆，适合庭院种植或盆栽观赏。性喜半阴环境，不耐强光直射，喜湿润排水良好的土壤。花期通常在春末至夏季，凋谢后及时修剪残花可促进来年开花。是园林绿化和家庭园艺中广受欢迎的灌木花卉。</t>
@@ -39544,8 +39156,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H812" t="inlineStr"/>
-      <c r="I812" t="inlineStr"/>
       <c r="J812" t="inlineStr">
         <is>
           <t>园艺沸石是一种天然矿物材料，具有多孔结构，可改善土壤透气性和保水性。能调节土壤酸碱度，增加微量元素释放，促进植物根系发育。适用于多肉植物、兰花等对排水要求高的植物，也可用于扦插繁殖介质调配。通常颗粒状，便于与营养土混合使用，1.6L容量适合家庭阳台种植使用。</t>
@@ -39640,8 +39250,6 @@
           <t>领优</t>
         </is>
       </c>
-      <c r="H814" t="inlineStr"/>
-      <c r="I814" t="inlineStr"/>
       <c r="J814" t="inlineStr">
         <is>
           <t>领优养护套装家庭装是一款综合性的园艺护理产品套装，专为家庭园艺设计。套装通常包含植物生长所需的肥料、杀菌剂、杀虫剂等护理用品，可用于花卉、蔬菜、果树等多种植物的日常养护。该套装产品使用方便，适合园艺爱好者进行植物病虫害防治和营养补充，帮助植物健康生长，提高园艺种植效果。</t>
@@ -39684,8 +39292,6 @@
           <t>维特</t>
         </is>
       </c>
-      <c r="H815" t="inlineStr"/>
-      <c r="I815" t="inlineStr"/>
       <c r="J815" t="inlineStr">
         <is>
           <t>维特0-15黑泥炭是一种高品质的纯黑色泥炭土，颗粒度为0-15mm，适合作为园艺种植的基础介质。该产品具有良好的透气性和保水性，pH值适中，富含腐殖质，可直接用于花卉、蔬菜、苗木等的栽培基质。Big Bale大包装形式适合规模化种植或专业园艺场所使用，可有效降低单位成本。使用时可与其他介质材料混合调配，以达到最佳种植效果。</t>
@@ -39931,7 +39537,6 @@
           <t>络石藤</t>
         </is>
       </c>
-      <c r="G820" t="inlineStr"/>
       <c r="H820" t="inlineStr">
         <is>
           <t>络石藤</t>
@@ -39979,13 +39584,11 @@
           <t>其他灌木</t>
         </is>
       </c>
-      <c r="G821" t="inlineStr"/>
       <c r="H821" t="inlineStr">
         <is>
           <t>喷雪花</t>
         </is>
       </c>
-      <c r="I821" t="inlineStr"/>
       <c r="J821" t="inlineStr">
         <is>
           <t>喷雪花学名Spiraea thunbergii，蔷薇科绣线菊属落叶灌木。原产中国、日本等地，高1-1.5米，枝条细长拱形。早春开花，花白色、小而密集，呈雪片状分布，故名"喷雪花"。喜光耐半阴，耐寒耐旱，适应性强。园林中常用于丛植、片植于路旁、山石旁或建筑物侧，也可作花篱。是春季重要的观花灌木，花期3-4月，花开如雪，观赏价值高。养护注意保持土壤湿润，避免积水。</t>
@@ -40132,8 +39735,6 @@
           <t>BerryBird</t>
         </is>
       </c>
-      <c r="H824" t="inlineStr"/>
-      <c r="I824" t="inlineStr"/>
       <c r="J824" t="inlineStr">
         <is>
           <t>BerryBird树叶手铲是专为园艺爱好者设计的种植工具，采用优质钢材制作，树叶造型独特美观，握感舒适。2025世界花园大会纪念版，限量发行，具有收藏价值。适用于盆栽换土、小型挖掘、移栽种苗等园艺操作，轻便耐用，适合家庭园艺使用。使用后建议用干布擦拭干净，避免潮湿环境存放以防止生锈。</t>
@@ -40176,8 +39777,6 @@
           <t>BerryBird</t>
         </is>
       </c>
-      <c r="H825" t="inlineStr"/>
-      <c r="I825" t="inlineStr"/>
       <c r="J825" t="inlineStr">
         <is>
           <t>BerryBird木柄尖头花枝剪是一款专业园艺修剪工具，采用优质木材手柄，手感舒适，防滑耐用。尖头设计精准锋利，适合精细修剪花枝、果枝及细小枝条。人体工学设计减轻手部疲劳，提高修剪效率。适用于花卉、果树、灌木等多种植物的日常养护与整形修剪。</t>
@@ -40220,8 +39819,6 @@
           <t>爱好</t>
         </is>
       </c>
-      <c r="H826" t="inlineStr"/>
-      <c r="I826" t="inlineStr"/>
       <c r="J826" t="inlineStr">
         <is>
           <t>爱好环保系列圆型托盘，采用环保材质制作，专为花盆配套使用。白色设计简洁大方，XS尺寸适合小型花盆底部承托。托盘可有效防止浇水时水分外溢，保护桌面地面清洁，同时收集多余水分保持环境整洁。结实耐用，易于清洁，是家庭园艺和阳台种植的理想配件选择。</t>
@@ -40420,8 +40017,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H830" t="inlineStr"/>
-      <c r="I830" t="inlineStr"/>
       <c r="J830" t="inlineStr">
         <is>
           <t>帝罗马托斯卡尼亚方型托盘是一款经典的陶土材质园艺配件，产自意大利著名陶盆产区。方形设计适合搭配同系列方形花盆使用，托盘可有效承接多余水分，防止浇水时弄湿地面，同时保持植物根系透气。陶土材质具有良好的排水性和耐久性，适合室内外各种园艺场景使用。</t>
@@ -40464,8 +40059,6 @@
           <t>北欧</t>
         </is>
       </c>
-      <c r="H831" t="inlineStr"/>
-      <c r="I831" t="inlineStr"/>
       <c r="J831" t="inlineStr">
         <is>
           <t>北欧风格简约设计花盆，线条流畅造型时尚，适合现代家居装饰。特大号尺寸适合种植大型观叶植物或小型灌木，如琴叶榕、龟背竹等，可作为室内客厅或阳台焦点装饰。花盆材质坚固耐用，排水设计合理，便于植物根系呼吸和水分管理。搭配各式绿植能营造自然清新的居家氛围。</t>
@@ -40503,9 +40096,6 @@
           <t>水溶肥</t>
         </is>
       </c>
-      <c r="G832" t="inlineStr"/>
-      <c r="H832" t="inlineStr"/>
-      <c r="I832" t="inlineStr"/>
       <c r="J832" t="inlineStr">
         <is>
           <t>水溶性肥料是一种可直接溶于水的速效肥料，氮磷钾比例均衡（20-20-20），添加了TE微量元素（铁、锌、锰、铜、硼、钼等），养分全面、配比合理。适用于各类花卉、蔬菜、果树等植物的追肥使用，可通过浇灌、滴灌、叶面喷施等方式施用。使用时应按说明稀释，避免浓度过高造成肥害。建议在植物生长期每7-14天施用一次，薄肥勤施效果更佳。注意密封保存，阴凉干燥处储存。</t>
@@ -40548,8 +40138,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H833" t="inlineStr"/>
-      <c r="I833" t="inlineStr"/>
       <c r="J833" t="inlineStr">
         <is>
           <t>帝罗马经典宽边高圆型花盆，采用白陶材质搭配白条纹设计，呈现经典意式陶盆风格。盆器规格为22cm，圆型深盆设计搭配宽边口沿，提供良好的稳定性和美观度。陶土材质透气性好，排水性能优良，适合种植各类草本花卉、灌木或小型乔木。可用于室内外园艺场景，装饰性与实用性兼具。</t>
@@ -40951,13 +40539,11 @@
           <t>其他灌木</t>
         </is>
       </c>
-      <c r="G841" t="inlineStr"/>
       <c r="H841" t="inlineStr">
         <is>
           <t>腊梅</t>
         </is>
       </c>
-      <c r="I841" t="inlineStr"/>
       <c r="J841" t="inlineStr">
         <is>
           <t>腊梅是冬季开花的落叶灌木，原产中国，花黄色或淡黄色，带有浓郁香气是其最大特色。株高3-5米，枝条灰褐色，单叶对生。性喜阳光充足、耐寒耐旱，对土壤要求不严，但以疏松排水良好的土壤为佳。花期在12月至次年2月，正是寒冬时节绽放，故有“冬日梅花”之称。主要用于庭院、园林观赏，也可作为切花材料。养护较为简单，冬季需注意防风，夏季适当修剪促进新枝生长。</t>
@@ -41651,14 +41237,41 @@
           <t>HY-皋月杜鹃“白琳”</t>
         </is>
       </c>
-      <c r="C855" t="inlineStr"/>
-      <c r="D855" t="inlineStr"/>
-      <c r="E855" t="inlineStr"/>
-      <c r="F855" t="inlineStr"/>
-      <c r="G855" t="inlineStr"/>
-      <c r="H855" t="inlineStr"/>
-      <c r="I855" t="inlineStr"/>
-      <c r="J855" t="inlineStr"/>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>植物</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>种苗苗木</t>
+        </is>
+      </c>
+      <c r="E855" t="inlineStr">
+        <is>
+          <t>灌木</t>
+        </is>
+      </c>
+      <c r="F855" t="inlineStr">
+        <is>
+          <t>杜鹃</t>
+        </is>
+      </c>
+      <c r="H855" t="inlineStr">
+        <is>
+          <t>杜鹃</t>
+        </is>
+      </c>
+      <c r="I855" t="inlineStr">
+        <is>
+          <t>白琳</t>
+        </is>
+      </c>
+      <c r="J855" t="inlineStr">
+        <is>
+          <t>皋月杜鹃"白琳"是日系杜鹃花品种，花朵通常为白色或粉白色，花型秀气，花期在5-6月。属于低矮灌木，株型紧凑，适合庭院地栽或盆栽观赏。喜酸性土壤，喜半阴环境，忌暴晒。开花时节花量丰富，具有较高的观赏价值，是阳台和花园中常见的观赏灌木。养护时需保持土壤湿润，夏季注意遮荫，冬季适当防寒。</t>
+        </is>
+      </c>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
@@ -41673,34 +41286,42 @@
       </c>
       <c r="C856" t="inlineStr">
         <is>
-          <t>非植</t>
+          <t>植物</t>
         </is>
       </c>
       <c r="D856" t="inlineStr">
         <is>
-          <t>工具</t>
+          <t>种苗苗木</t>
         </is>
       </c>
       <c r="E856" t="inlineStr">
         <is>
-          <t>种植工具</t>
+          <t>灌木</t>
         </is>
       </c>
       <c r="F856" t="inlineStr">
         <is>
-          <t>其他种植工具</t>
+          <t>杜鹃</t>
         </is>
       </c>
       <c r="G856" t="inlineStr">
         <is>
-          <t>BerryBird</t>
-        </is>
-      </c>
-      <c r="H856" t="inlineStr"/>
-      <c r="I856" t="inlineStr"/>
+          <t>HY</t>
+        </is>
+      </c>
+      <c r="H856" t="inlineStr">
+        <is>
+          <t>杜鹃</t>
+        </is>
+      </c>
+      <c r="I856" t="inlineStr">
+        <is>
+          <t>白琳</t>
+        </is>
+      </c>
       <c r="J856" t="inlineStr">
         <is>
-          <t>BerryBird不锈钢鹤嘴锄是一款高品质园艺工具，采用优质不锈钢材质，具有耐腐蚀、耐磨损、坚固耐用的特点。鹤嘴锄设计独特，锄头呈尖嘴状，适合用于挖掘、疏松土壤、除草、移栽幼苗等园艺作业。不锈钢材质确保工具易于清洁保养，长期使用不易生锈。人体工学手柄设计，握持舒适省力，提高园艺工作效率。适用于家庭园艺、庭院种植、苗圃作业等多种场景，是园艺爱好者必备的基础工具之一。</t>
+          <t>皋月杜鹃是杜鹃花科的重要品类，白琳为其精选品种。该品种为灌木植物，株型紧凑，叶片翠绿有光泽，花朵洁白素雅，花期通常在春季。花量大，观赏价值高，适合庭院种植或盆栽观赏。喜半阴环境，适宜疏松肥沃、排水良好的酸性土壤，需保持湿润但忌积水。冬季注意防寒修剪，可适当施肥促进生长。</t>
         </is>
       </c>
     </row>
@@ -41740,8 +41361,6 @@
           <t>马雅Maya</t>
         </is>
       </c>
-      <c r="H857" t="inlineStr"/>
-      <c r="I857" t="inlineStr"/>
       <c r="J857" t="inlineStr">
         <is>
           <t>马雅Maya15矿物有机肥采用缓释颗粒工艺，将有机成分与矿物元素科学配比，养分释放平稳持久，避免烧根风险。产品富含腐植酸和微量元素，可改善土壤结构，增加土壤透气性和保水性。适用于家庭园艺各类盆栽花卉、蔬菜、果树及庭院植物，尤其适合生长期较长的多年生植物使用。315g包装便于家庭使用，颗粒状便于均匀撒施，配合浇水即可缓慢释放肥效，持效期可达2-3个月。使用时建议按照说明书用量施用，避免过量。</t>
@@ -42304,8 +41923,6 @@
           <t>嘉伯瑞</t>
         </is>
       </c>
-      <c r="H868" t="inlineStr"/>
-      <c r="I868" t="inlineStr"/>
       <c r="J868" t="inlineStr">
         <is>
           <t>嘉伯瑞梅卡系列花盆，规格20寸（约50cm口径），泥红色调呈现出自然质朴的视觉效果。该系列花盆采用优质树脂材质，具有轻便耐用、抗晒防老化、排水透气等特点，适合室内外各种花卉绿植栽培使用。花盆设计简约大方，可搭配多种装修风格的阳台、庭院或客厅空间，是家庭园艺爱好者的实用选择。</t>
@@ -42348,8 +41965,6 @@
           <t>BerryBird</t>
         </is>
       </c>
-      <c r="H869" t="inlineStr"/>
-      <c r="I869" t="inlineStr"/>
       <c r="J869" t="inlineStr">
         <is>
           <t>BerryBird不锈钢灌木耙是一款专业园艺工具，采用优质不锈钢材质精制而成，具有防锈耐腐蚀、坚固耐用的特点。耙齿设计合理，可有效松土、碎土、清理杂草及整理植株周围土壤。适用于花园、菜园、果园等多种园艺场景，是种植和养护灌木及多年生植物的理想辅助工具。人性化手柄设计，握持舒适，使用省力，提升园艺工作效率。</t>
@@ -42387,7 +42002,6 @@
           <t>其他灌木</t>
         </is>
       </c>
-      <c r="G870" t="inlineStr"/>
       <c r="H870" t="inlineStr">
         <is>
           <t>石斑木</t>
@@ -42492,8 +42106,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H872" t="inlineStr"/>
-      <c r="I872" t="inlineStr"/>
       <c r="J872" t="inlineStr">
         <is>
           <t>蛭石是一种轻质、多孔的硅酸盐矿物材料，具有优异的保水性和透气性。在园艺中广泛用作土壤改良剂，可改善土壤结构，促进根系发育。50L大包装适合家庭园艺、育苗、扦插繁殖等场景使用。蛭石本身无菌无毒，pH值接近中性，适合各类植物生长需求。可单独使用或与泥炭、椰糠等混合配制成优质栽培介质。</t>
@@ -42531,7 +42143,6 @@
           <t>其他灌木</t>
         </is>
       </c>
-      <c r="G873" t="inlineStr"/>
       <c r="H873" t="inlineStr">
         <is>
           <t>枸骨</t>
@@ -42631,13 +42242,11 @@
           <t>络石藤</t>
         </is>
       </c>
-      <c r="G875" t="inlineStr"/>
       <c r="H875" t="inlineStr">
         <is>
           <t>络石藤</t>
         </is>
       </c>
-      <c r="I875" t="inlineStr"/>
       <c r="J875" t="inlineStr">
         <is>
           <t>络石藤是夹竹桃科络石属的常绿藤本植物，又名风车茉莉。叶片革质对生，呈椭圆形至卵状披针形，边缘全缘。春季开花，花白色如风车，具有芳香气味。攀援能力强，适合做立体绿化、廊架装饰、墙面立体绿化等。喜温暖湿润环境，耐半阴，适应性较强，是优良的园林藤本植物品种。</t>
@@ -42883,7 +42492,6 @@
           <t>绣球</t>
         </is>
       </c>
-      <c r="G880" t="inlineStr"/>
       <c r="H880" t="inlineStr">
         <is>
           <t>绣球</t>
@@ -42936,8 +42544,6 @@
           <t>马雅</t>
         </is>
       </c>
-      <c r="H881" t="inlineStr"/>
-      <c r="I881" t="inlineStr"/>
       <c r="J881" t="inlineStr">
         <is>
           <t>马雅100矿物有机肥是一款通用型肥料产品，净含量160g。该肥料融合矿物营养与有机成分，肥效温和持久，适合各类家庭园艺植物使用。可用于蔬菜、花卉、果树、观叶植物等的基肥或追肥施用。使用时建议根据植物种类和生长阶段适量施用，避免过量造成肥害。适合阳台园艺、室内绿植及庭院花卉养护使用。</t>
@@ -42980,8 +42586,6 @@
           <t>嘉伯瑞</t>
         </is>
       </c>
-      <c r="H882" t="inlineStr"/>
-      <c r="I882" t="inlineStr"/>
       <c r="J882" t="inlineStr">
         <is>
           <t>嘉伯瑞梵谷圆型仿陶花盆，采用优质仿陶工艺制作，外观呈现自然红陶色泽，质感逼真，兼具美观性与实用性。圆型设计适合种植各类花卉植物，底部设有排水孔，透气性好，便于植物根系生长。25号尺寸适合中小型植物盆栽使用，是家庭园艺、室内绿植装饰的理想选择。</t>
@@ -43024,8 +42628,6 @@
           <t>HB-101</t>
         </is>
       </c>
-      <c r="H883" t="inlineStr"/>
-      <c r="I883" t="inlineStr"/>
       <c r="J883" t="inlineStr">
         <is>
           <t>HB-101植物活力液是一种天然植物提取物制剂，主要成分来自松、枞、柏等植物精华。可促进植物生根、增强抗逆性、提高光合作用效率。适用于花卉、蔬菜、果树等各类植物的叶面喷施或灌根使用。产品规格为6ml×3瓶装，便于稀释使用。建议按照1:1000比例兑水使用，每7-10天施用一次效果更佳。广泛用于花卉栽培、蔬菜种植、果树管理等领域，是家庭园艺和专业种植常用的植物生长促进剂。</t>
@@ -43043,14 +42645,46 @@
           <t>虹安铁线莲 蓝色沙龙舞</t>
         </is>
       </c>
-      <c r="C884" t="inlineStr"/>
-      <c r="D884" t="inlineStr"/>
-      <c r="E884" t="inlineStr"/>
-      <c r="F884" t="inlineStr"/>
-      <c r="G884" t="inlineStr"/>
-      <c r="H884" t="inlineStr"/>
-      <c r="I884" t="inlineStr"/>
-      <c r="J884" t="inlineStr"/>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>植物</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>种苗苗木</t>
+        </is>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>藤本</t>
+        </is>
+      </c>
+      <c r="F884" t="inlineStr">
+        <is>
+          <t>铁线莲</t>
+        </is>
+      </c>
+      <c r="G884" t="inlineStr">
+        <is>
+          <t>虹安</t>
+        </is>
+      </c>
+      <c r="H884" t="inlineStr">
+        <is>
+          <t>铁线莲</t>
+        </is>
+      </c>
+      <c r="I884" t="inlineStr">
+        <is>
+          <t>蓝色沙龙舞</t>
+        </is>
+      </c>
+      <c r="J884" t="inlineStr">
+        <is>
+          <t>虹安铁线莲蓝色沙龙舞是一款经典的藤本花卉品种，以其优雅的蓝色花朵著称，花型呈沙龙舞般的立体美感。该品种具有较强的攀援能力，适合用于花架、拱门、篱笆等垂直绿化装饰。铁线莲喜阳光充足但忌强光直射，耐寒性较强，生长期间需保持土壤湿润但排水良好，建议使用疏松肥沃的土壤种植，春季萌芽前可进行适当修剪以促进新枝萌发和花量增加。</t>
+        </is>
+      </c>
     </row>
     <row r="885">
       <c r="A885" t="inlineStr">
@@ -43075,12 +42709,12 @@
       </c>
       <c r="E885" t="inlineStr">
         <is>
-          <t>多年生草本</t>
+          <t>藤本</t>
         </is>
       </c>
       <c r="F885" t="inlineStr">
         <is>
-          <t>其他多年生草本</t>
+          <t>铁线莲</t>
         </is>
       </c>
       <c r="G885" t="inlineStr">
@@ -43090,17 +42724,17 @@
       </c>
       <c r="H885" t="inlineStr">
         <is>
-          <t>百子莲</t>
+          <t>铁线莲</t>
         </is>
       </c>
       <c r="I885" t="inlineStr">
         <is>
-          <t>小旋风</t>
+          <t>蓝色沙龙舞</t>
         </is>
       </c>
       <c r="J885" t="inlineStr">
         <is>
-          <t>百子莲是石蒜科百子莲属多年生草本植物，原产南非，又称紫君子兰、蓝花君子兰。"小旋风"是进口改良品种，株型紧凑，花茎粗壮，花朵呈漏斗状，色彩艳丽丰富，盛花期在夏季。耐热耐寒，适应性强，适合庭院花境、岩石园或盆栽观赏。喜阳光充足、排水良好的环境，浇水见干见湿，冬季注意控水防冻。</t>
+          <t>铁线莲是毛茛科铁线莲属的多年生藤本植物，被誉为“藤本皇后”。蓝色沙龙舞是该品种的简称，花朵呈蓝紫色系，花瓣质感独特，观赏价值高。该品种攀援能力强，适合用于花墙、花柱、拱门、篱笆等垂直绿化。喜阳光充足、通风良好的环境，土壤需疏松肥沃、排水良好。耐寒性较好，但夏季需注意避免积水。春季萌芽前可进行修剪，促进新枝萌发和开花。</t>
         </is>
       </c>
     </row>
@@ -43140,8 +42774,6 @@
           <t>ARTSTONE</t>
         </is>
       </c>
-      <c r="H886" t="inlineStr"/>
-      <c r="I886" t="inlineStr"/>
       <c r="J886" t="inlineStr">
         <is>
           <t>ARTSTONE正方酷边型花盆，采用简约现代设计理念，黑色配色低调大方，适合各种家居和园艺场景。正方形造型节省空间，酷边设计增添时尚感。材质坚固耐用，排水透气性良好，适用于室内外盆栽种植，可种植多肉、绿植、花卉等多种植物，是家庭园艺和商业空间的理想选择。</t>
@@ -43288,8 +42920,6 @@
           <t>马雅</t>
         </is>
       </c>
-      <c r="H889" t="inlineStr"/>
-      <c r="I889" t="inlineStr"/>
       <c r="J889" t="inlineStr">
         <is>
           <t>马雅Maya93.1多肉植物专用营养液，每条10ml，共10条装。采用科学配方，专为多肉植物研制，富含氮磷钾及微量元素，稀释后浇灌使用。能够促进多肉植物根系发育、叶片肥厚、颜色艳丽，提高植物抗病能力。使用时按说明比例兑水，避免浓度过高灼伤植物。适合景天科、番杏科、十二卷等多肉品种的日常养护。建议在生长期（春秋季）每月使用1-2次，夏季高温和冬季低温时可减少使用频率。</t>
@@ -43644,8 +43274,6 @@
           <t>马雅</t>
         </is>
       </c>
-      <c r="H896" t="inlineStr"/>
-      <c r="I896" t="inlineStr"/>
       <c r="J896" t="inlineStr">
         <is>
           <t>马雅Maya11.1缓释颗粒是一款专为天南星科植物设计的缓释肥料，净含量315g。采用优质原料配比，氮磷钾比例科学合理，能够为龟背竹、绿萝、滴水观音、琴叶榕等天南星科植物提供持久的营养供给。缓释技术使肥效温和持久，避免烧根风险，使用方便省心，适合家庭园艺和室内绿植养护。使用时均匀撒施于盆土表面，轻浇清水即可，建议每隔2-3个月追施一次。</t>
@@ -43688,8 +43316,6 @@
           <t>领优</t>
         </is>
       </c>
-      <c r="H897" t="inlineStr"/>
-      <c r="I897" t="inlineStr"/>
       <c r="J897" t="inlineStr">
         <is>
           <t>领优杀菌剂家庭装是一款家庭园艺专用杀菌剂产品，主要用于预防和治疗花卉、蔬菜等植物的真菌性疾病，如白粉病、灰霉病、锈病等。产品采用家庭装设计，方便家庭园艺爱好者使用，操作简单，安全可靠。使用时需按照说明书比例稀释后均匀喷施于植物叶面，建议在发病初期或高发期前预防使用，效果更佳。</t>
@@ -43732,8 +43358,6 @@
           <t>爱丽思</t>
         </is>
       </c>
-      <c r="H898" t="inlineStr"/>
-      <c r="I898" t="inlineStr"/>
       <c r="J898" t="inlineStr">
         <is>
           <t>爱丽思盆是一种高品质的园艺花盆品牌，采用优质塑料材质，轻便耐用，排水透气性好。适合种植各种花卉、蔬菜和小型植物。规格中的1%可能指产品型号或尺寸等级。该品牌花盆广泛应用于家庭园艺、阳台种植和商业花卉栽培，具有良好的耐候性和使用寿命。</t>
@@ -43776,8 +43400,6 @@
           <t>BerryBird</t>
         </is>
       </c>
-      <c r="H899" t="inlineStr"/>
-      <c r="I899" t="inlineStr"/>
       <c r="J899" t="inlineStr">
         <is>
           <t>BerryBird园艺垫是一款实用的园艺配件，尺寸为120*73cm，采用防水耐磨材质制成。主要用于保护地面、隔离土壤，防止在换盆、施肥或修剪时弄脏地面。表面易清洁，可反复使用，适合室内外园艺操作使用，是园艺爱好者进行盆栽管理时的得力助手。</t>
@@ -43820,8 +43442,6 @@
           <t>BerryBird</t>
         </is>
       </c>
-      <c r="H900" t="inlineStr"/>
-      <c r="I900" t="inlineStr"/>
       <c r="J900" t="inlineStr">
         <is>
           <t>BerryBird不锈钢女士盆栽勺是专为女性园艺爱好者设计的轻便种植工具。采用优质不锈钢材质，耐腐蚀、耐磨损，使用寿命长。勺身设计符合人体工程学，握持舒适，适合用于盆栽种植、松土、施肥等日常园艺操作。小巧精致，便于收纳和携带，是家庭园艺的实用辅助工具。</t>
@@ -43916,8 +43536,6 @@
           <t>马雅</t>
         </is>
       </c>
-      <c r="H902" t="inlineStr"/>
-      <c r="I902" t="inlineStr"/>
       <c r="J902" t="inlineStr">
         <is>
           <t>马雅Maya91.1天南星科专用肥料，容量500ml，专为天南星科植物（如龟背竹、绿萝、春羽、花烛、白掌、马蹄莲等）配制的营养液。该产品根据天南星科植物的生长需求特点，补充氮磷钾及微量元素，促进叶片生长，增强植株抗性。使用时按比例稀释后浇灌或叶面喷施，适合家庭园艺养护天南星科观叶植物。建议存放在阴凉干燥处，避免阳光直射。</t>
@@ -43960,8 +43578,6 @@
           <t>ARTSTONE</t>
         </is>
       </c>
-      <c r="H903" t="inlineStr"/>
-      <c r="I903" t="inlineStr"/>
       <c r="J903" t="inlineStr">
         <is>
           <t>ARTSTONE克莱尔圆型套盆13黑色是一款高品质的室内外通用花盆，采用优质树脂材质制成，具有防腐蚀、耐老化、坚固耐用的特点。圆型设计简洁大方，黑色外观时尚百搭，适合各种家居风格。套盆设计方便更换植物，适合种植各类花卉绿植，如多肉植物、小型观叶植物等。底部设有排水孔设计，防止积水烂根，是家庭园艺的理想选择。</t>
@@ -44259,7 +43875,6 @@
           <t>女贞</t>
         </is>
       </c>
-      <c r="G909" t="inlineStr"/>
       <c r="H909" t="inlineStr">
         <is>
           <t>女贞</t>
@@ -44307,7 +43922,6 @@
           <t>枫树</t>
         </is>
       </c>
-      <c r="G910" t="inlineStr"/>
       <c r="H910" t="inlineStr">
         <is>
           <t>枫树</t>
@@ -44355,7 +43969,6 @@
           <t>冬青</t>
         </is>
       </c>
-      <c r="G911" t="inlineStr"/>
       <c r="H911" t="inlineStr">
         <is>
           <t>冬青</t>
@@ -44408,8 +44021,6 @@
           <t>BerryBird</t>
         </is>
       </c>
-      <c r="H912" t="inlineStr"/>
-      <c r="I912" t="inlineStr"/>
       <c r="J912" t="inlineStr">
         <is>
           <t>BerryBird不锈钢手刮锄是一款实用的园艺除草松土工具，采用优质不锈钢材质，具有耐腐蚀、不生锈、坚固耐用的特点。手刮锄设计符合人体工程学，便于握持操作，可轻松刮除杂草、松动土壤，适用于花园、菜园、果园等多种园艺场景的土壤管理工作。不锈钢材质确保了工具的持久耐用性，是园艺爱好者必备的基础种植工具。</t>
@@ -44452,8 +44063,6 @@
           <t>维特</t>
         </is>
       </c>
-      <c r="H913" t="inlineStr"/>
-      <c r="I913" t="inlineStr"/>
       <c r="J913" t="inlineStr">
         <is>
           <t>维特纯泥炭是一种高品质的园艺栽培介质，规格为20-40mm（颗粒大小），以Big Bale大包装形式销售。纯泥炭具有良好的保水性、透气性和酸碱缓冲能力，是花卉、蔬菜育苗和盆栽的理想基质。可单独使用或与其他介质混合，适用于各种园艺植物的种植，能够提供良好的根系生长环境。储存时应保持干燥，避免雨淋受潮。</t>
@@ -44496,8 +44105,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H914" t="inlineStr"/>
-      <c r="I914" t="inlineStr"/>
       <c r="J914" t="inlineStr">
         <is>
           <t>帝罗马托斯卡尼亚长条圆角托盘，是意大利知名园艺品牌Terrazzo系列的经典配件产品。采用优质树脂材质，具有防水防腐、耐晒耐寒的特性。托盘设计为长条形配圆角造型，简约大方，可搭配帝罗马托斯卡尼亚系列花盆使用。35代表托盘长度为35厘米，尺寸适中，适合用于阳台、露台或室内花园，用于承接花盆底部的渗水，保持地面整洁，同时防止水分直接接触地面造成污染。该托盘底部配有排水孔设计，可有效排水，避免积水。是园艺种植中实用且美观的配件产品。</t>
@@ -44743,7 +44350,6 @@
           <t>高杆</t>
         </is>
       </c>
-      <c r="G919" t="inlineStr"/>
       <c r="H919" t="inlineStr">
         <is>
           <t>石斑木</t>
@@ -45056,8 +44662,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H925" t="inlineStr"/>
-      <c r="I925" t="inlineStr"/>
       <c r="J925" t="inlineStr">
         <is>
           <t>花彩师天南星科专业介质是专为天南星科植物研发的种植基质，适用于龟背竹、绿萝、滴水观音、观音莲等天南星科观叶植物。该介质采用优质泥炭、珍珠岩、椰糠等原材料科学配比，具有良好的透气性、排水性和保水性，能为植物根系提供适宜的生长环境，促进养分吸收，适合室内观叶植物盆栽使用。</t>
@@ -45100,8 +44704,6 @@
           <t>爱贝施</t>
         </is>
       </c>
-      <c r="H926" t="inlineStr"/>
-      <c r="I926" t="inlineStr"/>
       <c r="J926" t="inlineStr">
         <is>
           <t>爱贝施缓释肥料14-14-14+TE是一款均衡型缓释肥料，氮磷钾比例均为14%，并添加了植物所需的微量元素（TE），可满足植物全生长周期的营养需求。采用缓释技术，肥效可持续释放3-4个月，减少施肥次数，省时省力。适用于家庭园艺中的花卉、蔬菜、果树等多种植物。使用时需均匀撒施于盆土表面或浅埋于土中，避免直接接触根系，适合基肥和追肥使用。</t>
@@ -45196,8 +44798,6 @@
           <t>领优崇绿</t>
         </is>
       </c>
-      <c r="H928" t="inlineStr"/>
-      <c r="I928" t="inlineStr"/>
       <c r="J928" t="inlineStr">
         <is>
           <t>领优崇绿100ml杀虫剂是一款家庭园艺专用杀虫产品，主要用于防治蚜虫、青虫、蚊蝇等多种常见害虫。产品规格为100ml，适合家庭阳台花卉、蔬菜等植物的害虫防治使用。产品为喷雾型，使用方便，可直接喷施于植物叶面及害虫活动区域。注意使用时需按照说明书比例稀释，避免高温时段施用，确保通风良好环境下操作。</t>
@@ -45240,8 +44840,6 @@
           <t>领优</t>
         </is>
       </c>
-      <c r="H929" t="inlineStr"/>
-      <c r="I929" t="inlineStr"/>
       <c r="J929" t="inlineStr">
         <is>
           <t>领优杀螨剂家庭装是一款专为家庭园艺设计的植物保护用品，主要用于防治花卉、蔬菜、果树等植物上的螨虫类害虫（如红蜘蛛、黄蜘蛛等）。该产品具有高效低毒、杀螨迅速、持效期长等特点，适用于月季、茉莉、杜鹃、多肉、番茄、黄瓜等多种室内外观赏植物和蔬果作物。使用时需按照说明书比例稀释后均匀喷施叶面正反面及枝干，间隔7-10天再次施用效果更佳。建议存放在阴凉干燥处，避免儿童接触。</t>
@@ -45336,8 +44934,6 @@
           <t>成都神龙</t>
         </is>
       </c>
-      <c r="H931" t="inlineStr"/>
-      <c r="I931" t="inlineStr"/>
       <c r="J931" t="inlineStr">
         <is>
           <t>成都神龙番茄种植配方营养土是专为番茄种植设计的栽培介质，容量60L，采用简装包装。配方科学配比，富含番茄生长所需的有机质和营养元素，透气性和保水性良好，有利于番茄根系发育和植株健壮生长。适用于家庭菜园、阳台盆栽番茄种植，使用时可根据需要适量添加底肥，注意保持土壤湿润但避免积水，定期追肥以满足番茄不同生长阶段的营养需求。</t>
@@ -45380,8 +44976,6 @@
           <t>嘉伯瑞</t>
         </is>
       </c>
-      <c r="H932" t="inlineStr"/>
-      <c r="I932" t="inlineStr"/>
       <c r="J932" t="inlineStr">
         <is>
           <t>嘉伯瑞四叶草托小号花盆，采用经典四叶草造型设计，烟煤灰色色调沉稳大气，增添园艺格调。小号规格适合桌面或小型植物使用，便于摆放和移动。品牌嘉伯瑞专注于园艺盆器设计，产品做工精细，耐用性好。适用于多肉、小型草本植物或桌面绿植栽培，可有效承接浇水溢出的水分，保持桌面清洁。搭配花彩师系列使用，整体视觉效果协调统一。</t>
@@ -45424,8 +45018,6 @@
           <t>君沐</t>
         </is>
       </c>
-      <c r="H933" t="inlineStr"/>
-      <c r="I933" t="inlineStr"/>
       <c r="J933" t="inlineStr">
         <is>
           <t>君沐0.4m浇水把手是一款园艺浇水工具配件，采用优质材料制作，长度为0.4米，设计轻巧便携。该把手可与浇水壶或其他浇水设备配合使用，延长浇水范围，方便对高处或远距离植物进行浇水作业。适用于阳台花卉、窗台盆栽等浇水场景，是家庭园艺日常管理的实用辅助工具。</t>
@@ -45443,14 +45035,46 @@
           <t>虹安果树 G丑八怪（不知火）</t>
         </is>
       </c>
-      <c r="C934" t="inlineStr"/>
-      <c r="D934" t="inlineStr"/>
-      <c r="E934" t="inlineStr"/>
-      <c r="F934" t="inlineStr"/>
-      <c r="G934" t="inlineStr"/>
-      <c r="H934" t="inlineStr"/>
-      <c r="I934" t="inlineStr"/>
-      <c r="J934" t="inlineStr"/>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>植物</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>种苗苗木</t>
+        </is>
+      </c>
+      <c r="E934" t="inlineStr">
+        <is>
+          <t>乔木</t>
+        </is>
+      </c>
+      <c r="F934" t="inlineStr">
+        <is>
+          <t>其他乔木</t>
+        </is>
+      </c>
+      <c r="G934" t="inlineStr">
+        <is>
+          <t>虹安果树</t>
+        </is>
+      </c>
+      <c r="H934" t="inlineStr">
+        <is>
+          <t>果树</t>
+        </is>
+      </c>
+      <c r="I934" t="inlineStr">
+        <is>
+          <t>丑八怪（不知火）</t>
+        </is>
+      </c>
+      <c r="J934" t="inlineStr">
+        <is>
+          <t>虹安果树品牌的丑八怪（不知火）果苗，为柑橘类果树品种。不知火又名丑橘，果皮粗糙呈橙黄色，果肉清脆多汁，甜度高且带有独特风味。该品种适应性强，耐寒性较好，适合我国南方大部分地区种植。树势中等偏旺，成年后为乔木形态。种植时应选择排水良好的土壤，保持充足光照，定期施肥修剪，以促进果实品质和产量。盛果期亩产可达2000-3000公斤，经济效益较好。</t>
+        </is>
+      </c>
     </row>
     <row r="935">
       <c r="A935" t="inlineStr">
@@ -45475,32 +45099,32 @@
       </c>
       <c r="E935" t="inlineStr">
         <is>
-          <t>多年生草本</t>
+          <t>灌木</t>
         </is>
       </c>
       <c r="F935" t="inlineStr">
         <is>
-          <t>其他多年生草本</t>
+          <t>其他灌木</t>
         </is>
       </c>
       <c r="G935" t="inlineStr">
         <is>
-          <t>FJGD</t>
+          <t>虹安果树</t>
         </is>
       </c>
       <c r="H935" t="inlineStr">
         <is>
-          <t>其他多年生草本</t>
+          <t>柑橘</t>
         </is>
       </c>
       <c r="I935" t="inlineStr">
         <is>
-          <t>甜心</t>
+          <t>不知火</t>
         </is>
       </c>
       <c r="J935" t="inlineStr">
         <is>
-          <t>该商品为FJGD品牌下的甜心系列多年生草本植物种苗。商品名中包含"甜心"字样，通常指代特定的花卉品种，具体形态特征因实际商品而异。作为多年生草本植物，该类商品一般具有多年生长周期，管理相对简便，适合家庭园艺种植。购买前建议了解具体品种的生长习性、开花季节及养护要求。</t>
+          <t>不知火又名丑橘、丑八怪，是日本培育的杂交柑橘品种。果实呈扁圆形，果皮橙黄色，表面粗糙有突起，果肉脆嫩多汁，甜度高且易剥皮。该品种适应性强，耐寒性较好，适合我国南方地区种植。树势中等，萌芽力和成枝力较强，栽培管理相对简单。苗木定植后2-3年可结果，盛果期亩产可达2000-3000公斤。需注意防治炭疽病、脚腐病等常见病害。</t>
         </is>
       </c>
     </row>
@@ -45535,7 +45159,6 @@
           <t>茶花</t>
         </is>
       </c>
-      <c r="G936" t="inlineStr"/>
       <c r="H936" t="inlineStr">
         <is>
           <t>茶梅</t>
@@ -45588,8 +45211,6 @@
           <t>美乐棵</t>
         </is>
       </c>
-      <c r="H937" t="inlineStr"/>
-      <c r="I937" t="inlineStr"/>
       <c r="J937" t="inlineStr">
         <is>
           <t>美乐棵家庭园艺浓缩营养液是一款水溶性液态肥料，规格500ml，适合各类家庭花卉、蔬菜、果树等植物使用。浓缩配方需按比例稀释后浇灌或叶面喷施，能快速补充植物生长所需的氮磷钾及微量元素。使用便捷，适合室内绿植、阳台花卉及庭院植物的日常追肥。建议生长期每7-14天施用一次，薄肥勤施，避免浓度过高造成肥害。</t>
@@ -45632,8 +45253,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H938" t="inlineStr"/>
-      <c r="I938" t="inlineStr"/>
       <c r="J938" t="inlineStr">
         <is>
           <t>帝罗马橄榄枝长条型盆40是一款造型独特的品牌花盆，采用优质树脂材料制作，具有良好的耐久性和防老化性能。盆体设计灵感来源于橄榄枝纹样，线条流畅自然。长条型设计适合种植多肉植物、香草或小型花卉，也可用于阳台、窗台等空间装饰。底部设有排水孔设计，有效防止积水烂根，是室内外园艺的理想选择。</t>
@@ -45676,8 +45295,6 @@
           <t>BerryBird</t>
         </is>
       </c>
-      <c r="H939" t="inlineStr"/>
-      <c r="I939" t="inlineStr"/>
       <c r="J939" t="inlineStr">
         <is>
           <t>BerryBird木柄迷你修枝剪是一款专业的园艺修剪工具，采用优质木材手柄，手感舒适，便于操作。迷你设计适合精细修剪工作，如修剪花卉、果树嫩枝、多肉植物等。刀片锋利耐用，可轻松剪断细小枝条，是家庭园艺和专业园艺爱好者必备的工具。日常使用后建议清洁刀面并涂抹防锈油以延长使用寿命。</t>
@@ -45720,8 +45337,6 @@
           <t>雪瑞奇</t>
         </is>
       </c>
-      <c r="H940" t="inlineStr"/>
-      <c r="I940" t="inlineStr"/>
       <c r="J940" t="inlineStr">
         <is>
           <t>雪瑞奇小鸟滴水器S透明色是一款适合小型盆栽的自动浇水工具，采用透明设计便于观察水位。采用滴灌原理，通过缓慢滴水为植物提供均匀水分，有效防止浇水过量或不足。适合外出时使用或日常辅助浇水，可连接常见矿泉水瓶使用，安装简便。透明材质可直观看到剩余水量，及时补充。是阳台花卉、室内绿植的理想浇水辅助工具。</t>
@@ -45759,9 +45374,6 @@
           <t>水溶肥</t>
         </is>
       </c>
-      <c r="G941" t="inlineStr"/>
-      <c r="H941" t="inlineStr"/>
-      <c r="I941" t="inlineStr"/>
       <c r="J941" t="inlineStr">
         <is>
           <t>水溶性肥料SL10-30-20是一种高磷配方的开花专用肥料，氮磷钾比例为10-30-20，适用于各类开花植物在花期前后使用。能有效促进花芽分化，增加花苞数量，提升花朵色泽与质量。使用时需按说明稀释后均匀浇灌或叶面喷施，遵循薄肥勤施原则，避免浓肥烧根。</t>
@@ -45804,8 +45416,6 @@
           <t>领优</t>
         </is>
       </c>
-      <c r="H942" t="inlineStr"/>
-      <c r="I942" t="inlineStr"/>
       <c r="J942" t="inlineStr">
         <is>
           <t>领优缓释药肥是一种集施肥与防虫于一体的园艺用品，采用缓释技术使养分和药效缓慢释放，持续为植物提供营养的同时有效防治害虫。10克×10袋的小包装设计便于保存和使用，撒施方式操作简便，适用于家庭园艺花卉、蔬菜、果树等多种植物的日常养护。使用时均匀撒施于盆土表面或土壤中，配合浇水效果更佳。注意避免与种子或幼苗直接接触，使用时做好防护措施。</t>
@@ -45848,8 +45458,6 @@
           <t>维特</t>
         </is>
       </c>
-      <c r="H943" t="inlineStr"/>
-      <c r="I943" t="inlineStr"/>
       <c r="J943" t="inlineStr">
         <is>
           <t>维特0-25泥炭是一种园艺栽培介质，颗粒规格为0-25mm，适合作为植物栽培基质或土壤改良材料。泥炭具有优异的保水性和透气性，能有效改善土壤结构，适用于花卉、蔬菜、果树等多种植物的种植。Big Bale大包装设计适合规模化园艺生产或专业苗圃使用。</t>
@@ -45892,8 +45500,6 @@
           <t>BerryBird</t>
         </is>
       </c>
-      <c r="H944" t="inlineStr"/>
-      <c r="I944" t="inlineStr"/>
       <c r="J944" t="inlineStr">
         <is>
           <t>BerryBird小蛮腰镰刀是一款专为园艺修剪设计的工具，造型纤细灵巧，握柄符合人体工学，舒适省力。刀刃锋利耐用，适合修剪枝条、收割草本植物、清理杂草等园艺作业。独特的小蛮腰设计便于握持和操控，适合家庭园艺爱好者日常使用。</t>
@@ -45936,8 +45542,6 @@
           <t>爱贝施</t>
         </is>
       </c>
-      <c r="H945" t="inlineStr"/>
-      <c r="I945" t="inlineStr"/>
       <c r="J945" t="inlineStr">
         <is>
           <t>爱贝施缓释肥料是一种包膜型缓释肥料，氮磷钾配比为16-06-16，并添加TE（微量元素），可维持5-6个月的肥效释放。适用于各类园艺植物的基肥或追肥使用，能持续为植物提供均衡营养，减少施肥频次，省时省力。使用时建议作为基肥与土壤混合，或撒施于盆土表面后轻拌，注意避免直接接触根系。使用量可根据植株大小和容器规格适当调整。</t>
@@ -46059,14 +45663,46 @@
           <t>HY-东洋鹃“爱丁堡”</t>
         </is>
       </c>
-      <c r="C948" t="inlineStr"/>
-      <c r="D948" t="inlineStr"/>
-      <c r="E948" t="inlineStr"/>
-      <c r="F948" t="inlineStr"/>
-      <c r="G948" t="inlineStr"/>
-      <c r="H948" t="inlineStr"/>
-      <c r="I948" t="inlineStr"/>
-      <c r="J948" t="inlineStr"/>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>植物</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>种苗苗木</t>
+        </is>
+      </c>
+      <c r="E948" t="inlineStr">
+        <is>
+          <t>灌木</t>
+        </is>
+      </c>
+      <c r="F948" t="inlineStr">
+        <is>
+          <t>杜鹃</t>
+        </is>
+      </c>
+      <c r="G948" t="inlineStr">
+        <is>
+          <t>HY</t>
+        </is>
+      </c>
+      <c r="H948" t="inlineStr">
+        <is>
+          <t>东洋鹃</t>
+        </is>
+      </c>
+      <c r="I948" t="inlineStr">
+        <is>
+          <t>爱丁堡</t>
+        </is>
+      </c>
+      <c r="J948" t="inlineStr">
+        <is>
+          <t>东洋杜鹃'爱丁堡'是经典的观赏性灌木花卉，株型紧凑小巧，花色艳丽丰富，花期较长。喜酸性、疏松透气的土壤环境，喜半阴通风条件，忌暴晒和积水。适合庭院种植、花境搭配或盆栽观赏。春季开花为主，花量大，观赏价值高。养护时注意保持土壤酸性，适时修剪施肥，冬季注意防寒。</t>
+        </is>
+      </c>
     </row>
     <row r="949">
       <c r="A949" t="inlineStr">
@@ -46096,27 +45732,27 @@
       </c>
       <c r="F949" t="inlineStr">
         <is>
-          <t>其他灌木</t>
+          <t>杜鹃</t>
         </is>
       </c>
       <c r="G949" t="inlineStr">
         <is>
-          <t>蓝标</t>
+          <t>HY</t>
         </is>
       </c>
       <c r="H949" t="inlineStr">
         <is>
-          <t>穗花牡荆</t>
+          <t>杜鹃</t>
         </is>
       </c>
       <c r="I949" t="inlineStr">
         <is>
-          <t>AC0001-AC0095</t>
+          <t>爱丁堡</t>
         </is>
       </c>
       <c r="J949" t="inlineStr">
         <is>
-          <t>穗花牡荆是马鞭草科牡荆属的落叶灌木植物，原产于北美地区。其特点是花序呈穗状，花色通常为蓝色或紫色，花期较长，具有较高的观赏价值。株型紧凑，适应性强，耐热耐寒，适合庭院种植或作为景观点缀。喜阳光充足的环境，土壤要求不严，管理粗放，是优良的园艺灌木品种。</t>
+          <t>东洋杜鹃‘爱丁堡’是经典的杜鹃花品种，花色艳丽，花期较长，适合庭院种植和盆栽观赏。性喜酸性土壤和半阴环境，怕强光直射，需保持湿润但不积水。冬季注意防寒，夏季适当遮阴。开花时花朵密集，具有较高的观赏价值，是园林绿化和家庭园艺的优选品种。</t>
         </is>
       </c>
     </row>
@@ -46416,8 +46052,6 @@
           <t>雪瑞奇</t>
         </is>
       </c>
-      <c r="H955" t="inlineStr"/>
-      <c r="I955" t="inlineStr"/>
       <c r="J955" t="inlineStr">
         <is>
           <t>雪瑞奇小鸟造型滴水器M型橙色款，是一款可爱的园艺浇水辅助工具。采用小鸟外观设计，兼具装饰性与实用性，可实现缓慢、均匀的滴灌效果，适用于盆栽植物、花卉育苗等场景的精准浇水需求，有效避免水流过大造成土壤冲刷或植物根系损伤，是家庭园艺、小型花园的实用浇水配件。</t>
@@ -46460,8 +46094,6 @@
           <t>嘉伯瑞</t>
         </is>
       </c>
-      <c r="H956" t="inlineStr"/>
-      <c r="I956" t="inlineStr"/>
       <c r="J956" t="inlineStr">
         <is>
           <t>嘉伯瑞魔法师创意盆22#海岩蓝色系，设计独特美观，适合室内外绿植栽培养护。优质树脂材质，坚固耐用，透气性好，有利于植物根系生长。22号尺寸适中，可种植各类小型花卉、蔬菜或多肉植物。海岩蓝色清新自然，为家居园艺增添时尚气息。</t>
@@ -46504,8 +46136,6 @@
           <t>ARTSTONE</t>
         </is>
       </c>
-      <c r="H957" t="inlineStr"/>
-      <c r="I957" t="inlineStr"/>
       <c r="J957" t="inlineStr">
         <is>
           <t>ARTSTONE品牌水泥花盆，正方形设计，边缘采用酷边造型，37厘米规格，灰色配色。适合家庭园艺种植，可用于阳台、庭院、花园等空间摆放。水泥材质坚固耐用，具有良好的透气性和排水性，适合种植各类草本花卉、灌木等植物。灰色设计简约大方，可与现代园艺风格完美搭配。日常养护时注意避免暴晒和过度潮湿，定期清洁保持美观。</t>
@@ -46704,8 +46334,6 @@
           <t>未提供</t>
         </is>
       </c>
-      <c r="H961" t="inlineStr"/>
-      <c r="I961" t="inlineStr"/>
       <c r="J961" t="inlineStr">
         <is>
           <t>定制家庭园艺营养土，专为家庭园艺设计，容量12L。采用科学配比的混合介质，富含植物生长所需的有机质和营养成分，透气性好、保水性强，适合种植蔬菜、花卉、果树等各类家庭园艺植物。可直接用于盆栽、花坛或阳台种植，能够改善土壤结构，促进根系发育，提高植物成活率和生长质量。适合家庭园艺新手和日常花卉蔬菜种植使用。</t>
@@ -46852,8 +46480,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H964" t="inlineStr"/>
-      <c r="I964" t="inlineStr"/>
       <c r="J964" t="inlineStr">
         <is>
           <t>帝罗马带边高圆型白陶花盆，优质陶土高温烧制而成，质地细腻坚硬，透气性好，适合栽种各类室内外植物。白色陶瓷表面简洁大方，带边设计增加稳定性，高圆型盆身适合种植株型较高的植物，如绿植、花卉或多肉植物等。21号规格（21厘米口径），是家用园艺的经典选择，适用于阳台、花园、客厅等多种场景。</t>
@@ -46896,8 +46522,6 @@
           <t>未提供</t>
         </is>
       </c>
-      <c r="H965" t="inlineStr"/>
-      <c r="I965" t="inlineStr"/>
       <c r="J965" t="inlineStr">
         <is>
           <t>园艺通用触屏手套是一款专为园艺作业设计的防护手套，采用导电纤维材质，可在戴手套时直接操作手机触屏设备，方便用户在园艺操作过程中接听电话或查看信息。手套尺码为S号，浅蓝色设计，尺寸小巧轻便，适合手型较小的用户使用。主要用于园林种植、修剪、浇水等园艺活动中保护双手，同时避免频繁穿脱手套的麻烦，提升园艺作业的便利性和效率。</t>
@@ -46940,8 +46564,6 @@
           <t>马雅</t>
         </is>
       </c>
-      <c r="H966" t="inlineStr"/>
-      <c r="I966" t="inlineStr"/>
       <c r="J966" t="inlineStr">
         <is>
           <t>马雅92.1玫瑰月季专用液体肥料，容量500ml，专为月季植物研发的配方肥料。富含月季生长所需的氮磷钾及微量元素，能有效促进月季开花、增强抗病能力、改善土壤环境。适用于家庭园艺月季盆栽及庭院月季的日常养护，按比例稀释后浇灌或叶面喷施。使用便捷，适合春夏季月季生长旺期及花期前后施用。</t>
@@ -47036,8 +46658,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H968" t="inlineStr"/>
-      <c r="I968" t="inlineStr"/>
       <c r="J968" t="inlineStr">
         <is>
           <t>花彩师缓释肥料是一款通用型肥料，氮磷钾配比为14-14-14，营养均衡全面，并特别添加TE微量元素，可满足各类花卉、蔬菜、果树等植物生长需求。500g包装适合家庭园艺使用。缓释技术使养分缓慢释放，持续供应约2-3个月，减少施肥频率，避免烧根。使用方便，适用于基肥和追肥，可直接撒施或浅埋于盆土中。</t>
@@ -47288,8 +46908,6 @@
           <t>嘉伯瑞</t>
         </is>
       </c>
-      <c r="H973" t="inlineStr"/>
-      <c r="I973" t="inlineStr"/>
       <c r="J973" t="inlineStr">
         <is>
           <t>嘉伯瑞魔法师创意盆22#星空灰是一款设计独特的园艺花盆，采用创意魔法师主题设计，星空灰色调营造神秘优雅的视觉效果。22号规格适合种植中小型植物，可用于阳台、庭院、客厅等场景摆设。该盆具有良好的透气性和排水性，有助于植物根系呼吸和水分管理。采用优质材料制作，耐用性强，适合室内外使用。</t>
@@ -47332,8 +46950,6 @@
           <t>嘉伯瑞</t>
         </is>
       </c>
-      <c r="H974" t="inlineStr"/>
-      <c r="I974" t="inlineStr"/>
       <c r="J974" t="inlineStr">
         <is>
           <t>嘉伯瑞品牌米兰花盆45#，采用摩卡色设计，外观简约大方，适合室内外绿植栽培养护。树脂材质，轻便耐用，不易碎裂，便于搬运和摆放。口径约45cm，深度适中，适合种植中大型植物或小型灌木。透气性好，有利于植物根系生长。经典的摩卡色调能够与多种家居风格和植物搭配，提升整体观赏效果。</t>
@@ -47376,8 +46992,6 @@
           <t>君沐</t>
         </is>
       </c>
-      <c r="H975" t="inlineStr"/>
-      <c r="I975" t="inlineStr"/>
       <c r="J975" t="inlineStr">
         <is>
           <t>君沐0.76米浇水把手是一款实用的园艺浇水配件，长度为0.76米，采用人体工学设计，握持舒适，操作便捷。该产品未带开关设计，适用于连接水管进行浇水作业。延长把手设计适合需要远程浇水的场景，如阳台花卉、高处植物或大面积庭院灌溉。材质坚固耐用，适用于各类园艺浇水场景，是家庭园艺和庭院浇水的理想辅助工具。</t>
@@ -47420,8 +47034,6 @@
           <t>嘉伯瑞</t>
         </is>
       </c>
-      <c r="H976" t="inlineStr"/>
-      <c r="I976" t="inlineStr"/>
       <c r="J976" t="inlineStr">
         <is>
           <t>嘉伯瑞梅卡系列花盆，规格24#，泥红色配色。该花盆采用优质树脂材质，轻便耐用，适合室内外园艺使用。具有良好的透气透水性设计，底部设有排水孔，可有效防止积水烂根。简约时尚的设计风格，适合种植各类草本花卉、盆栽植物等。抗老化、耐候性强，可长期户外使用。</t>
@@ -47464,8 +47076,6 @@
           <t>嘉伯瑞</t>
         </is>
       </c>
-      <c r="H977" t="inlineStr"/>
-      <c r="I977" t="inlineStr"/>
       <c r="J977" t="inlineStr">
         <is>
           <t>嘉伯瑞梅卡系列花盆29#，采用优质树脂材质制成，泥红色配色自然温馨。29号规格适合种植中小型花卉植物，如多肉植物、小型观叶植物等。花盆设计具有良好的透气性和排水性，底部设有排水孔，防止积水导致根系腐烂。外观造型简约大方，适合家庭阳台、窗台、桌面等场景摆放。耐久度高，不易褪色，可长期室内外使用。日常清洁只需用湿布擦拭即可。</t>
@@ -47763,13 +47373,11 @@
           <t>其他灌木</t>
         </is>
       </c>
-      <c r="G983" t="inlineStr"/>
       <c r="H983" t="inlineStr">
         <is>
           <t>喷雪花</t>
         </is>
       </c>
-      <c r="I983" t="inlineStr"/>
       <c r="J983" t="inlineStr">
         <is>
           <t>喷雪花学名Spiraea thunbergii，又称雪柳，是蔷薇科绣线菊属落叶灌木。其特点为春季开白色小花，花量极大，盛花时枝条上布满白色花朵，形似喷洒的雪花，故名"喷雪花"。株高可达1-2米，枝条细长柔软，呈拱形下垂。喜阳光充足的环境，耐寒性强，适应范围广，对土壤要求不严。适合种植于庭院、花境、路边或作绿篱使用，也可作为盆景素材。花后适当修剪可促进新枝生长，增加来年开花量。</t>
@@ -47812,8 +47420,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H984" t="inlineStr"/>
-      <c r="I984" t="inlineStr"/>
       <c r="J984" t="inlineStr">
         <is>
           <t>花彩师植物高浓缩营养液是一种高效液体肥料，采用科学配比，富含氮磷钾及微量元素，适合各类花卉、蔬菜、果树使用。高浓缩配方，小包装大能量，使用时按比例稀释即可。通用型设计，适用于家庭园艺、蔬菜种植、室内绿植养护等场景。液体形态溶解迅速，植物吸收率高，可通过浇灌或叶面喷施方式补充养分，促进植物健康生长、叶片翠绿、开花结果。</t>
@@ -47856,8 +47462,6 @@
           <t>花彩师</t>
         </is>
       </c>
-      <c r="H985" t="inlineStr"/>
-      <c r="I985" t="inlineStr"/>
       <c r="J985" t="inlineStr">
         <is>
           <t>花彩师松鳞洋兰介质是一款专为兰科植物（洋兰）配制的栽培基质。以松树皮鳞片为主要原料，经科学配方调制，具有良好的排水透气性，同时兼顾保水性，能有效防止兰科植物根部积水烂根。颗粒规格（7-15）适合洋兰根系附着生长。容量50L，适用于蝴蝶兰、石斛兰、文心兰等兰科花卉的盆栽种植和换盆使用。</t>
@@ -47952,8 +47556,6 @@
           <t>BerryBird</t>
         </is>
       </c>
-      <c r="H987" t="inlineStr"/>
-      <c r="I987" t="inlineStr"/>
       <c r="J987" t="inlineStr">
         <is>
           <t>BerryBird不锈钢女士手叉是专为女性设计的园艺种植工具，采用优质不锈钢材质，耐腐蚀、耐用。前端手叉设计方便松土、挖坑、移栽等种植操作。人性化手柄符合人体工程学，抓握舒适省力，适合花园种植、蔬菜栽培、花卉养护等场景使用。轻便耐用，是家庭园艺种植的好帮手。</t>
@@ -47996,8 +47598,6 @@
           <t>马雅</t>
         </is>
       </c>
-      <c r="H988" t="inlineStr"/>
-      <c r="I988" t="inlineStr"/>
       <c r="J988" t="inlineStr">
         <is>
           <t>马雅园艺浓缩营养液（观叶植物型）是一款专为观叶植物研发的液态肥料，容量500ml，采用浓缩配方设计，配备定量罐便于精准配比使用。产品含有均衡的氮磷钾元素及微量元素，能有效促进观叶植物的叶片生长和色泽鲜艳。使用时需按说明稀释后浇灌或叶面喷施，适用于绿萝、吊兰、龟背竹、虎皮兰等各类观叶植物。建议生长期每7-14天施用一次，冬季可适当减少施肥频率。</t>
@@ -48040,8 +47640,6 @@
           <t>马雅</t>
         </is>
       </c>
-      <c r="H989" t="inlineStr"/>
-      <c r="I989" t="inlineStr"/>
       <c r="J989" t="inlineStr">
         <is>
           <t>马雅Maya15浓缩有机颗粒缓释肥是一种高品质园艺肥料，净含量815g。采用有机颗粒配方，富含植物生长所需的氮磷钾等营养元素。缓释技术使肥料均匀释放，肥效持久可达数月，减少施肥频率。浓缩型设计用量省，适合各类花卉、蔬菜、果树及室内绿植使用。颗粒状便于撒施，可直接穴施或追肥。改善土壤结构，促进植物健康生长，增强抗病能力。适合家庭园艺、阳台种植及专业园艺场所使用。</t>
@@ -48084,8 +47682,6 @@
           <t>帝罗马</t>
         </is>
       </c>
-      <c r="H990" t="inlineStr"/>
-      <c r="I990" t="inlineStr"/>
       <c r="J990" t="inlineStr">
         <is>
           <t>帝罗马品牌圆型托盘，采用白色陶土材质，质感细腻温润，适合搭配帝罗马系列花盆使用。托盘设计用于承接花盆底部多余水分，防止积水污染地面，同时保持盆底通风透气。适用于室内外各种盆栽摆放场景，便于移动清洁，是盆栽养护的实用配件选择。</t>
@@ -48128,8 +47724,6 @@
           <t>BerryBird</t>
         </is>
       </c>
-      <c r="H991" t="inlineStr"/>
-      <c r="I991" t="inlineStr"/>
       <c r="J991" t="inlineStr">
         <is>
           <t>BerryBird不锈钢儿童手铲是一款专为儿童设计的园艺工具，采用优质不锈钢材质，耐用防腐，安全圆头设计保护儿童使用安全。适合3岁以上儿童进行园艺活动，如挖土、移植小植物等，帮助培养孩子的园艺兴趣和动手能力。手柄设计符合儿童人体工程学，握持舒适，是亲子园艺活动的理想工具。</t>
@@ -48484,8 +48078,6 @@
           <t>虹越</t>
         </is>
       </c>
-      <c r="H998" t="inlineStr"/>
-      <c r="I998" t="inlineStr"/>
       <c r="J998" t="inlineStr">
         <is>
           <t>虹越自配颗粒介质是一种预先混合好的园艺专用土壤，由多种颗粒状基质材料配制而成，透气性良好、保水保肥能力强。适用于盆栽植物、花园育苗等多种园艺场景，可直接使用或与其他土壤混合使用。使用前建议先松散介质结构，根据植物种类适当调整配方比例，注意保持介质蓬松避免过度压实。</t>
